--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>58.8</v>
+        <v>55.9</v>
       </c>
       <c r="E5" t="n">
         <v>60.8</v>
@@ -595,10 +595,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>17.6</v>
+        <v>15.9</v>
       </c>
       <c r="H5" t="n">
-        <v>705.4</v>
+        <v>671.3</v>
       </c>
       <c r="I5" t="n">
         <v>826</v>
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>53.3</v>
+        <v>55.7</v>
       </c>
       <c r="E6" t="n">
-        <v>63.6</v>
+        <v>56.2</v>
       </c>
       <c r="F6" t="n">
-        <v>79.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7</v>
+        <v>15.5</v>
       </c>
       <c r="H6" t="n">
-        <v>373.2</v>
+        <v>613</v>
       </c>
       <c r="I6" t="n">
-        <v>833.7</v>
+        <v>818.2</v>
       </c>
       <c r="J6" t="n">
-        <v>953</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>52.9</v>
+        <v>53.3</v>
       </c>
       <c r="E7" t="n">
-        <v>53.1</v>
+        <v>63.6</v>
       </c>
       <c r="F7" t="n">
-        <v>87.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="G7" t="n">
-        <v>15.5</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>528.9</v>
+        <v>373.2</v>
       </c>
       <c r="I7" t="n">
-        <v>816.4</v>
+        <v>833.7</v>
       </c>
       <c r="J7" t="n">
-        <v>960</v>
+        <v>953</v>
       </c>
     </row>
     <row r="8">
@@ -1249,7 +1249,9 @@
       <c r="L6" t="n">
         <v>838</v>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>836</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1845,7 +1847,9 @@
       <c r="L6" t="n">
         <v>50</v>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1887,7 +1891,7 @@
         <v>29.6</v>
       </c>
       <c r="M7" t="n">
-        <v>50</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="8">
@@ -2506,19 +2510,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>773</v>
+        <v>804.5</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="E13" t="n">
-        <v>773</v>
+        <v>804.5</v>
       </c>
       <c r="F13" t="n">
-        <v>773</v>
+        <v>836</v>
       </c>
       <c r="G13" t="n">
         <v>773</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>76.2</v>
       </c>
       <c r="E3" t="n">
-        <v>79.7</v>
+        <v>82</v>
       </c>
       <c r="F3" t="n">
         <v>97.7</v>
@@ -530,10 +530,10 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>825.3</v>
+        <v>914.8</v>
       </c>
       <c r="I3" t="n">
-        <v>877.8</v>
+        <v>880.5</v>
       </c>
       <c r="J3" t="n">
         <v>991</v>
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>55.9</v>
+        <v>55.6</v>
       </c>
       <c r="E5" t="n">
         <v>60.8</v>
@@ -595,10 +595,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>15.9</v>
+        <v>11.7</v>
       </c>
       <c r="H5" t="n">
-        <v>671.3</v>
+        <v>667.1</v>
       </c>
       <c r="I5" t="n">
         <v>826</v>
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>55.7</v>
+        <v>53.3</v>
       </c>
       <c r="E6" t="n">
-        <v>56.2</v>
+        <v>63.6</v>
       </c>
       <c r="F6" t="n">
-        <v>87.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="G6" t="n">
-        <v>15.5</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>613</v>
+        <v>373.2</v>
       </c>
       <c r="I6" t="n">
-        <v>818.2</v>
+        <v>833.7</v>
       </c>
       <c r="J6" t="n">
-        <v>960</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>53.3</v>
+        <v>52.4</v>
       </c>
       <c r="E7" t="n">
-        <v>63.6</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>79.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>373.2</v>
+        <v>576.3</v>
       </c>
       <c r="I7" t="n">
-        <v>833.7</v>
+        <v>818.2</v>
       </c>
       <c r="J7" t="n">
-        <v>953</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8">
@@ -1101,7 +1101,9 @@
       <c r="L2" t="n">
         <v>898</v>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>910</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1699,7 +1701,9 @@
       <c r="L2" t="n">
         <v>77.3</v>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>89.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1848,7 +1852,7 @@
         <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>84.09999999999999</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="7">
@@ -1891,7 +1895,7 @@
         <v>29.6</v>
       </c>
       <c r="M7" t="n">
-        <v>15.9</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="8">
@@ -2510,19 +2514,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>804.5</v>
+        <v>839.7</v>
       </c>
       <c r="D13" t="n">
-        <v>31.5</v>
+        <v>56</v>
       </c>
       <c r="E13" t="n">
-        <v>804.5</v>
+        <v>836</v>
       </c>
       <c r="F13" t="n">
-        <v>836</v>
+        <v>910</v>
       </c>
       <c r="G13" t="n">
         <v>773</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>76.2</v>
+        <v>75</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>79.7</v>
       </c>
       <c r="F3" t="n">
         <v>97.7</v>
@@ -530,10 +530,10 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>914.8</v>
+        <v>825.3</v>
       </c>
       <c r="I3" t="n">
-        <v>880.5</v>
+        <v>877.8</v>
       </c>
       <c r="J3" t="n">
         <v>991</v>
@@ -583,25 +583,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>55.6</v>
+        <v>59.6</v>
       </c>
       <c r="E5" t="n">
-        <v>60.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>11.7</v>
+        <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>667.1</v>
+        <v>655.4</v>
       </c>
       <c r="I5" t="n">
-        <v>826</v>
+        <v>830.8</v>
       </c>
       <c r="J5" t="n">
         <v>975</v>
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>52.4</v>
+        <v>52.9</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>53.1</v>
       </c>
       <c r="F7" t="n">
         <v>87.90000000000001</v>
@@ -666,10 +666,10 @@
         <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>576.3</v>
+        <v>528.9</v>
       </c>
       <c r="I7" t="n">
-        <v>818.2</v>
+        <v>816.4</v>
       </c>
       <c r="J7" t="n">
         <v>960</v>
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>waltkin</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="E9" t="n">
-        <v>44.8</v>
+        <v>47.8</v>
       </c>
       <c r="F9" t="n">
-        <v>90.90000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>480</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>798.3</v>
+        <v>824</v>
       </c>
       <c r="J9" t="n">
-        <v>928</v>
+        <v>845</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>waltkin</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>47.8</v>
+        <v>45.1</v>
       </c>
       <c r="E10" t="n">
-        <v>47.8</v>
+        <v>38.9</v>
       </c>
       <c r="F10" t="n">
-        <v>91.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>95.59999999999999</v>
+        <v>495.9</v>
       </c>
       <c r="I10" t="n">
-        <v>824</v>
+        <v>785.4</v>
       </c>
       <c r="J10" t="n">
-        <v>845</v>
+        <v>928</v>
       </c>
     </row>
     <row r="11">
@@ -889,25 +889,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>14.3</v>
+        <v>21.2</v>
       </c>
       <c r="E14" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="F14" t="n">
-        <v>44.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>128.3</v>
+        <v>212.4</v>
       </c>
       <c r="I14" t="n">
-        <v>684.6</v>
+        <v>695.4</v>
       </c>
       <c r="J14" t="n">
         <v>832</v>
@@ -1101,9 +1101,7 @@
       <c r="L2" t="n">
         <v>898</v>
       </c>
-      <c r="M2" t="n">
-        <v>910</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1251,9 +1249,7 @@
       <c r="L6" t="n">
         <v>838</v>
       </c>
-      <c r="M6" t="n">
-        <v>836</v>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1294,9 +1290,7 @@
       <c r="L7" t="n">
         <v>795</v>
       </c>
-      <c r="M7" t="n">
-        <v>773</v>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1335,7 +1329,9 @@
       <c r="L8" t="n">
         <v>699</v>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>656</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1556,7 +1552,9 @@
       <c r="L15" t="n">
         <v>728</v>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>793</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1701,9 +1699,7 @@
       <c r="L2" t="n">
         <v>77.3</v>
       </c>
-      <c r="M2" t="n">
-        <v>89.5</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1851,9 +1847,7 @@
       <c r="L6" t="n">
         <v>50</v>
       </c>
-      <c r="M6" t="n">
-        <v>47.4</v>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1894,9 +1888,7 @@
       <c r="L7" t="n">
         <v>29.6</v>
       </c>
-      <c r="M7" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1935,7 +1927,9 @@
       <c r="L8" t="n">
         <v>4.2</v>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2156,7 +2150,9 @@
       <c r="L15" t="n">
         <v>8.5</v>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2514,22 +2510,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>839.7</v>
+        <v>724.5</v>
       </c>
       <c r="D13" t="n">
-        <v>56</v>
+        <v>68.5</v>
       </c>
       <c r="E13" t="n">
-        <v>836</v>
+        <v>724.5</v>
       </c>
       <c r="F13" t="n">
-        <v>910</v>
+        <v>793</v>
       </c>
       <c r="G13" t="n">
-        <v>773</v>
+        <v>656</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>45.1</v>
+        <v>42.6</v>
       </c>
       <c r="E10" t="n">
-        <v>38.9</v>
+        <v>37.4</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,10 +768,10 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>495.9</v>
+        <v>511.8</v>
       </c>
       <c r="I10" t="n">
-        <v>785.4</v>
+        <v>774.6</v>
       </c>
       <c r="J10" t="n">
         <v>928</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>21.2</v>
+        <v>27</v>
       </c>
       <c r="E14" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>212.4</v>
+        <v>296.5</v>
       </c>
       <c r="I14" t="n">
-        <v>695.4</v>
+        <v>704.3</v>
       </c>
       <c r="J14" t="n">
         <v>832</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1061,6 +1061,11 @@
           <t>9/13/26</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>9/14/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1102,6 +1107,7 @@
         <v>898</v>
       </c>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1143,6 +1149,7 @@
         <v>956</v>
       </c>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1178,6 +1185,7 @@
         <v>798</v>
       </c>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1211,6 +1219,7 @@
         <v>866</v>
       </c>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1250,6 +1259,7 @@
         <v>838</v>
       </c>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1291,6 +1301,7 @@
         <v>795</v>
       </c>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1330,6 +1341,9 @@
         <v>699</v>
       </c>
       <c r="M8" t="n">
+        <v>656</v>
+      </c>
+      <c r="N8" t="n">
         <v>656</v>
       </c>
     </row>
@@ -1353,6 +1367,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1392,6 +1407,7 @@
         <v>860</v>
       </c>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1419,6 +1435,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1446,6 +1463,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1503,7 @@
         <v>942</v>
       </c>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1516,6 +1535,7 @@
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1553,6 +1573,9 @@
         <v>728</v>
       </c>
       <c r="M15" t="n">
+        <v>793</v>
+      </c>
+      <c r="N15" t="n">
         <v>793</v>
       </c>
     </row>
@@ -1578,6 +1601,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1590,7 +1614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1659,6 +1683,11 @@
           <t>9/13/26</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>9/14/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1700,6 +1729,7 @@
         <v>77.3</v>
       </c>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1741,6 +1771,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1776,6 +1807,7 @@
         <v>30.9</v>
       </c>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1809,6 +1841,7 @@
         <v>63.6</v>
       </c>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1848,6 +1881,7 @@
         <v>50</v>
       </c>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1889,6 +1923,7 @@
         <v>29.6</v>
       </c>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1928,6 +1963,9 @@
         <v>4.2</v>
       </c>
       <c r="M8" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N8" t="n">
         <v>15.9</v>
       </c>
     </row>
@@ -1951,6 +1989,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1990,6 +2029,7 @@
         <v>60.8</v>
       </c>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2017,6 +2057,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2044,6 +2085,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2083,6 +2125,7 @@
         <v>90.2</v>
       </c>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2114,6 +2157,7 @@
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2151,6 +2195,9 @@
         <v>8.5</v>
       </c>
       <c r="M15" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="N15" t="n">
         <v>84.09999999999999</v>
       </c>
     </row>
@@ -2176,6 +2223,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2188,7 +2236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2528,6 +2576,31 @@
         <v>656</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>9/14/26</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>724.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>724.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>793</v>
+      </c>
+      <c r="G14" t="n">
+        <v>656</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>59.6</v>
+        <v>58.1</v>
       </c>
       <c r="E5" t="n">
-        <v>65.40000000000001</v>
+        <v>60.8</v>
       </c>
       <c r="F5" t="n">
         <v>89.09999999999999</v>
@@ -598,10 +598,10 @@
         <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>655.4</v>
+        <v>697.2</v>
       </c>
       <c r="I5" t="n">
-        <v>830.8</v>
+        <v>820.5</v>
       </c>
       <c r="J5" t="n">
         <v>975</v>
@@ -756,7 +756,7 @@
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>511.8</v>
+        <v>509.3</v>
       </c>
       <c r="I10" t="n">
         <v>774.6</v>
@@ -892,19 +892,19 @@
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="E14" t="n">
         <v>10.5</v>
       </c>
       <c r="F14" t="n">
-        <v>84.09999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>296.5</v>
+        <v>303</v>
       </c>
       <c r="I14" t="n">
         <v>704.3</v>
@@ -1301,7 +1301,9 @@
         <v>795</v>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>707</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1923,7 +1925,9 @@
         <v>29.6</v>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>41.8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1966,7 +1970,7 @@
         <v>15.9</v>
       </c>
       <c r="N8" t="n">
-        <v>15.9</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="9">
@@ -2198,7 +2202,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>84.09999999999999</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2583,16 +2587,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>724.5</v>
+        <v>718.7</v>
       </c>
       <c r="D14" t="n">
-        <v>68.5</v>
+        <v>56.5</v>
       </c>
       <c r="E14" t="n">
-        <v>724.5</v>
+        <v>707</v>
       </c>
       <c r="F14" t="n">
         <v>793</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>58.1</v>
+        <v>57.5</v>
       </c>
       <c r="E5" t="n">
         <v>60.8</v>
@@ -598,7 +598,7 @@
         <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>697.2</v>
+        <v>689.9</v>
       </c>
       <c r="I5" t="n">
         <v>820.5</v>
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>52.9</v>
+        <v>53.2</v>
       </c>
       <c r="E7" t="n">
-        <v>53.1</v>
+        <v>54.5</v>
       </c>
       <c r="F7" t="n">
-        <v>87.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>15.5</v>
+        <v>22.2</v>
       </c>
       <c r="H7" t="n">
-        <v>528.9</v>
+        <v>479</v>
       </c>
       <c r="I7" t="n">
-        <v>816.4</v>
+        <v>816.1</v>
       </c>
       <c r="J7" t="n">
-        <v>960</v>
+        <v>930</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>51.2</v>
+        <v>52.9</v>
       </c>
       <c r="E8" t="n">
-        <v>51.8</v>
+        <v>53.1</v>
       </c>
       <c r="F8" t="n">
-        <v>80.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>22.2</v>
+        <v>15.5</v>
       </c>
       <c r="H8" t="n">
-        <v>409.3</v>
+        <v>528.9</v>
       </c>
       <c r="I8" t="n">
-        <v>823.9</v>
+        <v>816.4</v>
       </c>
       <c r="J8" t="n">
-        <v>930</v>
+        <v>960</v>
       </c>
     </row>
     <row r="9">
@@ -756,7 +756,7 @@
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>42.4</v>
+        <v>42</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>509.3</v>
+        <v>504.1</v>
       </c>
       <c r="I10" t="n">
         <v>774.6</v>
@@ -898,13 +898,13 @@
         <v>10.5</v>
       </c>
       <c r="F14" t="n">
-        <v>90.59999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>303</v>
+        <v>302.3</v>
       </c>
       <c r="I14" t="n">
         <v>704.3</v>
@@ -1185,7 +1185,9 @@
         <v>798</v>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>754</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1809,7 +1811,9 @@
         <v>30.9</v>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>69.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1926,7 +1930,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>41.8</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="8">
@@ -1970,7 +1974,7 @@
         <v>15.9</v>
       </c>
       <c r="N8" t="n">
-        <v>13.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2202,7 +2206,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>90.59999999999999</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2587,16 +2591,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>718.7</v>
+        <v>727.5</v>
       </c>
       <c r="D14" t="n">
-        <v>56.5</v>
+        <v>51.3</v>
       </c>
       <c r="E14" t="n">
-        <v>707</v>
+        <v>730.5</v>
       </c>
       <c r="F14" t="n">
         <v>793</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,25 +481,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>80.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="E2" t="n">
-        <v>86.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>94.2</v>
       </c>
       <c r="G2" t="n">
-        <v>40.5</v>
+        <v>38.9</v>
       </c>
       <c r="H2" t="n">
-        <v>887.1</v>
+        <v>926</v>
       </c>
       <c r="I2" t="n">
-        <v>893.7</v>
+        <v>879.5</v>
       </c>
       <c r="J2" t="n">
         <v>997</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>76.5</v>
       </c>
       <c r="E3" t="n">
-        <v>79.7</v>
+        <v>82</v>
       </c>
       <c r="F3" t="n">
         <v>97.7</v>
@@ -530,10 +530,10 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>825.3</v>
+        <v>918.2</v>
       </c>
       <c r="I3" t="n">
-        <v>877.8</v>
+        <v>871.8</v>
       </c>
       <c r="J3" t="n">
         <v>991</v>
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>57.5</v>
+        <v>56.8</v>
       </c>
       <c r="E5" t="n">
         <v>60.8</v>
@@ -598,7 +598,7 @@
         <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>689.9</v>
+        <v>682</v>
       </c>
       <c r="I5" t="n">
         <v>820.5</v>
@@ -654,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>53.2</v>
+        <v>52.7</v>
       </c>
       <c r="E7" t="n">
         <v>54.5</v>
@@ -666,7 +666,7 @@
         <v>22.2</v>
       </c>
       <c r="H7" t="n">
-        <v>479</v>
+        <v>474.1</v>
       </c>
       <c r="I7" t="n">
         <v>816.1</v>
@@ -685,25 +685,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>52.9</v>
+        <v>49.4</v>
       </c>
       <c r="E8" t="n">
-        <v>53.1</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
         <v>87.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>15.5</v>
+        <v>14.1</v>
       </c>
       <c r="H8" t="n">
-        <v>528.9</v>
+        <v>543</v>
       </c>
       <c r="I8" t="n">
-        <v>816.4</v>
+        <v>804.5</v>
       </c>
       <c r="J8" t="n">
         <v>960</v>
@@ -756,7 +756,7 @@
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>504.1</v>
+        <v>500.2</v>
       </c>
       <c r="I10" t="n">
         <v>774.6</v>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="E12" t="n">
-        <v>36.6</v>
+        <v>40.2</v>
       </c>
       <c r="F12" t="n">
         <v>67.5</v>
@@ -836,10 +836,10 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>349.5</v>
+        <v>393.4</v>
       </c>
       <c r="I12" t="n">
-        <v>765.4</v>
+        <v>762.1</v>
       </c>
       <c r="J12" t="n">
         <v>924</v>
@@ -892,19 +892,19 @@
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="E14" t="n">
         <v>10.5</v>
       </c>
       <c r="F14" t="n">
-        <v>89.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="G14" t="n">
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>302.3</v>
+        <v>301.2</v>
       </c>
       <c r="I14" t="n">
         <v>704.3</v>
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>26.8</v>
       </c>
       <c r="E15" t="n">
-        <v>6.9</v>
+        <v>10.5</v>
       </c>
       <c r="F15" t="n">
-        <v>40.4</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>55.5</v>
+        <v>133.9</v>
       </c>
       <c r="I15" t="n">
-        <v>702</v>
+        <v>716.2</v>
       </c>
       <c r="J15" t="n">
         <v>832</v>
@@ -1107,7 +1107,9 @@
         <v>898</v>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>805</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1149,7 +1151,9 @@
         <v>956</v>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>723</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1261,7 +1265,9 @@
         <v>838</v>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>686</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1411,7 +1417,9 @@
         <v>860</v>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>729</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1439,7 +1447,9 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>773</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1733,7 +1743,9 @@
         <v>77.3</v>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>92.90000000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1775,7 +1787,9 @@
         <v>92.90000000000001</v>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>38.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1812,7 +1826,7 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>69.7</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="5">
@@ -1887,7 +1901,9 @@
         <v>50</v>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>14.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1930,7 +1946,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>34.5</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="8">
@@ -1974,7 +1990,7 @@
         <v>15.9</v>
       </c>
       <c r="N8" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="9">
@@ -2037,7 +2053,9 @@
         <v>60.8</v>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>43.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2065,7 +2083,9 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>78.40000000000001</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2206,7 +2226,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>89.90000000000001</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="16">
@@ -2591,19 +2611,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>727.5</v>
+        <v>736.2</v>
       </c>
       <c r="D14" t="n">
-        <v>51.3</v>
+        <v>46.7</v>
       </c>
       <c r="E14" t="n">
-        <v>730.5</v>
+        <v>729</v>
       </c>
       <c r="F14" t="n">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="G14" t="n">
         <v>656</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="E2" t="n">
         <v>86.09999999999999</v>
@@ -493,10 +493,10 @@
         <v>94.2</v>
       </c>
       <c r="G2" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>926</v>
+        <v>927.6</v>
       </c>
       <c r="I2" t="n">
         <v>879.5</v>
@@ -518,7 +518,7 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>76.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E3" t="n">
         <v>82</v>
@@ -530,7 +530,7 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>918.2</v>
+        <v>919.6</v>
       </c>
       <c r="I3" t="n">
         <v>871.8</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>67.09999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="E4" t="n">
-        <v>79.8</v>
+        <v>78.3</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>671.3</v>
+        <v>702.7</v>
       </c>
       <c r="I4" t="n">
-        <v>842.5</v>
+        <v>830.6</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="E5" t="n">
         <v>60.8</v>
@@ -598,7 +598,7 @@
         <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>682</v>
+        <v>682.9</v>
       </c>
       <c r="I5" t="n">
         <v>820.5</v>
@@ -654,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>52.7</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
         <v>54.5</v>
@@ -666,7 +666,7 @@
         <v>22.2</v>
       </c>
       <c r="H7" t="n">
-        <v>474.1</v>
+        <v>476.6</v>
       </c>
       <c r="I7" t="n">
         <v>816.1</v>
@@ -697,10 +697,10 @@
         <v>87.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="H8" t="n">
-        <v>543</v>
+        <v>543.3</v>
       </c>
       <c r="I8" t="n">
         <v>804.5</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>500.2</v>
+        <v>500.1</v>
       </c>
       <c r="I10" t="n">
         <v>774.6</v>
@@ -824,7 +824,7 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="E12" t="n">
         <v>40.2</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>393.4</v>
+        <v>395.2</v>
       </c>
       <c r="I12" t="n">
         <v>762.1</v>
@@ -892,19 +892,19 @@
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="E14" t="n">
         <v>10.5</v>
       </c>
       <c r="F14" t="n">
-        <v>88.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>301.2</v>
+        <v>303</v>
       </c>
       <c r="I14" t="n">
         <v>704.3</v>
@@ -926,19 +926,19 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>26.8</v>
+        <v>27.3</v>
       </c>
       <c r="E15" t="n">
         <v>10.5</v>
       </c>
       <c r="F15" t="n">
-        <v>78.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>133.9</v>
+        <v>136.4</v>
       </c>
       <c r="I15" t="n">
         <v>716.2</v>
@@ -1517,7 +1517,9 @@
         <v>942</v>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>712</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1744,7 +1746,7 @@
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>92.90000000000001</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="3">
@@ -1788,7 +1790,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="4">
@@ -1826,7 +1828,7 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>64.8</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="5">
@@ -1902,7 +1904,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="7">
@@ -1946,7 +1948,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>26.6</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="8">
@@ -1990,7 +1992,7 @@
         <v>15.9</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="9">
@@ -2054,7 +2056,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>43.9</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="11">
@@ -2084,7 +2086,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>78.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2153,7 +2155,9 @@
         <v>90.2</v>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>31.4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2226,7 +2230,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>88.8</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2611,16 +2615,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>736.2</v>
+        <v>733.8</v>
       </c>
       <c r="D14" t="n">
-        <v>46.7</v>
+        <v>44.9</v>
       </c>
       <c r="E14" t="n">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="F14" t="n">
         <v>805</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>77.3</v>
+        <v>76.8</v>
       </c>
       <c r="E2" t="n">
         <v>86.09999999999999</v>
@@ -493,10 +493,10 @@
         <v>94.2</v>
       </c>
       <c r="G2" t="n">
-        <v>40.5</v>
+        <v>34.4</v>
       </c>
       <c r="H2" t="n">
-        <v>927.6</v>
+        <v>921.5</v>
       </c>
       <c r="I2" t="n">
         <v>879.5</v>
@@ -518,10 +518,10 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>76.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>78.5</v>
       </c>
       <c r="F3" t="n">
         <v>97.7</v>
@@ -530,7 +530,7 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>919.6</v>
+        <v>899.5</v>
       </c>
       <c r="I3" t="n">
         <v>871.8</v>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>waltkin</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>63.9</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>78.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>93.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>11.4</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>702.7</v>
+        <v>195.2</v>
       </c>
       <c r="I4" t="n">
-        <v>830.6</v>
+        <v>869.3</v>
       </c>
       <c r="J4" t="n">
-        <v>991</v>
+        <v>960</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>56.9</v>
+        <v>63.7</v>
       </c>
       <c r="E5" t="n">
-        <v>60.8</v>
+        <v>78.3</v>
       </c>
       <c r="F5" t="n">
-        <v>89.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>17.6</v>
+        <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>682.9</v>
+        <v>700.6</v>
       </c>
       <c r="I5" t="n">
-        <v>820.5</v>
+        <v>830.6</v>
       </c>
       <c r="J5" t="n">
-        <v>975</v>
+        <v>991</v>
       </c>
     </row>
     <row r="6">
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>53.3</v>
+        <v>56.9</v>
       </c>
       <c r="E6" t="n">
-        <v>63.6</v>
+        <v>60.8</v>
       </c>
       <c r="F6" t="n">
-        <v>79.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7</v>
+        <v>17.6</v>
       </c>
       <c r="H6" t="n">
-        <v>373.2</v>
+        <v>682.6</v>
       </c>
       <c r="I6" t="n">
-        <v>833.7</v>
+        <v>820.5</v>
       </c>
       <c r="J6" t="n">
-        <v>953</v>
+        <v>975</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>53.3</v>
       </c>
       <c r="E7" t="n">
-        <v>54.5</v>
+        <v>63.6</v>
       </c>
       <c r="F7" t="n">
-        <v>80.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="G7" t="n">
-        <v>22.2</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>476.6</v>
+        <v>373.2</v>
       </c>
       <c r="I7" t="n">
-        <v>816.1</v>
+        <v>833.7</v>
       </c>
       <c r="J7" t="n">
-        <v>930</v>
+        <v>953</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>49.4</v>
+        <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="F8" t="n">
-        <v>87.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>14.4</v>
+        <v>22.2</v>
       </c>
       <c r="H8" t="n">
-        <v>543.3</v>
+        <v>459.1</v>
       </c>
       <c r="I8" t="n">
-        <v>804.5</v>
+        <v>816.1</v>
       </c>
       <c r="J8" t="n">
-        <v>960</v>
+        <v>930</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>waltkin</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>47.8</v>
+        <v>49.8</v>
       </c>
       <c r="E9" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>91.59999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="H9" t="n">
-        <v>95.59999999999999</v>
+        <v>547.9</v>
       </c>
       <c r="I9" t="n">
-        <v>824</v>
+        <v>804.5</v>
       </c>
       <c r="J9" t="n">
-        <v>845</v>
+        <v>960</v>
       </c>
     </row>
     <row r="10">
@@ -756,7 +756,7 @@
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>41.7</v>
+        <v>42.2</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>500.1</v>
+        <v>506.2</v>
       </c>
       <c r="I10" t="n">
         <v>774.6</v>
@@ -824,10 +824,10 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>35.9</v>
+        <v>35.2</v>
       </c>
       <c r="E12" t="n">
-        <v>40.2</v>
+        <v>37.2</v>
       </c>
       <c r="F12" t="n">
         <v>67.5</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>395.2</v>
+        <v>386.7</v>
       </c>
       <c r="I12" t="n">
         <v>762.1</v>
@@ -892,19 +892,19 @@
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>27.5</v>
+        <v>25.6</v>
       </c>
       <c r="E14" t="n">
         <v>10.5</v>
       </c>
       <c r="F14" t="n">
-        <v>90.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>303</v>
+        <v>281.4</v>
       </c>
       <c r="I14" t="n">
         <v>704.3</v>
@@ -926,19 +926,19 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>27.3</v>
+        <v>23</v>
       </c>
       <c r="E15" t="n">
         <v>10.5</v>
       </c>
       <c r="F15" t="n">
-        <v>80.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="G15" t="n">
         <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>136.4</v>
+        <v>115</v>
       </c>
       <c r="I15" t="n">
         <v>716.2</v>
@@ -1617,7 +1617,9 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>960</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1746,7 +1748,7 @@
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>94.3</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="3">
@@ -1790,7 +1792,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>40.5</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="4">
@@ -1828,7 +1830,7 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>67.3</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="5">
@@ -1904,7 +1906,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>14.4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -1948,7 +1950,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="8">
@@ -1992,7 +1994,7 @@
         <v>15.9</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="9">
@@ -2056,7 +2058,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>45.7</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="11">
@@ -2086,7 +2088,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>80.90000000000001</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="12">
@@ -2156,7 +2158,7 @@
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>31.4</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="14">
@@ -2230,7 +2232,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>90.59999999999999</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">
@@ -2255,7 +2257,9 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>99.59999999999999</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2615,19 +2619,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>733.8</v>
+        <v>754.4</v>
       </c>
       <c r="D14" t="n">
-        <v>44.9</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="F14" t="n">
-        <v>805</v>
+        <v>960</v>
       </c>
       <c r="G14" t="n">
         <v>656</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>76.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>86.09999999999999</v>
@@ -493,10 +493,10 @@
         <v>94.2</v>
       </c>
       <c r="G2" t="n">
-        <v>34.4</v>
+        <v>32</v>
       </c>
       <c r="H2" t="n">
-        <v>921.5</v>
+        <v>919.1</v>
       </c>
       <c r="I2" t="n">
         <v>879.5</v>
@@ -518,7 +518,7 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>78.5</v>
@@ -530,7 +530,7 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>899.5</v>
+        <v>898.3</v>
       </c>
       <c r="I3" t="n">
         <v>871.8</v>
@@ -586,7 +586,7 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>63.7</v>
+        <v>63.5</v>
       </c>
       <c r="E5" t="n">
         <v>78.3</v>
@@ -598,7 +598,7 @@
         <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>700.6</v>
+        <v>698.3</v>
       </c>
       <c r="I5" t="n">
         <v>830.6</v>
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>56.9</v>
+        <v>56.7</v>
       </c>
       <c r="E6" t="n">
         <v>60.8</v>
@@ -632,7 +632,7 @@
         <v>17.6</v>
       </c>
       <c r="H6" t="n">
-        <v>682.6</v>
+        <v>680.2</v>
       </c>
       <c r="I6" t="n">
         <v>820.5</v>
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>53.3</v>
+        <v>55.7</v>
       </c>
       <c r="E7" t="n">
-        <v>63.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F7" t="n">
         <v>79.7</v>
@@ -666,10 +666,10 @@
         <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>373.2</v>
+        <v>445.8</v>
       </c>
       <c r="I7" t="n">
-        <v>833.7</v>
+        <v>830</v>
       </c>
       <c r="J7" t="n">
         <v>953</v>
@@ -688,10 +688,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="E8" t="n">
-        <v>49.8</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
         <v>80.40000000000001</v>
@@ -700,7 +700,7 @@
         <v>22.2</v>
       </c>
       <c r="H8" t="n">
-        <v>459.1</v>
+        <v>456.9</v>
       </c>
       <c r="I8" t="n">
         <v>816.1</v>
@@ -722,7 +722,7 @@
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -734,7 +734,7 @@
         <v>15.5</v>
       </c>
       <c r="H9" t="n">
-        <v>547.9</v>
+        <v>545.8</v>
       </c>
       <c r="I9" t="n">
         <v>804.5</v>
@@ -756,7 +756,7 @@
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>506.2</v>
+        <v>504.7</v>
       </c>
       <c r="I10" t="n">
         <v>774.6</v>
@@ -824,10 +824,10 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>35.2</v>
+        <v>34.9</v>
       </c>
       <c r="E12" t="n">
-        <v>37.2</v>
+        <v>34.9</v>
       </c>
       <c r="F12" t="n">
         <v>67.5</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>386.7</v>
+        <v>384.4</v>
       </c>
       <c r="I12" t="n">
         <v>762.1</v>
@@ -892,7 +892,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="E14" t="n">
         <v>10.5</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>281.4</v>
+        <v>279.9</v>
       </c>
       <c r="I14" t="n">
         <v>704.3</v>
@@ -926,19 +926,19 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="E15" t="n">
         <v>10.5</v>
       </c>
       <c r="F15" t="n">
-        <v>59.5</v>
+        <v>57.6</v>
       </c>
       <c r="G15" t="n">
         <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>115</v>
+        <v>113.1</v>
       </c>
       <c r="I15" t="n">
         <v>716.2</v>
@@ -1225,7 +1225,9 @@
         <v>866</v>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>804</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1748,7 +1750,7 @@
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>74.2</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -1792,7 +1794,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>34.4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -1830,7 +1832,7 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>49.8</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="5">
@@ -1865,7 +1867,9 @@
         <v>63.6</v>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>72.59999999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1906,7 +1910,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>19</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="7">
@@ -1950,7 +1954,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>27.2</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="8">
@@ -1994,7 +1998,7 @@
         <v>15.9</v>
       </c>
       <c r="N8" t="n">
-        <v>10.3</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2058,7 +2062,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>37.2</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="11">
@@ -2088,7 +2092,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>59.5</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="12">
@@ -2158,7 +2162,7 @@
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>29.3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -2232,7 +2236,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>69</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="16">
@@ -2619,16 +2623,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>754.4</v>
+        <v>758.5</v>
       </c>
       <c r="D14" t="n">
-        <v>77.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="E14" t="n">
-        <v>729</v>
+        <v>741.5</v>
       </c>
       <c r="F14" t="n">
         <v>960</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>76.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="E2" t="n">
         <v>86.09999999999999</v>
@@ -493,10 +493,10 @@
         <v>94.2</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
-        <v>919.1</v>
+        <v>918.1</v>
       </c>
       <c r="I2" t="n">
         <v>879.5</v>
@@ -530,7 +530,7 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>898.3</v>
+        <v>898.8</v>
       </c>
       <c r="I3" t="n">
         <v>871.8</v>
@@ -558,13 +558,13 @@
         <v>91.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="G4" t="n">
         <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>195.2</v>
+        <v>195.3</v>
       </c>
       <c r="I4" t="n">
         <v>869.3</v>
@@ -586,7 +586,7 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>63.5</v>
+        <v>63.4</v>
       </c>
       <c r="E5" t="n">
         <v>78.3</v>
@@ -598,7 +598,7 @@
         <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>698.3</v>
+        <v>697.1</v>
       </c>
       <c r="I5" t="n">
         <v>830.6</v>
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="E6" t="n">
         <v>60.8</v>
@@ -632,7 +632,7 @@
         <v>17.6</v>
       </c>
       <c r="H6" t="n">
-        <v>680.2</v>
+        <v>679.1</v>
       </c>
       <c r="I6" t="n">
         <v>820.5</v>
@@ -654,7 +654,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>55.7</v>
+        <v>55.8</v>
       </c>
       <c r="E7" t="n">
         <v>64.59999999999999</v>
@@ -666,7 +666,7 @@
         <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>445.8</v>
+        <v>446.2</v>
       </c>
       <c r="I7" t="n">
         <v>830</v>
@@ -688,7 +688,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="E8" t="n">
         <v>49</v>
@@ -700,7 +700,7 @@
         <v>22.2</v>
       </c>
       <c r="H8" t="n">
-        <v>456.9</v>
+        <v>456.4</v>
       </c>
       <c r="I8" t="n">
         <v>816.1</v>
@@ -722,7 +722,7 @@
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -734,7 +734,7 @@
         <v>15.5</v>
       </c>
       <c r="H9" t="n">
-        <v>545.8</v>
+        <v>544.6</v>
       </c>
       <c r="I9" t="n">
         <v>804.5</v>
@@ -756,7 +756,7 @@
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>504.7</v>
+        <v>503.7</v>
       </c>
       <c r="I10" t="n">
         <v>774.6</v>
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>37.6</v>
+        <v>40</v>
       </c>
       <c r="E11" t="n">
-        <v>36.4</v>
+        <v>52.3</v>
       </c>
       <c r="F11" t="n">
         <v>64.7</v>
@@ -802,10 +802,10 @@
         <v>14.8</v>
       </c>
       <c r="H11" t="n">
-        <v>225.4</v>
+        <v>280.2</v>
       </c>
       <c r="I11" t="n">
-        <v>767.3</v>
+        <v>767.4</v>
       </c>
       <c r="J11" t="n">
         <v>916</v>
@@ -827,7 +827,7 @@
         <v>34.9</v>
       </c>
       <c r="E12" t="n">
-        <v>34.9</v>
+        <v>33.9</v>
       </c>
       <c r="F12" t="n">
         <v>67.5</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>384.4</v>
+        <v>383.4</v>
       </c>
       <c r="I12" t="n">
         <v>762.1</v>
@@ -892,7 +892,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="E14" t="n">
         <v>10.5</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>279.9</v>
+        <v>280.2</v>
       </c>
       <c r="I14" t="n">
         <v>704.3</v>
@@ -932,13 +932,13 @@
         <v>10.5</v>
       </c>
       <c r="F15" t="n">
-        <v>57.6</v>
+        <v>57.5</v>
       </c>
       <c r="G15" t="n">
         <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>113.1</v>
+        <v>113</v>
       </c>
       <c r="I15" t="n">
         <v>716.2</v>
@@ -1553,7 +1553,9 @@
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>768</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1750,7 +1752,7 @@
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>73</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="3">
@@ -1794,7 +1796,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -1832,7 +1834,7 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>47.6</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="5">
@@ -1868,7 +1870,7 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>72.59999999999999</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -1910,7 +1912,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>16.9</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="7">
@@ -1954,7 +1956,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>24.8</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="8">
@@ -1998,7 +2000,7 @@
         <v>15.9</v>
       </c>
       <c r="N8" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="9">
@@ -2062,7 +2064,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>34.9</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="11">
@@ -2092,7 +2094,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>57.6</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="12">
@@ -2162,7 +2164,7 @@
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>27</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2197,9 @@
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>54.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2236,7 +2240,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>67.5</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="16">
@@ -2262,7 +2266,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
     </row>
   </sheetData>
@@ -2623,16 +2627,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>758.5</v>
+        <v>759.2</v>
       </c>
       <c r="D14" t="n">
-        <v>75.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>741.5</v>
+        <v>754</v>
       </c>
       <c r="F14" t="n">
         <v>960</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>56.6</v>
+        <v>55.8</v>
       </c>
       <c r="E6" t="n">
-        <v>60.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>89.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="G6" t="n">
-        <v>17.6</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>679.1</v>
+        <v>446.2</v>
       </c>
       <c r="I6" t="n">
-        <v>820.5</v>
+        <v>830</v>
       </c>
       <c r="J6" t="n">
-        <v>975</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>55.8</v>
+        <v>53.5</v>
       </c>
       <c r="E7" t="n">
-        <v>64.59999999999999</v>
+        <v>56.3</v>
       </c>
       <c r="F7" t="n">
-        <v>79.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>15.9</v>
       </c>
       <c r="H7" t="n">
-        <v>446.2</v>
+        <v>695</v>
       </c>
       <c r="I7" t="n">
-        <v>830</v>
+        <v>816.4</v>
       </c>
       <c r="J7" t="n">
-        <v>953</v>
+        <v>975</v>
       </c>
     </row>
     <row r="8">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>42</v>
+        <v>45.2</v>
       </c>
       <c r="E10" t="n">
-        <v>37.4</v>
+        <v>38.9</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,10 +768,10 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>503.7</v>
+        <v>587.8</v>
       </c>
       <c r="I10" t="n">
-        <v>774.6</v>
+        <v>784.3</v>
       </c>
       <c r="J10" t="n">
         <v>928</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1066,6 +1066,11 @@
           <t>9/14/26</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>9/15/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1110,6 +1115,7 @@
       <c r="N2" t="n">
         <v>805</v>
       </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1154,6 +1160,7 @@
       <c r="N3" t="n">
         <v>723</v>
       </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1192,6 +1199,7 @@
       <c r="N4" t="n">
         <v>754</v>
       </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1228,6 +1236,7 @@
       <c r="N5" t="n">
         <v>804</v>
       </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1270,6 +1279,7 @@
       <c r="N6" t="n">
         <v>686</v>
       </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1314,6 +1324,9 @@
       <c r="N7" t="n">
         <v>707</v>
       </c>
+      <c r="O7" t="n">
+        <v>767</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1357,6 +1370,9 @@
       </c>
       <c r="N8" t="n">
         <v>656</v>
+      </c>
+      <c r="O8" t="n">
+        <v>901</v>
       </c>
     </row>
     <row r="9">
@@ -1380,6 +1396,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1422,6 +1439,7 @@
       <c r="N10" t="n">
         <v>729</v>
       </c>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1452,6 +1470,7 @@
       <c r="N11" t="n">
         <v>773</v>
       </c>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1480,6 +1499,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1522,6 +1542,7 @@
       <c r="N13" t="n">
         <v>712</v>
       </c>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1556,6 +1577,7 @@
       <c r="N14" t="n">
         <v>768</v>
       </c>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1598,6 +1620,7 @@
       <c r="N15" t="n">
         <v>793</v>
       </c>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1624,6 +1647,7 @@
       <c r="N16" t="n">
         <v>960</v>
       </c>
+      <c r="O16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1636,7 +1660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,6 +1734,11 @@
           <t>9/14/26</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>9/15/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1754,6 +1783,7 @@
       <c r="N2" t="n">
         <v>73.5</v>
       </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1798,6 +1828,7 @@
       <c r="N3" t="n">
         <v>31</v>
       </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1836,6 +1867,7 @@
       <c r="N4" t="n">
         <v>47.1</v>
       </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1872,6 +1904,7 @@
       <c r="N5" t="n">
         <v>73</v>
       </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1914,6 +1947,7 @@
       <c r="N6" t="n">
         <v>15.7</v>
       </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1958,6 +1992,9 @@
       <c r="N7" t="n">
         <v>23.7</v>
       </c>
+      <c r="O7" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2001,6 +2038,9 @@
       </c>
       <c r="N8" t="n">
         <v>7.8</v>
+      </c>
+      <c r="O8" t="n">
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2024,6 +2064,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2066,6 +2107,7 @@
       <c r="N10" t="n">
         <v>33.9</v>
       </c>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2096,6 +2138,7 @@
       <c r="N11" t="n">
         <v>57.5</v>
       </c>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2124,6 +2167,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2166,6 +2210,7 @@
       <c r="N13" t="n">
         <v>25.8</v>
       </c>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2200,6 +2245,7 @@
       <c r="N14" t="n">
         <v>54.8</v>
       </c>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2242,6 +2288,7 @@
       <c r="N15" t="n">
         <v>67.8</v>
       </c>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2268,6 +2315,7 @@
       <c r="N16" t="n">
         <v>99.7</v>
       </c>
+      <c r="O16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2280,7 +2328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2645,6 +2693,31 @@
         <v>656</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>9/15/26</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>834</v>
+      </c>
+      <c r="D15" t="n">
+        <v>67</v>
+      </c>
+      <c r="E15" t="n">
+        <v>834</v>
+      </c>
+      <c r="F15" t="n">
+        <v>901</v>
+      </c>
+      <c r="G15" t="n">
+        <v>767</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -663,10 +663,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>15.9</v>
+        <v>4.9</v>
       </c>
       <c r="H7" t="n">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="I7" t="n">
         <v>816.4</v>
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>50.7</v>
+        <v>52.5</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>53.1</v>
       </c>
       <c r="F8" t="n">
-        <v>80.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>22.2</v>
+        <v>15.5</v>
       </c>
       <c r="H8" t="n">
-        <v>456.4</v>
+        <v>629.6</v>
       </c>
       <c r="I8" t="n">
-        <v>816.1</v>
+        <v>816.3</v>
       </c>
       <c r="J8" t="n">
-        <v>930</v>
+        <v>960</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>49.5</v>
+        <v>51.6</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>51.8</v>
       </c>
       <c r="F9" t="n">
-        <v>87.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>15.5</v>
+        <v>22.2</v>
       </c>
       <c r="H9" t="n">
-        <v>544.6</v>
+        <v>516.5</v>
       </c>
       <c r="I9" t="n">
-        <v>804.5</v>
+        <v>823.9</v>
       </c>
       <c r="J9" t="n">
-        <v>960</v>
+        <v>930</v>
       </c>
     </row>
     <row r="10">
@@ -756,7 +756,7 @@
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>45.2</v>
+        <v>43.7</v>
       </c>
       <c r="E10" t="n">
         <v>38.9</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>587.8</v>
+        <v>567.8</v>
       </c>
       <c r="I10" t="n">
         <v>784.3</v>
@@ -1199,7 +1199,9 @@
       <c r="N4" t="n">
         <v>754</v>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1279,7 +1281,9 @@
       <c r="N6" t="n">
         <v>686</v>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>946</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1867,7 +1871,9 @@
       <c r="N4" t="n">
         <v>47.1</v>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>60.1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1947,7 +1953,9 @@
       <c r="N6" t="n">
         <v>15.7</v>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1993,7 +2001,7 @@
         <v>23.7</v>
       </c>
       <c r="O7" t="n">
-        <v>15.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="8">
@@ -2040,7 +2048,7 @@
         <v>7.8</v>
       </c>
       <c r="O8" t="n">
-        <v>84.09999999999999</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2700,19 +2708,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>834</v>
+        <v>877</v>
       </c>
       <c r="D15" t="n">
-        <v>67</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>834</v>
+        <v>897.5</v>
       </c>
       <c r="F15" t="n">
-        <v>901</v>
+        <v>946</v>
       </c>
       <c r="G15" t="n">
         <v>767</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>74.90000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>78.5</v>
+        <v>79.7</v>
       </c>
       <c r="F3" t="n">
         <v>97.7</v>
@@ -530,10 +530,10 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>898.8</v>
+        <v>986.9</v>
       </c>
       <c r="I3" t="n">
-        <v>871.8</v>
+        <v>880.5</v>
       </c>
       <c r="J3" t="n">
         <v>991</v>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -663,10 +663,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="H7" t="n">
-        <v>684</v>
+        <v>682.8</v>
       </c>
       <c r="I7" t="n">
         <v>816.4</v>
@@ -688,7 +688,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="E8" t="n">
         <v>53.1</v>
@@ -700,7 +700,7 @@
         <v>15.5</v>
       </c>
       <c r="H8" t="n">
-        <v>629.6</v>
+        <v>618.5</v>
       </c>
       <c r="I8" t="n">
         <v>816.3</v>
@@ -722,10 +722,10 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>51.6</v>
+        <v>50.4</v>
       </c>
       <c r="E9" t="n">
-        <v>51.8</v>
+        <v>48.2</v>
       </c>
       <c r="F9" t="n">
         <v>80.40000000000001</v>
@@ -734,7 +734,7 @@
         <v>22.2</v>
       </c>
       <c r="H9" t="n">
-        <v>516.5</v>
+        <v>503.8</v>
       </c>
       <c r="I9" t="n">
         <v>823.9</v>
@@ -756,7 +756,7 @@
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>43.7</v>
+        <v>42.7</v>
       </c>
       <c r="E10" t="n">
         <v>38.9</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>567.8</v>
+        <v>554.9</v>
       </c>
       <c r="I10" t="n">
         <v>784.3</v>
@@ -1115,7 +1115,9 @@
       <c r="N2" t="n">
         <v>805</v>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>986</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1787,7 +1789,9 @@
       <c r="N2" t="n">
         <v>73.5</v>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>88.09999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1872,7 +1876,7 @@
         <v>47.1</v>
       </c>
       <c r="O4" t="n">
-        <v>60.1</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="5">
@@ -1954,7 +1958,7 @@
         <v>15.7</v>
       </c>
       <c r="O6" t="n">
-        <v>85</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2001,7 +2005,7 @@
         <v>23.7</v>
       </c>
       <c r="O7" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="8">
@@ -2048,7 +2052,7 @@
         <v>7.8</v>
       </c>
       <c r="O8" t="n">
-        <v>64.09999999999999</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="9">
@@ -2708,19 +2712,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>877</v>
+        <v>898.8</v>
       </c>
       <c r="D15" t="n">
-        <v>66.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="E15" t="n">
-        <v>897.5</v>
+        <v>901</v>
       </c>
       <c r="F15" t="n">
-        <v>946</v>
+        <v>986</v>
       </c>
       <c r="G15" t="n">
         <v>767</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -477,32 +477,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pparril</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>76.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>86.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="F2" t="n">
-        <v>94.2</v>
+        <v>97.7</v>
       </c>
       <c r="G2" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>918.1</v>
+        <v>988.9</v>
       </c>
       <c r="I2" t="n">
-        <v>879.5</v>
+        <v>880.5</v>
       </c>
       <c r="J2" t="n">
-        <v>997</v>
+        <v>991</v>
       </c>
     </row>
     <row r="3">
@@ -511,32 +511,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>pparril</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>79.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>97.7</v>
+        <v>94.2</v>
       </c>
       <c r="G3" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>986.9</v>
+        <v>969.7</v>
       </c>
       <c r="I3" t="n">
-        <v>880.5</v>
+        <v>881.6</v>
       </c>
       <c r="J3" t="n">
-        <v>991</v>
+        <v>997</v>
       </c>
     </row>
     <row r="4">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>55.8</v>
+        <v>56.9</v>
       </c>
       <c r="E6" t="n">
-        <v>64.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F6" t="n">
         <v>79.7</v>
@@ -632,10 +632,10 @@
         <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>446.2</v>
+        <v>511.9</v>
       </c>
       <c r="I6" t="n">
-        <v>830</v>
+        <v>841.1</v>
       </c>
       <c r="J6" t="n">
         <v>953</v>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -663,10 +663,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
-        <v>682.8</v>
+        <v>680.6</v>
       </c>
       <c r="I7" t="n">
         <v>816.4</v>
@@ -688,7 +688,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="E8" t="n">
         <v>53.1</v>
@@ -700,7 +700,7 @@
         <v>15.5</v>
       </c>
       <c r="H8" t="n">
-        <v>618.5</v>
+        <v>619</v>
       </c>
       <c r="I8" t="n">
         <v>816.3</v>
@@ -722,10 +722,10 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>48.2</v>
+        <v>48</v>
       </c>
       <c r="F9" t="n">
         <v>80.40000000000001</v>
@@ -734,7 +734,7 @@
         <v>22.2</v>
       </c>
       <c r="H9" t="n">
-        <v>503.8</v>
+        <v>499.9</v>
       </c>
       <c r="I9" t="n">
         <v>823.9</v>
@@ -756,7 +756,7 @@
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>42.7</v>
+        <v>42.4</v>
       </c>
       <c r="E10" t="n">
         <v>38.9</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>554.9</v>
+        <v>551.5</v>
       </c>
       <c r="I10" t="n">
         <v>784.3</v>
@@ -1162,7 +1162,9 @@
       <c r="N3" t="n">
         <v>723</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>907</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1240,7 +1242,9 @@
       <c r="N5" t="n">
         <v>804</v>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>930</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1790,7 +1794,7 @@
         <v>73.5</v>
       </c>
       <c r="O2" t="n">
-        <v>88.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1836,7 +1840,9 @@
       <c r="N3" t="n">
         <v>31</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>51.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1876,7 +1882,7 @@
         <v>47.1</v>
       </c>
       <c r="O4" t="n">
-        <v>47.4</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="5">
@@ -1914,7 +1920,9 @@
       <c r="N5" t="n">
         <v>73</v>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>65.7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1958,7 +1966,7 @@
         <v>15.7</v>
       </c>
       <c r="O6" t="n">
-        <v>73.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2005,7 +2013,7 @@
         <v>23.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
@@ -2052,7 +2060,7 @@
         <v>7.8</v>
       </c>
       <c r="O8" t="n">
-        <v>51.2</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="9">
@@ -2712,16 +2720,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>898.8</v>
+        <v>904.4</v>
       </c>
       <c r="D15" t="n">
-        <v>73.8</v>
+        <v>63.3</v>
       </c>
       <c r="E15" t="n">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="F15" t="n">
         <v>986</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>76.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="E2" t="n">
         <v>79.7</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>988.9</v>
+        <v>986</v>
       </c>
       <c r="I2" t="n">
         <v>880.5</v>
@@ -518,7 +518,7 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="E3" t="n">
         <v>85.40000000000001</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>969.7</v>
+        <v>964</v>
       </c>
       <c r="I3" t="n">
         <v>881.6</v>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>waltkin</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>65.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>91.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="F4" t="n">
-        <v>99.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>195.3</v>
+        <v>781.1</v>
       </c>
       <c r="I4" t="n">
-        <v>869.3</v>
+        <v>842.8</v>
       </c>
       <c r="J4" t="n">
-        <v>960</v>
+        <v>991</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>waltkin</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>63.4</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>78.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>93.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="G5" t="n">
-        <v>11.4</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>697.1</v>
+        <v>195.3</v>
       </c>
       <c r="I5" t="n">
-        <v>830.6</v>
+        <v>869.3</v>
       </c>
       <c r="J5" t="n">
-        <v>991</v>
+        <v>960</v>
       </c>
     </row>
     <row r="6">
@@ -620,10 +620,10 @@
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>56.9</v>
+        <v>56.3</v>
       </c>
       <c r="E6" t="n">
-        <v>65.59999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="F6" t="n">
         <v>79.7</v>
@@ -632,7 +632,7 @@
         <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>511.9</v>
+        <v>506.4</v>
       </c>
       <c r="I6" t="n">
         <v>841.1</v>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -663,10 +663,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="H7" t="n">
-        <v>680.6</v>
+        <v>680.2</v>
       </c>
       <c r="I7" t="n">
         <v>816.4</v>
@@ -688,7 +688,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>51.6</v>
+        <v>51.2</v>
       </c>
       <c r="E8" t="n">
         <v>53.1</v>
@@ -700,7 +700,7 @@
         <v>15.5</v>
       </c>
       <c r="H8" t="n">
-        <v>619</v>
+        <v>614.1</v>
       </c>
       <c r="I8" t="n">
         <v>816.3</v>
@@ -722,7 +722,7 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>49.4</v>
       </c>
       <c r="E9" t="n">
         <v>48</v>
@@ -734,7 +734,7 @@
         <v>22.2</v>
       </c>
       <c r="H9" t="n">
-        <v>499.9</v>
+        <v>494.4</v>
       </c>
       <c r="I9" t="n">
         <v>823.9</v>
@@ -756,7 +756,7 @@
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>42.4</v>
+        <v>42</v>
       </c>
       <c r="E10" t="n">
         <v>38.9</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>551.5</v>
+        <v>545.9</v>
       </c>
       <c r="I10" t="n">
         <v>784.3</v>
@@ -1552,7 +1552,9 @@
       <c r="N13" t="n">
         <v>712</v>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>977</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1794,7 +1796,7 @@
         <v>73.5</v>
       </c>
       <c r="O2" t="n">
-        <v>90.09999999999999</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="3">
@@ -1841,7 +1843,7 @@
         <v>31</v>
       </c>
       <c r="O3" t="n">
-        <v>51.6</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="4">
@@ -1882,7 +1884,7 @@
         <v>47.1</v>
       </c>
       <c r="O4" t="n">
-        <v>43.5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -1921,7 +1923,7 @@
         <v>73</v>
       </c>
       <c r="O5" t="n">
-        <v>65.7</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="6">
@@ -1966,7 +1968,7 @@
         <v>15.7</v>
       </c>
       <c r="O6" t="n">
-        <v>74.40000000000001</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="7">
@@ -2013,7 +2015,7 @@
         <v>23.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
@@ -2060,7 +2062,7 @@
         <v>7.8</v>
       </c>
       <c r="O8" t="n">
-        <v>47.8</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="9">
@@ -2230,7 +2232,9 @@
       <c r="N13" t="n">
         <v>25.8</v>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2720,16 +2724,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>904.4</v>
+        <v>913.5</v>
       </c>
       <c r="D15" t="n">
-        <v>63.3</v>
+        <v>63.9</v>
       </c>
       <c r="E15" t="n">
-        <v>907</v>
+        <v>918.5</v>
       </c>
       <c r="F15" t="n">
         <v>986</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>75.8</v>
+        <v>76</v>
       </c>
       <c r="E2" t="n">
         <v>79.7</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>986</v>
+        <v>988.1</v>
       </c>
       <c r="I2" t="n">
         <v>880.5</v>
@@ -518,7 +518,7 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>74.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E3" t="n">
         <v>85.40000000000001</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="I3" t="n">
         <v>881.6</v>
@@ -552,7 +552,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>65.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="E4" t="n">
         <v>79.8</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>781.1</v>
+        <v>783.7</v>
       </c>
       <c r="I4" t="n">
         <v>842.8</v>
@@ -620,10 +620,10 @@
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>56.3</v>
+        <v>56.8</v>
       </c>
       <c r="E6" t="n">
-        <v>63.6</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>79.7</v>
@@ -632,7 +632,7 @@
         <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>506.4</v>
+        <v>511.6</v>
       </c>
       <c r="I6" t="n">
         <v>841.1</v>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -663,10 +663,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="H7" t="n">
-        <v>680.2</v>
+        <v>681</v>
       </c>
       <c r="I7" t="n">
         <v>816.4</v>
@@ -688,7 +688,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>51.2</v>
+        <v>51.5</v>
       </c>
       <c r="E8" t="n">
         <v>53.1</v>
@@ -700,7 +700,7 @@
         <v>15.5</v>
       </c>
       <c r="H8" t="n">
-        <v>614.1</v>
+        <v>618.4</v>
       </c>
       <c r="I8" t="n">
         <v>816.3</v>
@@ -722,7 +722,7 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>49.4</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
         <v>48</v>
@@ -734,7 +734,7 @@
         <v>22.2</v>
       </c>
       <c r="H9" t="n">
-        <v>494.4</v>
+        <v>500.5</v>
       </c>
       <c r="I9" t="n">
         <v>823.9</v>
@@ -756,7 +756,7 @@
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="E10" t="n">
         <v>38.9</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>545.9</v>
+        <v>552</v>
       </c>
       <c r="I10" t="n">
         <v>784.3</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>25.5</v>
+        <v>24.4</v>
       </c>
       <c r="E14" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>280.2</v>
+        <v>292.4</v>
       </c>
       <c r="I14" t="n">
-        <v>704.3</v>
+        <v>714.5</v>
       </c>
       <c r="J14" t="n">
         <v>832</v>
@@ -1632,7 +1632,9 @@
       <c r="N15" t="n">
         <v>793</v>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>827</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1796,7 +1798,7 @@
         <v>73.5</v>
       </c>
       <c r="O2" t="n">
-        <v>87.2</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="3">
@@ -1843,7 +1845,7 @@
         <v>31</v>
       </c>
       <c r="O3" t="n">
-        <v>45.9</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="4">
@@ -1884,7 +1886,7 @@
         <v>47.1</v>
       </c>
       <c r="O4" t="n">
-        <v>38</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="5">
@@ -1923,7 +1925,7 @@
         <v>73</v>
       </c>
       <c r="O5" t="n">
-        <v>60.2</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1968,7 +1970,7 @@
         <v>15.7</v>
       </c>
       <c r="O6" t="n">
-        <v>69.5</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="7">
@@ -2015,7 +2017,7 @@
         <v>23.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="8">
@@ -2062,7 +2064,7 @@
         <v>7.8</v>
       </c>
       <c r="O8" t="n">
-        <v>42.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="9">
@@ -2233,7 +2235,7 @@
         <v>25.8</v>
       </c>
       <c r="O13" t="n">
-        <v>84</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2312,7 +2314,9 @@
       <c r="N15" t="n">
         <v>67.8</v>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>12.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2724,16 +2728,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>913.5</v>
+        <v>903.9</v>
       </c>
       <c r="D15" t="n">
-        <v>63.9</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>918.5</v>
+        <v>907</v>
       </c>
       <c r="F15" t="n">
         <v>986</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="E2" t="n">
         <v>79.7</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>988.1</v>
+        <v>990</v>
       </c>
       <c r="I2" t="n">
         <v>880.5</v>
@@ -518,7 +518,7 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>85.40000000000001</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>970</v>
+        <v>973.6</v>
       </c>
       <c r="I3" t="n">
         <v>881.6</v>
@@ -552,7 +552,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>65.3</v>
+        <v>65.5</v>
       </c>
       <c r="E4" t="n">
         <v>79.8</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>783.7</v>
+        <v>785.8</v>
       </c>
       <c r="I4" t="n">
         <v>842.8</v>
@@ -620,10 +620,10 @@
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>56.8</v>
+        <v>57.2</v>
       </c>
       <c r="E6" t="n">
-        <v>65.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F6" t="n">
         <v>79.7</v>
@@ -632,7 +632,7 @@
         <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>511.6</v>
+        <v>515</v>
       </c>
       <c r="I6" t="n">
         <v>841.1</v>
@@ -663,10 +663,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>681</v>
+        <v>681.3</v>
       </c>
       <c r="I7" t="n">
         <v>816.4</v>
@@ -688,7 +688,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>51.5</v>
+        <v>51.8</v>
       </c>
       <c r="E8" t="n">
         <v>53.1</v>
@@ -700,7 +700,7 @@
         <v>15.5</v>
       </c>
       <c r="H8" t="n">
-        <v>618.4</v>
+        <v>621.5</v>
       </c>
       <c r="I8" t="n">
         <v>816.3</v>
@@ -722,10 +722,10 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
       <c r="F9" t="n">
         <v>80.40000000000001</v>
@@ -734,7 +734,7 @@
         <v>22.2</v>
       </c>
       <c r="H9" t="n">
-        <v>500.5</v>
+        <v>504</v>
       </c>
       <c r="I9" t="n">
         <v>823.9</v>
@@ -756,7 +756,7 @@
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="E10" t="n">
         <v>38.9</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>552</v>
+        <v>555.5</v>
       </c>
       <c r="I10" t="n">
         <v>784.3</v>
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="E12" t="n">
-        <v>33.9</v>
+        <v>36.6</v>
       </c>
       <c r="F12" t="n">
-        <v>67.5</v>
+        <v>62.8</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>383.4</v>
+        <v>138.9</v>
       </c>
       <c r="I12" t="n">
-        <v>762.1</v>
+        <v>765.2</v>
       </c>
       <c r="J12" t="n">
-        <v>924</v>
+        <v>849</v>
       </c>
     </row>
     <row r="13">
@@ -851,32 +851,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>34.7</v>
+        <v>33.7</v>
       </c>
       <c r="E13" t="n">
-        <v>36.6</v>
+        <v>33.4</v>
       </c>
       <c r="F13" t="n">
-        <v>62.8</v>
+        <v>67.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>138.9</v>
+        <v>404.2</v>
       </c>
       <c r="I13" t="n">
-        <v>765.2</v>
+        <v>769</v>
       </c>
       <c r="J13" t="n">
-        <v>849</v>
+        <v>924</v>
       </c>
     </row>
     <row r="14">
@@ -892,7 +892,7 @@
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="E14" t="n">
         <v>10.7</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>292.4</v>
+        <v>294</v>
       </c>
       <c r="I14" t="n">
         <v>714.5</v>
@@ -1449,7 +1449,9 @@
       <c r="N10" t="n">
         <v>729</v>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>845</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1798,7 +1800,7 @@
         <v>73.5</v>
       </c>
       <c r="O2" t="n">
-        <v>89.3</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="3">
@@ -1845,7 +1847,7 @@
         <v>31</v>
       </c>
       <c r="O3" t="n">
-        <v>51.9</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="4">
@@ -1886,7 +1888,7 @@
         <v>47.1</v>
       </c>
       <c r="O4" t="n">
-        <v>44.1</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="5">
@@ -1925,7 +1927,7 @@
         <v>73</v>
       </c>
       <c r="O5" t="n">
-        <v>65.40000000000001</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="6">
@@ -1970,7 +1972,7 @@
         <v>15.7</v>
       </c>
       <c r="O6" t="n">
-        <v>73.8</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2017,7 +2019,7 @@
         <v>23.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2066,7 @@
         <v>7.8</v>
       </c>
       <c r="O8" t="n">
-        <v>48.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="9">
@@ -2131,7 +2133,9 @@
       <c r="N10" t="n">
         <v>33.9</v>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2235,7 +2239,7 @@
         <v>25.8</v>
       </c>
       <c r="O13" t="n">
-        <v>86.59999999999999</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="14">
@@ -2315,7 +2319,7 @@
         <v>67.8</v>
       </c>
       <c r="O15" t="n">
-        <v>12.2</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="16">
@@ -2728,16 +2732,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>903.9</v>
+        <v>898</v>
       </c>
       <c r="D15" t="n">
-        <v>66.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="F15" t="n">
         <v>986</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>42.7</v>
+        <v>43.2</v>
       </c>
       <c r="E10" t="n">
-        <v>38.9</v>
+        <v>44.4</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,10 +768,10 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>555.5</v>
+        <v>605.5</v>
       </c>
       <c r="I10" t="n">
-        <v>784.3</v>
+        <v>787.3</v>
       </c>
       <c r="J10" t="n">
         <v>928</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1071,6 +1071,11 @@
           <t>9/15/26</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>9/16/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1118,6 +1123,7 @@
       <c r="O2" t="n">
         <v>986</v>
       </c>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1165,6 +1171,7 @@
       <c r="O3" t="n">
         <v>907</v>
       </c>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1206,6 +1213,7 @@
       <c r="O4" t="n">
         <v>894</v>
       </c>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1245,6 +1253,7 @@
       <c r="O5" t="n">
         <v>930</v>
       </c>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1290,6 +1299,7 @@
       <c r="O6" t="n">
         <v>946</v>
       </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1337,6 +1347,7 @@
       <c r="O7" t="n">
         <v>767</v>
       </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1383,6 +1394,9 @@
       </c>
       <c r="O8" t="n">
         <v>901</v>
+      </c>
+      <c r="P8" t="n">
+        <v>826</v>
       </c>
     </row>
     <row r="9">
@@ -1407,6 +1421,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1452,6 +1467,7 @@
       <c r="O10" t="n">
         <v>845</v>
       </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1483,6 +1499,7 @@
         <v>773</v>
       </c>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1512,6 +1529,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1557,6 +1575,7 @@
       <c r="O13" t="n">
         <v>977</v>
       </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1592,6 +1611,7 @@
         <v>768</v>
       </c>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1637,6 +1657,7 @@
       <c r="O15" t="n">
         <v>827</v>
       </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1664,6 +1685,7 @@
         <v>960</v>
       </c>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1676,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1755,6 +1777,11 @@
           <t>9/15/26</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>9/16/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1802,6 +1829,7 @@
       <c r="O2" t="n">
         <v>91.2</v>
       </c>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1849,6 +1877,7 @@
       <c r="O3" t="n">
         <v>55.5</v>
       </c>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1890,6 +1919,7 @@
       <c r="O4" t="n">
         <v>47.6</v>
       </c>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1929,6 +1959,7 @@
       <c r="O5" t="n">
         <v>68.8</v>
       </c>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1974,6 +2005,7 @@
       <c r="O6" t="n">
         <v>76.90000000000001</v>
       </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2021,6 +2053,7 @@
       <c r="O7" t="n">
         <v>2.2</v>
       </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2067,6 +2100,9 @@
       </c>
       <c r="O8" t="n">
         <v>51.8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -2091,6 +2127,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2136,6 +2173,7 @@
       <c r="O10" t="n">
         <v>20.8</v>
       </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2167,6 +2205,7 @@
         <v>57.5</v>
       </c>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2196,6 +2235,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2241,6 +2281,7 @@
       <c r="O13" t="n">
         <v>88.7</v>
       </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2276,6 +2317,7 @@
         <v>54.8</v>
       </c>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2321,6 +2363,7 @@
       <c r="O15" t="n">
         <v>13.8</v>
       </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2348,6 +2391,7 @@
         <v>99.7</v>
       </c>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2360,7 +2404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2750,6 +2794,31 @@
         <v>767</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>9/16/26</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>826</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>826</v>
+      </c>
+      <c r="F16" t="n">
+        <v>826</v>
+      </c>
+      <c r="G16" t="n">
+        <v>826</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>52.4</v>
+        <v>51.8</v>
       </c>
       <c r="E7" t="n">
-        <v>56.3</v>
+        <v>53.1</v>
       </c>
       <c r="F7" t="n">
-        <v>89.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2</v>
+        <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>681.3</v>
+        <v>621.5</v>
       </c>
       <c r="I7" t="n">
-        <v>816.4</v>
+        <v>816.3</v>
       </c>
       <c r="J7" t="n">
-        <v>975</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>51.8</v>
+        <v>50.4</v>
       </c>
       <c r="E8" t="n">
-        <v>53.1</v>
+        <v>48.3</v>
       </c>
       <c r="F8" t="n">
-        <v>87.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>15.5</v>
+        <v>22.2</v>
       </c>
       <c r="H8" t="n">
-        <v>621.5</v>
+        <v>504</v>
       </c>
       <c r="I8" t="n">
-        <v>816.3</v>
+        <v>823.9</v>
       </c>
       <c r="J8" t="n">
-        <v>960</v>
+        <v>930</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>50.4</v>
+        <v>49.8</v>
       </c>
       <c r="E9" t="n">
-        <v>48.3</v>
+        <v>50.1</v>
       </c>
       <c r="F9" t="n">
-        <v>80.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>504</v>
+        <v>697.2</v>
       </c>
       <c r="I9" t="n">
-        <v>823.9</v>
+        <v>810.3</v>
       </c>
       <c r="J9" t="n">
-        <v>930</v>
+        <v>975</v>
       </c>
     </row>
     <row r="10">
@@ -756,10 +756,10 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>43.2</v>
+        <v>45.7</v>
       </c>
       <c r="E10" t="n">
-        <v>44.4</v>
+        <v>44.8</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>605.5</v>
+        <v>639.6</v>
       </c>
       <c r="I10" t="n">
         <v>787.3</v>
@@ -1347,7 +1347,9 @@
       <c r="O7" t="n">
         <v>767</v>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>731</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2053,7 +2055,9 @@
       <c r="O7" t="n">
         <v>2.2</v>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2102,7 +2106,7 @@
         <v>51.8</v>
       </c>
       <c r="P8" t="n">
-        <v>50</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2801,22 +2805,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>826</v>
+        <v>778.5</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="E16" t="n">
-        <v>826</v>
+        <v>778.5</v>
       </c>
       <c r="F16" t="n">
         <v>826</v>
       </c>
       <c r="G16" t="n">
-        <v>826</v>
+        <v>731</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>51.8</v>
+        <v>50.9</v>
       </c>
       <c r="E7" t="n">
-        <v>53.1</v>
+        <v>50.1</v>
       </c>
       <c r="F7" t="n">
-        <v>87.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>15.5</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>621.5</v>
+        <v>712.9</v>
       </c>
       <c r="I7" t="n">
-        <v>816.3</v>
+        <v>810.3</v>
       </c>
       <c r="J7" t="n">
-        <v>960</v>
+        <v>975</v>
       </c>
     </row>
     <row r="8">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>49.8</v>
+        <v>49.2</v>
       </c>
       <c r="E9" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>89.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>15.5</v>
       </c>
       <c r="H9" t="n">
-        <v>697.2</v>
+        <v>639.6</v>
       </c>
       <c r="I9" t="n">
-        <v>810.3</v>
+        <v>808.1</v>
       </c>
       <c r="J9" t="n">
-        <v>975</v>
+        <v>960</v>
       </c>
     </row>
     <row r="10">
@@ -756,19 +756,19 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>45.7</v>
+        <v>46.2</v>
       </c>
       <c r="E10" t="n">
         <v>44.8</v>
       </c>
       <c r="F10" t="n">
-        <v>90.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="G10" t="n">
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>639.6</v>
+        <v>647.3</v>
       </c>
       <c r="I10" t="n">
         <v>787.3</v>
@@ -1299,7 +1299,9 @@
       <c r="O6" t="n">
         <v>946</v>
       </c>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>709</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2007,7 +2009,9 @@
       <c r="O6" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>18.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2056,7 +2060,7 @@
         <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>15.9</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="8">
@@ -2106,7 +2110,7 @@
         <v>51.8</v>
       </c>
       <c r="P8" t="n">
-        <v>84.09999999999999</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="9">
@@ -2805,22 +2809,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>778.5</v>
+        <v>755.3</v>
       </c>
       <c r="D16" t="n">
-        <v>47.5</v>
+        <v>50.8</v>
       </c>
       <c r="E16" t="n">
-        <v>778.5</v>
+        <v>731</v>
       </c>
       <c r="F16" t="n">
         <v>826</v>
       </c>
       <c r="G16" t="n">
-        <v>731</v>
+        <v>709</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>74.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="E3" t="n">
-        <v>85.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>973.6</v>
+        <v>1061.3</v>
       </c>
       <c r="I3" t="n">
-        <v>881.6</v>
+        <v>879.1</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>50.9</v>
+        <v>50.4</v>
       </c>
       <c r="E7" t="n">
-        <v>50.1</v>
+        <v>48.3</v>
       </c>
       <c r="F7" t="n">
-        <v>89.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="H7" t="n">
-        <v>712.9</v>
+        <v>504</v>
       </c>
       <c r="I7" t="n">
-        <v>810.3</v>
+        <v>823.9</v>
       </c>
       <c r="J7" t="n">
-        <v>975</v>
+        <v>930</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="E8" t="n">
-        <v>48.3</v>
+        <v>50.1</v>
       </c>
       <c r="F8" t="n">
-        <v>80.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>504</v>
+        <v>702.6</v>
       </c>
       <c r="I8" t="n">
-        <v>823.9</v>
+        <v>810.3</v>
       </c>
       <c r="J8" t="n">
-        <v>930</v>
+        <v>975</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +722,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>49.2</v>
+        <v>48.7</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -731,10 +731,10 @@
         <v>87.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>15.5</v>
+        <v>12.1</v>
       </c>
       <c r="H9" t="n">
-        <v>639.6</v>
+        <v>633.6</v>
       </c>
       <c r="I9" t="n">
         <v>808.1</v>
@@ -756,19 +756,19 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>46.2</v>
+        <v>45.3</v>
       </c>
       <c r="E10" t="n">
         <v>44.8</v>
       </c>
       <c r="F10" t="n">
-        <v>91.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>647.3</v>
+        <v>634.5</v>
       </c>
       <c r="I10" t="n">
         <v>787.3</v>
@@ -1171,7 +1171,9 @@
       <c r="O3" t="n">
         <v>907</v>
       </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>847</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1881,7 +1883,9 @@
       <c r="O3" t="n">
         <v>55.5</v>
       </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>87.7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2010,7 +2014,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>18.1</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="7">
@@ -2060,7 +2064,7 @@
         <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>31.6</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="8">
@@ -2110,7 +2114,7 @@
         <v>51.8</v>
       </c>
       <c r="P8" t="n">
-        <v>91.8</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -2809,19 +2813,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>755.3</v>
+        <v>778.2</v>
       </c>
       <c r="D16" t="n">
-        <v>50.8</v>
+        <v>59.2</v>
       </c>
       <c r="E16" t="n">
-        <v>731</v>
+        <v>778.5</v>
       </c>
       <c r="F16" t="n">
-        <v>826</v>
+        <v>847</v>
       </c>
       <c r="G16" t="n">
         <v>709</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -518,10 +518,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>75.8</v>
+        <v>74.7</v>
       </c>
       <c r="E3" t="n">
-        <v>86.09999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1061.3</v>
+        <v>1045.4</v>
       </c>
       <c r="I3" t="n">
         <v>879.1</v>
@@ -651,25 +651,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>50.4</v>
+        <v>54.2</v>
       </c>
       <c r="E7" t="n">
-        <v>48.3</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>80.40000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>22.2</v>
       </c>
       <c r="H7" t="n">
-        <v>504</v>
+        <v>595.9</v>
       </c>
       <c r="I7" t="n">
-        <v>823.9</v>
+        <v>831.5</v>
       </c>
       <c r="J7" t="n">
         <v>930</v>
@@ -688,7 +688,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>50.2</v>
+        <v>49.8</v>
       </c>
       <c r="E8" t="n">
         <v>50.1</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>702.6</v>
+        <v>697.5</v>
       </c>
       <c r="I8" t="n">
         <v>810.3</v>
@@ -722,7 +722,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -731,10 +731,10 @@
         <v>87.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>12.1</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>633.6</v>
+        <v>631.5</v>
       </c>
       <c r="I9" t="n">
         <v>808.1</v>
@@ -756,7 +756,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
       <c r="E10" t="n">
         <v>44.8</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>634.5</v>
+        <v>617.1</v>
       </c>
       <c r="I10" t="n">
         <v>787.3</v>
@@ -1215,7 +1215,9 @@
       <c r="O4" t="n">
         <v>894</v>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>908</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1884,7 +1886,7 @@
         <v>55.5</v>
       </c>
       <c r="P3" t="n">
-        <v>87.7</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="4">
@@ -1927,7 +1929,9 @@
       <c r="O4" t="n">
         <v>47.6</v>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>91.90000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2014,7 +2018,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>12.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -2064,7 +2068,7 @@
         <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>21.3</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="8">
@@ -2114,7 +2118,7 @@
         <v>51.8</v>
       </c>
       <c r="P8" t="n">
-        <v>79</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="9">
@@ -2813,19 +2817,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>778.2</v>
+        <v>804.2</v>
       </c>
       <c r="D16" t="n">
-        <v>59.2</v>
+        <v>74.2</v>
       </c>
       <c r="E16" t="n">
-        <v>778.5</v>
+        <v>826</v>
       </c>
       <c r="F16" t="n">
-        <v>847</v>
+        <v>908</v>
       </c>
       <c r="G16" t="n">
         <v>709</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1045.4</v>
+        <v>1045.2</v>
       </c>
       <c r="I3" t="n">
         <v>879.1</v>
@@ -654,19 +654,19 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
       <c r="E7" t="n">
         <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>91.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>22.2</v>
       </c>
       <c r="H7" t="n">
-        <v>595.9</v>
+        <v>596.9</v>
       </c>
       <c r="I7" t="n">
         <v>831.5</v>
@@ -688,7 +688,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="E8" t="n">
         <v>50.1</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>697.5</v>
+        <v>694.3</v>
       </c>
       <c r="I8" t="n">
         <v>810.3</v>
@@ -722,7 +722,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -731,10 +731,10 @@
         <v>87.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>7.3</v>
       </c>
       <c r="H9" t="n">
-        <v>631.5</v>
+        <v>628.8</v>
       </c>
       <c r="I9" t="n">
         <v>808.1</v>
@@ -756,7 +756,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="E10" t="n">
         <v>44.8</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>617.1</v>
+        <v>615.9</v>
       </c>
       <c r="I10" t="n">
         <v>787.3</v>
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>34.7</v>
+        <v>35.8</v>
       </c>
       <c r="E12" t="n">
-        <v>36.6</v>
+        <v>33.9</v>
       </c>
       <c r="F12" t="n">
-        <v>62.8</v>
+        <v>67.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>138.9</v>
+        <v>465.2</v>
       </c>
       <c r="I12" t="n">
-        <v>765.2</v>
+        <v>773.5</v>
       </c>
       <c r="J12" t="n">
-        <v>849</v>
+        <v>924</v>
       </c>
     </row>
     <row r="13">
@@ -851,32 +851,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>33.7</v>
+        <v>34.7</v>
       </c>
       <c r="E13" t="n">
-        <v>33.4</v>
+        <v>36.6</v>
       </c>
       <c r="F13" t="n">
-        <v>67.5</v>
+        <v>62.8</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>404.2</v>
+        <v>138.9</v>
       </c>
       <c r="I13" t="n">
-        <v>769</v>
+        <v>765.2</v>
       </c>
       <c r="J13" t="n">
-        <v>924</v>
+        <v>849</v>
       </c>
     </row>
     <row r="14">
@@ -1475,7 +1475,9 @@
       <c r="O10" t="n">
         <v>845</v>
       </c>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>827</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1886,7 +1888,7 @@
         <v>55.5</v>
       </c>
       <c r="P3" t="n">
-        <v>71.8</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1930,7 +1932,7 @@
         <v>47.6</v>
       </c>
       <c r="P4" t="n">
-        <v>91.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2018,7 +2020,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="7">
@@ -2068,7 +2070,7 @@
         <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>16.2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -2118,7 +2120,7 @@
         <v>51.8</v>
       </c>
       <c r="P8" t="n">
-        <v>61.6</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="9">
@@ -2189,7 +2191,9 @@
       <c r="O10" t="n">
         <v>20.8</v>
       </c>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2817,16 +2821,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>804.2</v>
+        <v>808</v>
       </c>
       <c r="D16" t="n">
-        <v>74.2</v>
+        <v>68.2</v>
       </c>
       <c r="E16" t="n">
-        <v>826</v>
+        <v>826.5</v>
       </c>
       <c r="F16" t="n">
         <v>908</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -518,7 +518,7 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>74.7</v>
+        <v>74.8</v>
       </c>
       <c r="E3" t="n">
         <v>81.09999999999999</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1045.2</v>
+        <v>1047.8</v>
       </c>
       <c r="I3" t="n">
         <v>879.1</v>
@@ -654,19 +654,19 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>54.3</v>
+        <v>54.5</v>
       </c>
       <c r="E7" t="n">
         <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="G7" t="n">
         <v>22.2</v>
       </c>
       <c r="H7" t="n">
-        <v>596.9</v>
+        <v>599.2</v>
       </c>
       <c r="I7" t="n">
         <v>831.5</v>
@@ -688,7 +688,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
       <c r="E8" t="n">
         <v>50.1</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>694.3</v>
+        <v>691.2</v>
       </c>
       <c r="I8" t="n">
         <v>810.3</v>
@@ -722,7 +722,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -731,10 +731,10 @@
         <v>87.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>7.3</v>
+        <v>4.9</v>
       </c>
       <c r="H9" t="n">
-        <v>628.8</v>
+        <v>626.4</v>
       </c>
       <c r="I9" t="n">
         <v>808.1</v>
@@ -756,7 +756,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="E10" t="n">
         <v>44.8</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>615.9</v>
+        <v>617.2</v>
       </c>
       <c r="I10" t="n">
         <v>787.3</v>
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E11" t="n">
-        <v>52.3</v>
+        <v>53.6</v>
       </c>
       <c r="F11" t="n">
         <v>64.7</v>
@@ -802,10 +802,10 @@
         <v>14.8</v>
       </c>
       <c r="H11" t="n">
-        <v>280.2</v>
+        <v>343.8</v>
       </c>
       <c r="I11" t="n">
-        <v>767.4</v>
+        <v>775.1</v>
       </c>
       <c r="J11" t="n">
         <v>916</v>
@@ -824,7 +824,7 @@
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="E12" t="n">
         <v>33.9</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>465.2</v>
+        <v>466.6</v>
       </c>
       <c r="I12" t="n">
         <v>773.5</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="E14" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>294</v>
+        <v>330.9</v>
       </c>
       <c r="I14" t="n">
-        <v>714.5</v>
+        <v>720.2</v>
       </c>
       <c r="J14" t="n">
         <v>832</v>
@@ -1621,7 +1621,9 @@
         <v>768</v>
       </c>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>829</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1667,7 +1669,9 @@
       <c r="O15" t="n">
         <v>827</v>
       </c>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>788</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1888,7 +1892,7 @@
         <v>55.5</v>
       </c>
       <c r="P3" t="n">
-        <v>71.59999999999999</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="4">
@@ -1932,7 +1936,7 @@
         <v>47.6</v>
       </c>
       <c r="P4" t="n">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="5">
@@ -2020,7 +2024,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>7.3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -2070,7 +2074,7 @@
         <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="8">
@@ -2120,7 +2124,7 @@
         <v>51.8</v>
       </c>
       <c r="P8" t="n">
-        <v>60.4</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="9">
@@ -2192,7 +2196,7 @@
         <v>20.8</v>
       </c>
       <c r="P10" t="n">
-        <v>61</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="11">
@@ -2337,7 +2341,9 @@
         <v>54.8</v>
       </c>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>63.6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2383,7 +2389,9 @@
       <c r="O15" t="n">
         <v>13.8</v>
       </c>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>36.9</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2821,13 +2829,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>808</v>
+        <v>808.1</v>
       </c>
       <c r="D16" t="n">
-        <v>68.2</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
         <v>826.5</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>76.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>79.7</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,10 +496,10 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>990</v>
+        <v>1079.3</v>
       </c>
       <c r="I2" t="n">
-        <v>880.5</v>
+        <v>881.3</v>
       </c>
       <c r="J2" t="n">
         <v>991</v>
@@ -518,7 +518,7 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>74.8</v>
+        <v>74.5</v>
       </c>
       <c r="E3" t="n">
         <v>81.09999999999999</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1047.8</v>
+        <v>1042.8</v>
       </c>
       <c r="I3" t="n">
         <v>879.1</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>65.5</v>
+        <v>66.3</v>
       </c>
       <c r="E4" t="n">
-        <v>79.8</v>
+        <v>78.3</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>785.8</v>
+        <v>862.3</v>
       </c>
       <c r="I4" t="n">
-        <v>842.8</v>
+        <v>844.2</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>57.2</v>
+        <v>54.3</v>
       </c>
       <c r="E6" t="n">
-        <v>65.59999999999999</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>79.7</v>
+        <v>93.7</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7</v>
+        <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>515</v>
+        <v>597.7</v>
       </c>
       <c r="I6" t="n">
-        <v>841.1</v>
+        <v>831.5</v>
       </c>
       <c r="J6" t="n">
-        <v>953</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>54.5</v>
+        <v>53.8</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>95.2</v>
+        <v>79.7</v>
       </c>
       <c r="G7" t="n">
-        <v>22.2</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>599.2</v>
+        <v>537.8</v>
       </c>
       <c r="I7" t="n">
-        <v>831.5</v>
+        <v>834.3</v>
       </c>
       <c r="J7" t="n">
-        <v>930</v>
+        <v>953</v>
       </c>
     </row>
     <row r="8">
@@ -688,7 +688,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="E8" t="n">
         <v>50.1</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>691.2</v>
+        <v>688.6</v>
       </c>
       <c r="I8" t="n">
         <v>810.3</v>
@@ -722,7 +722,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -731,10 +731,10 @@
         <v>87.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>626.4</v>
+        <v>624.9</v>
       </c>
       <c r="I9" t="n">
         <v>808.1</v>
@@ -756,7 +756,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>44.1</v>
+        <v>43.7</v>
       </c>
       <c r="E10" t="n">
         <v>44.8</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>617.2</v>
+        <v>611.4</v>
       </c>
       <c r="I10" t="n">
         <v>787.3</v>
@@ -790,7 +790,7 @@
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>43</v>
+        <v>42.3</v>
       </c>
       <c r="E11" t="n">
         <v>53.6</v>
@@ -802,7 +802,7 @@
         <v>14.8</v>
       </c>
       <c r="H11" t="n">
-        <v>343.8</v>
+        <v>338.1</v>
       </c>
       <c r="I11" t="n">
         <v>775.1</v>
@@ -824,7 +824,7 @@
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>35.9</v>
+        <v>35.4</v>
       </c>
       <c r="E12" t="n">
         <v>33.9</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>466.6</v>
+        <v>460.8</v>
       </c>
       <c r="I12" t="n">
         <v>773.5</v>
@@ -892,7 +892,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="E14" t="n">
         <v>10.9</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>330.9</v>
+        <v>325.1</v>
       </c>
       <c r="I14" t="n">
         <v>720.2</v>
@@ -1123,7 +1123,9 @@
       <c r="O2" t="n">
         <v>986</v>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>891</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1257,7 +1259,9 @@
       <c r="O5" t="n">
         <v>930</v>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>773</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1585,7 +1589,9 @@
       <c r="O13" t="n">
         <v>977</v>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>860</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1843,7 +1849,9 @@
       <c r="O2" t="n">
         <v>91.2</v>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>89.3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1892,7 +1900,7 @@
         <v>55.5</v>
       </c>
       <c r="P3" t="n">
-        <v>74.2</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="4">
@@ -1936,7 +1944,7 @@
         <v>47.6</v>
       </c>
       <c r="P4" t="n">
-        <v>95.2</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="5">
@@ -1977,7 +1985,9 @@
       <c r="O5" t="n">
         <v>68.8</v>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2024,7 +2034,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="7">
@@ -2074,7 +2084,7 @@
         <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8">
@@ -2124,7 +2134,7 @@
         <v>51.8</v>
       </c>
       <c r="P8" t="n">
-        <v>61.7</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="9">
@@ -2196,7 +2206,7 @@
         <v>20.8</v>
       </c>
       <c r="P10" t="n">
-        <v>62.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="11">
@@ -2305,7 +2315,9 @@
       <c r="O13" t="n">
         <v>88.7</v>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>76.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2342,7 +2354,7 @@
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>63.6</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="15">
@@ -2390,7 +2402,7 @@
         <v>13.8</v>
       </c>
       <c r="P15" t="n">
-        <v>36.9</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="16">
@@ -2829,16 +2841,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>808.1</v>
+        <v>817.2</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>59.3</v>
       </c>
       <c r="E16" t="n">
-        <v>826.5</v>
+        <v>827</v>
       </c>
       <c r="F16" t="n">
         <v>908</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>43.7</v>
+        <v>44.1</v>
       </c>
       <c r="E10" t="n">
-        <v>44.8</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,10 +768,10 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>611.4</v>
+        <v>661.4</v>
       </c>
       <c r="I10" t="n">
-        <v>787.3</v>
+        <v>788.7</v>
       </c>
       <c r="J10" t="n">
         <v>928</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1076,6 +1076,11 @@
           <t>9/16/26</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>9/17/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1126,6 +1131,7 @@
       <c r="P2" t="n">
         <v>891</v>
       </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1176,6 +1182,7 @@
       <c r="P3" t="n">
         <v>847</v>
       </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1220,6 +1227,7 @@
       <c r="P4" t="n">
         <v>908</v>
       </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1262,6 +1270,7 @@
       <c r="P5" t="n">
         <v>773</v>
       </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1310,6 +1319,7 @@
       <c r="P6" t="n">
         <v>709</v>
       </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1360,6 +1370,7 @@
       <c r="P7" t="n">
         <v>731</v>
       </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1409,6 +1420,9 @@
       </c>
       <c r="P8" t="n">
         <v>826</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>808</v>
       </c>
     </row>
     <row r="9">
@@ -1434,6 +1448,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1482,6 +1497,7 @@
       <c r="P10" t="n">
         <v>827</v>
       </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1514,6 +1530,7 @@
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1544,6 +1561,7 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1592,6 +1610,7 @@
       <c r="P13" t="n">
         <v>860</v>
       </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1630,6 +1649,7 @@
       <c r="P14" t="n">
         <v>829</v>
       </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1678,6 +1698,7 @@
       <c r="P15" t="n">
         <v>788</v>
       </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1706,6 +1727,7 @@
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1718,7 +1740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1802,6 +1824,11 @@
           <t>9/16/26</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>9/17/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1852,6 +1879,7 @@
       <c r="P2" t="n">
         <v>89.3</v>
       </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1902,6 +1930,7 @@
       <c r="P3" t="n">
         <v>69.2</v>
       </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1946,6 +1975,7 @@
       <c r="P4" t="n">
         <v>93.7</v>
       </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1988,6 +2018,7 @@
       <c r="P5" t="n">
         <v>22.8</v>
       </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2036,6 +2067,7 @@
       <c r="P6" t="n">
         <v>3.4</v>
       </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2086,6 +2118,7 @@
       <c r="P7" t="n">
         <v>7.3</v>
       </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2135,6 +2168,9 @@
       </c>
       <c r="P8" t="n">
         <v>55.9</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -2160,6 +2196,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2208,6 +2245,7 @@
       <c r="P10" t="n">
         <v>56.6</v>
       </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2240,6 +2278,7 @@
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2270,6 +2309,7 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2318,6 +2358,7 @@
       <c r="P13" t="n">
         <v>76.5</v>
       </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2356,6 +2397,7 @@
       <c r="P14" t="n">
         <v>57.9</v>
       </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2404,6 +2446,7 @@
       <c r="P15" t="n">
         <v>31.1</v>
       </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2432,6 +2475,7 @@
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2444,7 +2488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2859,6 +2903,31 @@
         <v>709</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>9/17/26</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>808</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>808</v>
+      </c>
+      <c r="F17" t="n">
+        <v>808</v>
+      </c>
+      <c r="G17" t="n">
+        <v>808</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -756,10 +756,10 @@
         <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>44.1</v>
+        <v>46.4</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>50.7</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>661.4</v>
+        <v>695.5</v>
       </c>
       <c r="I10" t="n">
         <v>788.7</v>
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>34.7</v>
+        <v>31</v>
       </c>
       <c r="E13" t="n">
-        <v>36.6</v>
+        <v>16.9</v>
       </c>
       <c r="F13" t="n">
         <v>62.8</v>
@@ -870,10 +870,10 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>138.9</v>
+        <v>154.8</v>
       </c>
       <c r="I13" t="n">
-        <v>765.2</v>
+        <v>761.8</v>
       </c>
       <c r="J13" t="n">
         <v>849</v>
@@ -1561,7 +1561,9 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>748</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2170,7 +2172,7 @@
         <v>55.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>50</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2309,7 +2311,9 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2910,22 +2914,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>808</v>
+        <v>778</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E17" t="n">
-        <v>808</v>
+        <v>778</v>
       </c>
       <c r="F17" t="n">
         <v>808</v>
       </c>
       <c r="G17" t="n">
-        <v>808</v>
+        <v>748</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>54.3</v>
+        <v>56.8</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>51.8</v>
       </c>
       <c r="F6" t="n">
         <v>93.7</v>
@@ -632,10 +632,10 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>597.7</v>
+        <v>681.1</v>
       </c>
       <c r="I6" t="n">
-        <v>831.5</v>
+        <v>837.9</v>
       </c>
       <c r="J6" t="n">
         <v>930</v>
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>49.2</v>
+        <v>50.5</v>
       </c>
       <c r="E8" t="n">
-        <v>50.1</v>
+        <v>53.1</v>
       </c>
       <c r="F8" t="n">
-        <v>89.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>688.6</v>
+        <v>707.2</v>
       </c>
       <c r="I8" t="n">
-        <v>810.3</v>
+        <v>815</v>
       </c>
       <c r="J8" t="n">
-        <v>975</v>
+        <v>960</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>48.1</v>
+        <v>49.2</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F9" t="n">
-        <v>87.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>624.9</v>
+        <v>688.6</v>
       </c>
       <c r="I9" t="n">
-        <v>808.1</v>
+        <v>810.3</v>
       </c>
       <c r="J9" t="n">
-        <v>960</v>
+        <v>975</v>
       </c>
     </row>
     <row r="10">
@@ -756,10 +756,10 @@
         <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>46.4</v>
+        <v>42.8</v>
       </c>
       <c r="E10" t="n">
-        <v>50.7</v>
+        <v>38.9</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>695.5</v>
+        <v>642</v>
       </c>
       <c r="I10" t="n">
         <v>788.7</v>
@@ -858,7 +858,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>29.4</v>
       </c>
       <c r="E13" t="n">
         <v>16.9</v>
@@ -870,7 +870,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>154.8</v>
+        <v>147.1</v>
       </c>
       <c r="I13" t="n">
         <v>761.8</v>
@@ -1227,7 +1227,9 @@
       <c r="P4" t="n">
         <v>908</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>908</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1319,7 +1321,9 @@
       <c r="P6" t="n">
         <v>709</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>905</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1977,7 +1981,9 @@
       <c r="P4" t="n">
         <v>93.7</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>83.40000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2069,7 +2075,9 @@
       <c r="P6" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>82.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2172,7 +2180,7 @@
         <v>55.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>84.09999999999999</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="9">
@@ -2312,7 +2320,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>15.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2914,19 +2922,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>778</v>
+        <v>842.2</v>
       </c>
       <c r="D17" t="n">
-        <v>30</v>
+        <v>67.7</v>
       </c>
       <c r="E17" t="n">
-        <v>778</v>
+        <v>856.5</v>
       </c>
       <c r="F17" t="n">
-        <v>808</v>
+        <v>908</v>
       </c>
       <c r="G17" t="n">
         <v>748</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>74.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>81.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1042.8</v>
+        <v>1104</v>
       </c>
       <c r="I3" t="n">
-        <v>879.1</v>
+        <v>878.1</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>681.1</v>
+        <v>681.9</v>
       </c>
       <c r="I6" t="n">
         <v>837.9</v>
@@ -688,7 +688,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E8" t="n">
         <v>53.1</v>
@@ -700,7 +700,7 @@
         <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>707.2</v>
+        <v>707.9</v>
       </c>
       <c r="I8" t="n">
         <v>815</v>
@@ -756,7 +756,7 @@
         <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>42.8</v>
+        <v>42.5</v>
       </c>
       <c r="E10" t="n">
         <v>38.9</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>642</v>
+        <v>637.8</v>
       </c>
       <c r="I10" t="n">
         <v>788.7</v>
@@ -858,7 +858,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>29.4</v>
+        <v>28.8</v>
       </c>
       <c r="E13" t="n">
         <v>16.9</v>
@@ -870,7 +870,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>147.1</v>
+        <v>144.2</v>
       </c>
       <c r="I13" t="n">
         <v>761.8</v>
@@ -1182,7 +1182,9 @@
       <c r="P3" t="n">
         <v>847</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>864</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1936,7 +1938,9 @@
       <c r="P3" t="n">
         <v>69.2</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>61.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1982,7 +1986,7 @@
         <v>93.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>83.40000000000001</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="5">
@@ -2076,7 +2080,7 @@
         <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>82.3</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
@@ -2180,7 +2184,7 @@
         <v>55.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>30.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="9">
@@ -2320,7 +2324,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="13">
@@ -2922,16 +2926,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>842.2</v>
+        <v>846.6</v>
       </c>
       <c r="D17" t="n">
-        <v>67.7</v>
+        <v>61.1</v>
       </c>
       <c r="E17" t="n">
-        <v>856.5</v>
+        <v>864</v>
       </c>
       <c r="F17" t="n">
         <v>908</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -518,7 +518,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>73.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>76.7</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1104</v>
+        <v>1116.3</v>
       </c>
       <c r="I3" t="n">
         <v>878.1</v>
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>56.8</v>
+        <v>57.1</v>
       </c>
       <c r="E6" t="n">
         <v>51.8</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>681.9</v>
+        <v>685.2</v>
       </c>
       <c r="I6" t="n">
         <v>837.9</v>
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>53.8</v>
+        <v>50.8</v>
       </c>
       <c r="E7" t="n">
-        <v>64.59999999999999</v>
+        <v>53.1</v>
       </c>
       <c r="F7" t="n">
-        <v>79.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>537.8</v>
+        <v>711.6</v>
       </c>
       <c r="I7" t="n">
-        <v>834.3</v>
+        <v>815</v>
       </c>
       <c r="J7" t="n">
-        <v>953</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>50.6</v>
+        <v>49.2</v>
       </c>
       <c r="E8" t="n">
-        <v>53.1</v>
+        <v>63.6</v>
       </c>
       <c r="F8" t="n">
-        <v>87.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="n">
-        <v>707.9</v>
+        <v>541</v>
       </c>
       <c r="I8" t="n">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="J8" t="n">
-        <v>960</v>
+        <v>953</v>
       </c>
     </row>
     <row r="9">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>49.2</v>
+        <v>48.6</v>
       </c>
       <c r="E9" t="n">
-        <v>50.1</v>
+        <v>43.9</v>
       </c>
       <c r="F9" t="n">
         <v>89.09999999999999</v>
@@ -734,10 +734,10 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>688.6</v>
+        <v>728.3</v>
       </c>
       <c r="I9" t="n">
-        <v>810.3</v>
+        <v>808.9</v>
       </c>
       <c r="J9" t="n">
         <v>975</v>
@@ -756,10 +756,10 @@
         <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>42.5</v>
+        <v>44</v>
       </c>
       <c r="E10" t="n">
-        <v>38.9</v>
+        <v>48.6</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>637.8</v>
+        <v>660</v>
       </c>
       <c r="I10" t="n">
         <v>788.7</v>
@@ -858,10 +858,10 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>28.8</v>
+        <v>32.3</v>
       </c>
       <c r="E13" t="n">
-        <v>16.9</v>
+        <v>22.8</v>
       </c>
       <c r="F13" t="n">
         <v>62.8</v>
@@ -870,7 +870,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>144.2</v>
+        <v>161.7</v>
       </c>
       <c r="I13" t="n">
         <v>761.8</v>
@@ -1274,7 +1274,9 @@
       <c r="P5" t="n">
         <v>773</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>655</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1376,7 +1378,9 @@
       <c r="P7" t="n">
         <v>731</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>789</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1939,7 +1943,7 @@
         <v>69.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>61.2</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="4">
@@ -1986,7 +1990,7 @@
         <v>93.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>84.2</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="5">
@@ -2030,7 +2034,9 @@
       <c r="P5" t="n">
         <v>22.8</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2080,7 +2086,7 @@
         <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>83</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="7">
@@ -2132,7 +2138,9 @@
       <c r="P7" t="n">
         <v>7.3</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>39.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2184,7 +2192,7 @@
         <v>55.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="9">
@@ -2324,7 +2332,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>5.3</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="13">
@@ -2926,22 +2934,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>846.6</v>
+        <v>811</v>
       </c>
       <c r="D17" t="n">
-        <v>61.1</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>808</v>
       </c>
       <c r="F17" t="n">
         <v>908</v>
       </c>
       <c r="G17" t="n">
-        <v>748</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -518,7 +518,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>74.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="E3" t="n">
         <v>76.7</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1116.3</v>
+        <v>1118</v>
       </c>
       <c r="I3" t="n">
         <v>878.1</v>
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="E6" t="n">
         <v>51.8</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>685.2</v>
+        <v>686.9</v>
       </c>
       <c r="I6" t="n">
         <v>837.9</v>
@@ -654,19 +654,19 @@
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="E7" t="n">
         <v>53.1</v>
       </c>
       <c r="F7" t="n">
-        <v>87.90000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="G7" t="n">
         <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>711.6</v>
+        <v>713.4</v>
       </c>
       <c r="I7" t="n">
         <v>815</v>
@@ -688,7 +688,7 @@
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E8" t="n">
         <v>63.6</v>
@@ -697,10 +697,10 @@
         <v>79.7</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>541</v>
+        <v>540.3</v>
       </c>
       <c r="I8" t="n">
         <v>818</v>
@@ -722,7 +722,7 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="E9" t="n">
         <v>43.9</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>728.3</v>
+        <v>728</v>
       </c>
       <c r="I9" t="n">
         <v>808.9</v>
@@ -759,7 +759,7 @@
         <v>44</v>
       </c>
       <c r="E10" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>660</v>
+        <v>660.3</v>
       </c>
       <c r="I10" t="n">
         <v>788.7</v>
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>42.3</v>
+        <v>42.8</v>
       </c>
       <c r="E11" t="n">
-        <v>53.6</v>
+        <v>52.3</v>
       </c>
       <c r="F11" t="n">
         <v>64.7</v>
@@ -802,10 +802,10 @@
         <v>14.8</v>
       </c>
       <c r="H11" t="n">
-        <v>338.1</v>
+        <v>385.4</v>
       </c>
       <c r="I11" t="n">
-        <v>775.1</v>
+        <v>778.4</v>
       </c>
       <c r="J11" t="n">
         <v>916</v>
@@ -858,10 +858,10 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="E13" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="F13" t="n">
         <v>62.8</v>
@@ -870,7 +870,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>161.7</v>
+        <v>160.4</v>
       </c>
       <c r="I13" t="n">
         <v>761.8</v>
@@ -1661,7 +1661,9 @@
       <c r="P14" t="n">
         <v>829</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>805</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1943,7 +1945,7 @@
         <v>69.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>73.5</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="4">
@@ -1990,7 +1992,7 @@
         <v>93.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>87.5</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="5">
@@ -2035,7 +2037,7 @@
         <v>22.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -2086,7 +2088,7 @@
         <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>86.7</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="7">
@@ -2139,7 +2141,7 @@
         <v>7.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>39.7</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="8">
@@ -2192,7 +2194,7 @@
         <v>55.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="9">
@@ -2332,7 +2334,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="13">
@@ -2421,7 +2423,9 @@
       <c r="P14" t="n">
         <v>57.9</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>47.3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2934,16 +2938,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>811</v>
+        <v>810.2</v>
       </c>
       <c r="D17" t="n">
-        <v>84.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>808</v>
+        <v>806.5</v>
       </c>
       <c r="F17" t="n">
         <v>908</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>77.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>84.3</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,10 +496,10 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1079.3</v>
+        <v>1169</v>
       </c>
       <c r="I2" t="n">
-        <v>881.3</v>
+        <v>883.7</v>
       </c>
       <c r="J2" t="n">
         <v>991</v>
@@ -518,7 +518,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>74.5</v>
+        <v>74.3</v>
       </c>
       <c r="E3" t="n">
         <v>76.7</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1118</v>
+        <v>1115.2</v>
       </c>
       <c r="I3" t="n">
         <v>878.1</v>
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>57.2</v>
+        <v>57.1</v>
       </c>
       <c r="E6" t="n">
         <v>51.8</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>686.9</v>
+        <v>685.2</v>
       </c>
       <c r="I6" t="n">
         <v>837.9</v>
@@ -654,19 +654,19 @@
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="E7" t="n">
         <v>53.1</v>
       </c>
       <c r="F7" t="n">
-        <v>88.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>713.4</v>
+        <v>711.7</v>
       </c>
       <c r="I7" t="n">
         <v>815</v>
@@ -697,10 +697,10 @@
         <v>79.7</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>540.3</v>
+        <v>539.8</v>
       </c>
       <c r="I8" t="n">
         <v>818</v>
@@ -722,7 +722,7 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="E9" t="n">
         <v>43.9</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>728</v>
+        <v>724.8</v>
       </c>
       <c r="I9" t="n">
         <v>808.9</v>
@@ -756,10 +756,10 @@
         <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="E10" t="n">
-        <v>48.9</v>
+        <v>45.5</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>660.3</v>
+        <v>656.9</v>
       </c>
       <c r="I10" t="n">
         <v>788.7</v>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>42.8</v>
+        <v>42.5</v>
       </c>
       <c r="E11" t="n">
         <v>52.3</v>
@@ -802,7 +802,7 @@
         <v>14.8</v>
       </c>
       <c r="H11" t="n">
-        <v>385.4</v>
+        <v>382.1</v>
       </c>
       <c r="I11" t="n">
         <v>778.4</v>
@@ -858,10 +858,10 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>32.1</v>
+        <v>31.6</v>
       </c>
       <c r="E13" t="n">
-        <v>21.5</v>
+        <v>19.2</v>
       </c>
       <c r="F13" t="n">
         <v>62.8</v>
@@ -870,7 +870,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>160.4</v>
+        <v>158.1</v>
       </c>
       <c r="I13" t="n">
         <v>761.8</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="E14" t="n">
-        <v>10.9</v>
+        <v>12.4</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>325.1</v>
+        <v>352.7</v>
       </c>
       <c r="I14" t="n">
-        <v>720.2</v>
+        <v>723.7</v>
       </c>
       <c r="J14" t="n">
         <v>832</v>
@@ -1131,7 +1131,9 @@
       <c r="P2" t="n">
         <v>891</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>917</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1712,7 +1714,9 @@
       <c r="P15" t="n">
         <v>788</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="n">
+        <v>770</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1893,7 +1897,9 @@
       <c r="P2" t="n">
         <v>89.3</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>89.7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1945,7 +1951,7 @@
         <v>69.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>75.2</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1992,7 +1998,7 @@
         <v>93.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>89.2</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="5">
@@ -2037,7 +2043,7 @@
         <v>22.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2088,7 +2094,7 @@
         <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>88.5</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="7">
@@ -2141,7 +2147,7 @@
         <v>7.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>39.4</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="8">
@@ -2194,7 +2200,7 @@
         <v>55.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>48.9</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="9">
@@ -2334,7 +2340,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>21.5</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="13">
@@ -2424,7 +2430,7 @@
         <v>57.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
@@ -2474,7 +2480,9 @@
       <c r="P15" t="n">
         <v>31.1</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="n">
+        <v>27.6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2938,10 +2946,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>810.2</v>
+        <v>816.9</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -2950,7 +2958,7 @@
         <v>806.5</v>
       </c>
       <c r="F17" t="n">
-        <v>908</v>
+        <v>917</v>
       </c>
       <c r="G17" t="n">
         <v>655</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>77.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="E2" t="n">
         <v>84.3</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1169</v>
+        <v>1170.6</v>
       </c>
       <c r="I2" t="n">
         <v>883.7</v>
@@ -518,7 +518,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>74.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E3" t="n">
         <v>76.7</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1115.2</v>
+        <v>1118.4</v>
       </c>
       <c r="I3" t="n">
         <v>878.1</v>
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>57.1</v>
+        <v>57.3</v>
       </c>
       <c r="E6" t="n">
         <v>51.8</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>685.2</v>
+        <v>687.1</v>
       </c>
       <c r="I6" t="n">
         <v>837.9</v>
@@ -654,19 +654,19 @@
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="E7" t="n">
         <v>53.1</v>
       </c>
       <c r="F7" t="n">
-        <v>87.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="G7" t="n">
         <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>711.7</v>
+        <v>713.6</v>
       </c>
       <c r="I7" t="n">
         <v>815</v>
@@ -697,10 +697,10 @@
         <v>79.7</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>539.8</v>
+        <v>540.4</v>
       </c>
       <c r="I8" t="n">
         <v>818</v>
@@ -722,7 +722,7 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
       <c r="E9" t="n">
         <v>43.9</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>724.8</v>
+        <v>728.7</v>
       </c>
       <c r="I9" t="n">
         <v>808.9</v>
@@ -756,10 +756,10 @@
         <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>43.8</v>
+        <v>44.1</v>
       </c>
       <c r="E10" t="n">
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>656.9</v>
+        <v>660.9</v>
       </c>
       <c r="I10" t="n">
         <v>788.7</v>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>42.5</v>
+        <v>42.9</v>
       </c>
       <c r="E11" t="n">
         <v>52.3</v>
@@ -802,7 +802,7 @@
         <v>14.8</v>
       </c>
       <c r="H11" t="n">
-        <v>382.1</v>
+        <v>386.1</v>
       </c>
       <c r="I11" t="n">
         <v>778.4</v>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>35.4</v>
+        <v>34.1</v>
       </c>
       <c r="E12" t="n">
-        <v>33.9</v>
+        <v>33.4</v>
       </c>
       <c r="F12" t="n">
         <v>67.5</v>
@@ -836,10 +836,10 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>460.8</v>
+        <v>476.8</v>
       </c>
       <c r="I12" t="n">
-        <v>773.5</v>
+        <v>770.4</v>
       </c>
       <c r="J12" t="n">
         <v>924</v>
@@ -858,10 +858,10 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>31.6</v>
+        <v>32.2</v>
       </c>
       <c r="E13" t="n">
-        <v>19.2</v>
+        <v>22.1</v>
       </c>
       <c r="F13" t="n">
         <v>62.8</v>
@@ -870,7 +870,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>158.1</v>
+        <v>161</v>
       </c>
       <c r="I13" t="n">
         <v>761.8</v>
@@ -892,7 +892,7 @@
         <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="E14" t="n">
         <v>12.4</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>352.7</v>
+        <v>356.3</v>
       </c>
       <c r="I14" t="n">
         <v>723.7</v>
@@ -1509,7 +1509,9 @@
       <c r="P10" t="n">
         <v>827</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>730</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1898,7 +1900,7 @@
         <v>89.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>89.7</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="3">
@@ -1951,7 +1953,7 @@
         <v>69.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>72.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1998,7 +2000,7 @@
         <v>93.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>87.5</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2043,7 +2045,7 @@
         <v>22.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -2094,7 +2096,7 @@
         <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>86.8</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="7">
@@ -2147,7 +2149,7 @@
         <v>7.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>36.2</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="8">
@@ -2200,7 +2202,7 @@
         <v>55.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="9">
@@ -2275,7 +2277,9 @@
       <c r="P10" t="n">
         <v>56.6</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2340,7 +2344,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>19.2</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="13">
@@ -2430,7 +2434,7 @@
         <v>57.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2481,7 +2485,7 @@
         <v>31.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>27.6</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="16">
@@ -2946,16 +2950,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>816.9</v>
+        <v>809</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>806.5</v>
+        <v>805</v>
       </c>
       <c r="F17" t="n">
         <v>917</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>84.3</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1170.6</v>
+        <v>1172</v>
       </c>
       <c r="I2" t="n">
         <v>883.7</v>
@@ -518,10 +518,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="E3" t="n">
-        <v>76.7</v>
+        <v>77.7</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1118.4</v>
+        <v>1120.5</v>
       </c>
       <c r="I3" t="n">
         <v>878.1</v>
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>57.3</v>
+        <v>57.4</v>
       </c>
       <c r="E6" t="n">
         <v>51.8</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>687.1</v>
+        <v>688.6</v>
       </c>
       <c r="I6" t="n">
         <v>837.9</v>
@@ -654,19 +654,19 @@
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="E7" t="n">
         <v>53.1</v>
       </c>
       <c r="F7" t="n">
-        <v>88.7</v>
+        <v>90.2</v>
       </c>
       <c r="G7" t="n">
         <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>713.6</v>
+        <v>715.1</v>
       </c>
       <c r="I7" t="n">
         <v>815</v>
@@ -722,7 +722,7 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="E9" t="n">
         <v>43.9</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>728.7</v>
+        <v>730.2</v>
       </c>
       <c r="I9" t="n">
         <v>808.9</v>
@@ -756,10 +756,10 @@
         <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="E10" t="n">
-        <v>49.5</v>
+        <v>50.7</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>660.9</v>
+        <v>662.8</v>
       </c>
       <c r="I10" t="n">
         <v>788.7</v>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="E11" t="n">
         <v>52.3</v>
@@ -802,7 +802,7 @@
         <v>14.8</v>
       </c>
       <c r="H11" t="n">
-        <v>386.1</v>
+        <v>388</v>
       </c>
       <c r="I11" t="n">
         <v>778.4</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>476.8</v>
+        <v>477.2</v>
       </c>
       <c r="I12" t="n">
         <v>770.4</v>
@@ -858,10 +858,10 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="E13" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="F13" t="n">
         <v>62.8</v>
@@ -870,7 +870,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>161</v>
+        <v>161.8</v>
       </c>
       <c r="I13" t="n">
         <v>761.8</v>
@@ -892,7 +892,7 @@
         <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="E14" t="n">
         <v>12.4</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>356.3</v>
+        <v>357.5</v>
       </c>
       <c r="I14" t="n">
         <v>723.7</v>
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>22.6</v>
+        <v>23.8</v>
       </c>
       <c r="E15" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
         <v>57.5</v>
@@ -938,10 +938,10 @@
         <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>113</v>
+        <v>142.6</v>
       </c>
       <c r="I15" t="n">
-        <v>716.2</v>
+        <v>724.2</v>
       </c>
       <c r="J15" t="n">
         <v>832</v>
@@ -1544,7 +1544,9 @@
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>764</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1900,7 +1902,7 @@
         <v>89.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>91.3</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="3">
@@ -1953,7 +1955,7 @@
         <v>69.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>75.59999999999999</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="4">
@@ -2000,7 +2002,7 @@
         <v>93.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>89.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2096,7 +2098,7 @@
         <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>88.7</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="7">
@@ -2149,7 +2151,7 @@
         <v>7.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>40.1</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="8">
@@ -2202,7 +2204,7 @@
         <v>55.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>49.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="9">
@@ -2278,7 +2280,7 @@
         <v>56.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="11">
@@ -2312,7 +2314,9 @@
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>29.6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2344,7 +2348,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="13">
@@ -2434,7 +2438,7 @@
         <v>57.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>48</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="15">
@@ -2485,7 +2489,7 @@
         <v>31.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.2</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="16">
@@ -2950,16 +2954,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>809</v>
+        <v>805.2</v>
       </c>
       <c r="D17" t="n">
-        <v>79.40000000000001</v>
+        <v>77</v>
       </c>
       <c r="E17" t="n">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="F17" t="n">
         <v>917</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>57.4</v>
+        <v>59.4</v>
       </c>
       <c r="E6" t="n">
-        <v>51.8</v>
+        <v>54.5</v>
       </c>
       <c r="F6" t="n">
         <v>93.7</v>
@@ -632,13 +632,13 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>688.6</v>
+        <v>772.7</v>
       </c>
       <c r="I6" t="n">
-        <v>837.9</v>
+        <v>847.2</v>
       </c>
       <c r="J6" t="n">
-        <v>930</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>51.1</v>
+        <v>49.1</v>
       </c>
       <c r="E7" t="n">
-        <v>53.1</v>
+        <v>63.6</v>
       </c>
       <c r="F7" t="n">
-        <v>90.2</v>
+        <v>79.7</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>715.1</v>
+        <v>540.4</v>
       </c>
       <c r="I7" t="n">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="J7" t="n">
-        <v>960</v>
+        <v>953</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>49.1</v>
+        <v>48.7</v>
       </c>
       <c r="E8" t="n">
-        <v>63.6</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>79.7</v>
+        <v>90.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>540.4</v>
+        <v>731</v>
       </c>
       <c r="I8" t="n">
-        <v>818</v>
+        <v>818.3</v>
       </c>
       <c r="J8" t="n">
-        <v>953</v>
+        <v>960</v>
       </c>
     </row>
     <row r="9">
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1081,6 +1081,11 @@
           <t>9/17/26</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>9/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1134,6 +1139,7 @@
       <c r="Q2" t="n">
         <v>917</v>
       </c>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1187,6 +1193,7 @@
       <c r="Q3" t="n">
         <v>864</v>
       </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1233,6 +1240,9 @@
       </c>
       <c r="Q4" t="n">
         <v>908</v>
+      </c>
+      <c r="R4" t="n">
+        <v>959</v>
       </c>
     </row>
     <row r="5">
@@ -1279,6 +1289,7 @@
       <c r="Q5" t="n">
         <v>655</v>
       </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1330,6 +1341,9 @@
       <c r="Q6" t="n">
         <v>905</v>
       </c>
+      <c r="R6" t="n">
+        <v>864</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1383,6 +1397,7 @@
       <c r="Q7" t="n">
         <v>789</v>
       </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1436,6 +1451,7 @@
       <c r="Q8" t="n">
         <v>808</v>
       </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1461,6 +1477,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1512,6 +1529,7 @@
       <c r="Q10" t="n">
         <v>730</v>
       </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1547,6 +1565,7 @@
       <c r="Q11" t="n">
         <v>764</v>
       </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1580,6 +1599,7 @@
       <c r="Q12" t="n">
         <v>748</v>
       </c>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1629,6 +1649,7 @@
         <v>860</v>
       </c>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1670,6 +1691,7 @@
       <c r="Q14" t="n">
         <v>805</v>
       </c>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1721,6 +1743,7 @@
       <c r="Q15" t="n">
         <v>770</v>
       </c>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1750,6 +1773,7 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1762,7 +1786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1851,6 +1875,11 @@
           <t>9/17/26</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>9/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1904,6 +1933,7 @@
       <c r="Q2" t="n">
         <v>92.7</v>
       </c>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1957,6 +1987,7 @@
       <c r="Q3" t="n">
         <v>77.7</v>
       </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2003,6 +2034,9 @@
       </c>
       <c r="Q4" t="n">
         <v>90.90000000000001</v>
+      </c>
+      <c r="R4" t="n">
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2049,6 +2083,7 @@
       <c r="Q5" t="n">
         <v>2.6</v>
       </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2100,6 +2135,9 @@
       <c r="Q6" t="n">
         <v>90.2</v>
       </c>
+      <c r="R6" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2153,6 +2191,7 @@
       <c r="Q7" t="n">
         <v>41.6</v>
       </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2206,6 +2245,7 @@
       <c r="Q8" t="n">
         <v>51.4</v>
       </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2231,6 +2271,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2282,6 +2323,7 @@
       <c r="Q10" t="n">
         <v>16.4</v>
       </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2317,6 +2359,7 @@
       <c r="Q11" t="n">
         <v>29.6</v>
       </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2350,6 +2393,7 @@
       <c r="Q12" t="n">
         <v>22.9</v>
       </c>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2399,6 +2443,7 @@
         <v>76.5</v>
       </c>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2440,6 +2485,7 @@
       <c r="Q14" t="n">
         <v>49.9</v>
       </c>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2491,6 +2537,7 @@
       <c r="Q15" t="n">
         <v>32.4</v>
       </c>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2520,6 +2567,7 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2532,7 +2580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2972,6 +3020,31 @@
         <v>655</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>9/18/26</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>911.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>911.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>959</v>
+      </c>
+      <c r="G18" t="n">
+        <v>864</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -620,7 +620,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>59.4</v>
+        <v>59.6</v>
       </c>
       <c r="E6" t="n">
         <v>54.5</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>772.7</v>
+        <v>774.4</v>
       </c>
       <c r="I6" t="n">
         <v>847.2</v>
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>49.1</v>
+        <v>51.7</v>
       </c>
       <c r="E7" t="n">
-        <v>63.6</v>
+        <v>56.2</v>
       </c>
       <c r="F7" t="n">
-        <v>79.7</v>
+        <v>90.2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>540.4</v>
+        <v>775.4</v>
       </c>
       <c r="I7" t="n">
-        <v>818</v>
+        <v>818.3</v>
       </c>
       <c r="J7" t="n">
-        <v>953</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>63.6</v>
       </c>
       <c r="F8" t="n">
-        <v>90.2</v>
+        <v>79.7</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>731</v>
+        <v>540.4</v>
       </c>
       <c r="I8" t="n">
-        <v>818.3</v>
+        <v>818</v>
       </c>
       <c r="J8" t="n">
-        <v>960</v>
+        <v>953</v>
       </c>
     </row>
     <row r="9">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>48.7</v>
+        <v>46.2</v>
       </c>
       <c r="E9" t="n">
-        <v>43.9</v>
+        <v>42.8</v>
       </c>
       <c r="F9" t="n">
         <v>89.09999999999999</v>
@@ -734,10 +734,10 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>730.2</v>
+        <v>739.3</v>
       </c>
       <c r="I9" t="n">
-        <v>808.9</v>
+        <v>800.6</v>
       </c>
       <c r="J9" t="n">
         <v>975</v>
@@ -1397,7 +1397,9 @@
       <c r="Q7" t="n">
         <v>789</v>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>677</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2036,7 +2038,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>84.09999999999999</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="5">
@@ -2136,7 +2138,7 @@
         <v>90.2</v>
       </c>
       <c r="R6" t="n">
-        <v>15.9</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="7">
@@ -2191,7 +2193,9 @@
       <c r="Q7" t="n">
         <v>41.6</v>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>9.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3027,22 +3031,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>911.5</v>
+        <v>833.3</v>
       </c>
       <c r="D18" t="n">
-        <v>47.5</v>
+        <v>117.2</v>
       </c>
       <c r="E18" t="n">
-        <v>911.5</v>
+        <v>864</v>
       </c>
       <c r="F18" t="n">
         <v>959</v>
       </c>
       <c r="G18" t="n">
-        <v>864</v>
+        <v>677</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>78.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>84.3</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,10 +496,10 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1172</v>
+        <v>1246.9</v>
       </c>
       <c r="I2" t="n">
-        <v>883.7</v>
+        <v>886</v>
       </c>
       <c r="J2" t="n">
         <v>991</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>74.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>77.7</v>
+        <v>79.2</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1120.5</v>
+        <v>1201.1</v>
       </c>
       <c r="I3" t="n">
-        <v>878.1</v>
+        <v>882.1</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -620,7 +620,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="E6" t="n">
         <v>54.5</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>774.4</v>
+        <v>773.2</v>
       </c>
       <c r="I6" t="n">
         <v>847.2</v>
@@ -654,10 +654,10 @@
         <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="E7" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="F7" t="n">
         <v>90.2</v>
@@ -666,7 +666,7 @@
         <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>775.4</v>
+        <v>771.2</v>
       </c>
       <c r="I7" t="n">
         <v>818.3</v>
@@ -722,7 +722,7 @@
         <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
       <c r="E9" t="n">
         <v>42.8</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>739.3</v>
+        <v>736.3</v>
       </c>
       <c r="I9" t="n">
         <v>800.6</v>
@@ -787,25 +787,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>43.1</v>
+        <v>40</v>
       </c>
       <c r="E11" t="n">
-        <v>52.3</v>
+        <v>51.1</v>
       </c>
       <c r="F11" t="n">
         <v>64.7</v>
       </c>
       <c r="G11" t="n">
-        <v>14.8</v>
+        <v>12.2</v>
       </c>
       <c r="H11" t="n">
-        <v>388</v>
+        <v>400.2</v>
       </c>
       <c r="I11" t="n">
-        <v>778.4</v>
+        <v>772.5</v>
       </c>
       <c r="J11" t="n">
         <v>916</v>
@@ -1139,7 +1139,9 @@
       <c r="Q2" t="n">
         <v>917</v>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>921</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1193,7 +1195,9 @@
       <c r="Q3" t="n">
         <v>864</v>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>942</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1693,7 +1697,9 @@
       <c r="Q14" t="n">
         <v>805</v>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>719</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1935,7 +1941,9 @@
       <c r="Q2" t="n">
         <v>92.7</v>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>74.90000000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1989,7 +1997,9 @@
       <c r="Q3" t="n">
         <v>77.7</v>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>80.59999999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2038,7 +2048,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>85.8</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2138,7 +2148,7 @@
         <v>90.2</v>
       </c>
       <c r="R6" t="n">
-        <v>60.3</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="7">
@@ -2194,7 +2204,7 @@
         <v>41.6</v>
       </c>
       <c r="R7" t="n">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="8">
@@ -2489,7 +2499,9 @@
       <c r="Q14" t="n">
         <v>49.9</v>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>12.2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3031,16 +3043,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>833.3</v>
+        <v>847</v>
       </c>
       <c r="D18" t="n">
-        <v>117.2</v>
+        <v>110</v>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>892.5</v>
       </c>
       <c r="F18" t="n">
         <v>959</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>77.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="E2" t="n">
         <v>82</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1246.9</v>
+        <v>1242.9</v>
       </c>
       <c r="I2" t="n">
         <v>886</v>
@@ -518,10 +518,10 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>75.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="E3" t="n">
-        <v>79.2</v>
+        <v>77.2</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1201.1</v>
+        <v>1197.2</v>
       </c>
       <c r="I3" t="n">
         <v>882.1</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>66.3</v>
+        <v>67.8</v>
       </c>
       <c r="E4" t="n">
-        <v>78.3</v>
+        <v>79.8</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>862.3</v>
+        <v>949.1</v>
       </c>
       <c r="I4" t="n">
-        <v>844.2</v>
+        <v>854.4</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -620,7 +620,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>59.5</v>
+        <v>59.2</v>
       </c>
       <c r="E6" t="n">
         <v>54.5</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>773.2</v>
+        <v>769.4</v>
       </c>
       <c r="I6" t="n">
         <v>847.2</v>
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>51.4</v>
+        <v>52.2</v>
       </c>
       <c r="E7" t="n">
-        <v>56.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>90.2</v>
+        <v>86.2</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>771.2</v>
+        <v>626.6</v>
       </c>
       <c r="I7" t="n">
-        <v>818.3</v>
+        <v>831.9</v>
       </c>
       <c r="J7" t="n">
-        <v>960</v>
+        <v>985</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>49.1</v>
+        <v>51.2</v>
       </c>
       <c r="E8" t="n">
-        <v>63.6</v>
+        <v>52.8</v>
       </c>
       <c r="F8" t="n">
-        <v>79.7</v>
+        <v>90.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>540.4</v>
+        <v>767.9</v>
       </c>
       <c r="I8" t="n">
-        <v>818</v>
+        <v>818.3</v>
       </c>
       <c r="J8" t="n">
-        <v>953</v>
+        <v>960</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +722,7 @@
         <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="E9" t="n">
         <v>42.8</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>736.3</v>
+        <v>736.8</v>
       </c>
       <c r="I9" t="n">
         <v>800.6</v>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>44.2</v>
+        <v>42.8</v>
       </c>
       <c r="E10" t="n">
-        <v>50.7</v>
+        <v>44.8</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,10 +768,10 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>662.8</v>
+        <v>685.1</v>
       </c>
       <c r="I10" t="n">
-        <v>788.7</v>
+        <v>787.2</v>
       </c>
       <c r="J10" t="n">
         <v>928</v>
@@ -799,10 +799,10 @@
         <v>64.7</v>
       </c>
       <c r="G11" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="H11" t="n">
-        <v>400.2</v>
+        <v>400.5</v>
       </c>
       <c r="I11" t="n">
         <v>772.5</v>
@@ -821,25 +821,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>34.1</v>
+        <v>36.6</v>
       </c>
       <c r="E12" t="n">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
       <c r="F12" t="n">
-        <v>67.5</v>
+        <v>71.5</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>477.2</v>
+        <v>548.7</v>
       </c>
       <c r="I12" t="n">
-        <v>770.4</v>
+        <v>780.5</v>
       </c>
       <c r="J12" t="n">
         <v>924</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>25.5</v>
+        <v>24.2</v>
       </c>
       <c r="E14" t="n">
-        <v>12.4</v>
+        <v>10.9</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>357.5</v>
+        <v>363.2</v>
       </c>
       <c r="I14" t="n">
-        <v>723.7</v>
+        <v>720</v>
       </c>
       <c r="J14" t="n">
         <v>832</v>
@@ -1293,7 +1293,9 @@
       <c r="Q5" t="n">
         <v>655</v>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>985</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1457,7 +1459,9 @@
       <c r="Q8" t="n">
         <v>808</v>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>765</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1535,7 +1539,9 @@
       <c r="Q10" t="n">
         <v>730</v>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>923</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1655,7 +1661,9 @@
         <v>860</v>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>988</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1751,7 +1759,9 @@
       <c r="Q15" t="n">
         <v>770</v>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>668</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1942,7 +1952,7 @@
         <v>92.7</v>
       </c>
       <c r="R2" t="n">
-        <v>74.90000000000001</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1998,7 +2008,7 @@
         <v>77.7</v>
       </c>
       <c r="R3" t="n">
-        <v>80.59999999999999</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="4">
@@ -2048,7 +2058,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>84.59999999999999</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="5">
@@ -2095,7 +2105,9 @@
       <c r="Q5" t="n">
         <v>2.6</v>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>86.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2148,7 +2160,7 @@
         <v>90.2</v>
       </c>
       <c r="R6" t="n">
-        <v>56.1</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="7">
@@ -2204,7 +2216,7 @@
         <v>41.6</v>
       </c>
       <c r="R7" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="8">
@@ -2259,7 +2271,9 @@
       <c r="Q8" t="n">
         <v>51.4</v>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2337,7 +2351,9 @@
       <c r="Q10" t="n">
         <v>16.4</v>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>71.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2457,7 +2473,9 @@
         <v>76.5</v>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>86.8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2500,7 +2518,7 @@
         <v>49.9</v>
       </c>
       <c r="R14" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="15">
@@ -2553,7 +2571,9 @@
       <c r="Q15" t="n">
         <v>32.4</v>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>5.7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3043,22 +3063,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>847</v>
+        <v>855.5</v>
       </c>
       <c r="D18" t="n">
-        <v>110</v>
+        <v>118.8</v>
       </c>
       <c r="E18" t="n">
-        <v>892.5</v>
+        <v>921</v>
       </c>
       <c r="F18" t="n">
-        <v>959</v>
+        <v>988</v>
       </c>
       <c r="G18" t="n">
-        <v>677</v>
+        <v>668</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>77.7</v>
+        <v>77.8</v>
       </c>
       <c r="E2" t="n">
         <v>82</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1242.9</v>
+        <v>1245.6</v>
       </c>
       <c r="I2" t="n">
         <v>886</v>
@@ -518,10 +518,10 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>74.8</v>
+        <v>75</v>
       </c>
       <c r="E3" t="n">
-        <v>77.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1197.2</v>
+        <v>1199.6</v>
       </c>
       <c r="I3" t="n">
         <v>882.1</v>
@@ -552,7 +552,7 @@
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>67.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E4" t="n">
         <v>79.8</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>949.1</v>
+        <v>950.8</v>
       </c>
       <c r="I4" t="n">
         <v>854.4</v>
@@ -620,7 +620,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>59.2</v>
+        <v>59.4</v>
       </c>
       <c r="E6" t="n">
         <v>54.5</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>769.4</v>
+        <v>771.6</v>
       </c>
       <c r="I6" t="n">
         <v>847.2</v>
@@ -654,19 +654,19 @@
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="E7" t="n">
         <v>64.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>86.2</v>
+        <v>88</v>
       </c>
       <c r="G7" t="n">
         <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>626.6</v>
+        <v>628.4</v>
       </c>
       <c r="I7" t="n">
         <v>831.9</v>
@@ -688,10 +688,10 @@
         <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
       <c r="E8" t="n">
-        <v>52.8</v>
+        <v>55.8</v>
       </c>
       <c r="F8" t="n">
         <v>90.2</v>
@@ -700,7 +700,7 @@
         <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>767.9</v>
+        <v>770.9</v>
       </c>
       <c r="I8" t="n">
         <v>818.3</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>736.8</v>
+        <v>737.6</v>
       </c>
       <c r="I9" t="n">
         <v>800.6</v>
@@ -756,7 +756,7 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="E10" t="n">
         <v>44.8</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>685.1</v>
+        <v>687.1</v>
       </c>
       <c r="I10" t="n">
         <v>787.2</v>
@@ -790,7 +790,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="E11" t="n">
         <v>51.1</v>
@@ -799,10 +799,10 @@
         <v>64.7</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5</v>
+        <v>13.8</v>
       </c>
       <c r="H11" t="n">
-        <v>400.5</v>
+        <v>401.8</v>
       </c>
       <c r="I11" t="n">
         <v>772.5</v>
@@ -824,19 +824,19 @@
         <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="E12" t="n">
         <v>33.9</v>
       </c>
       <c r="F12" t="n">
-        <v>71.5</v>
+        <v>74.2</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>548.7</v>
+        <v>551.4</v>
       </c>
       <c r="I12" t="n">
         <v>780.5</v>
@@ -892,7 +892,7 @@
         <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="E14" t="n">
         <v>10.9</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>363.2</v>
+        <v>363.9</v>
       </c>
       <c r="I14" t="n">
         <v>720</v>
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>20.7</v>
       </c>
       <c r="F15" t="n">
         <v>57.5</v>
@@ -938,10 +938,10 @@
         <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>142.6</v>
+        <v>163.3</v>
       </c>
       <c r="I15" t="n">
-        <v>724.2</v>
+        <v>728</v>
       </c>
       <c r="J15" t="n">
         <v>832</v>
@@ -1577,7 +1577,9 @@
       <c r="Q11" t="n">
         <v>764</v>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>751</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1952,7 +1954,7 @@
         <v>92.7</v>
       </c>
       <c r="R2" t="n">
-        <v>70.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -2008,7 +2010,7 @@
         <v>77.7</v>
       </c>
       <c r="R3" t="n">
-        <v>76.7</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2058,7 +2060,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>80.8</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5">
@@ -2106,7 +2108,7 @@
         <v>2.6</v>
       </c>
       <c r="R5" t="n">
-        <v>86.2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -2160,7 +2162,7 @@
         <v>90.2</v>
       </c>
       <c r="R6" t="n">
-        <v>52.8</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="7">
@@ -2216,7 +2218,7 @@
         <v>41.6</v>
       </c>
       <c r="R7" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="8">
@@ -2272,7 +2274,7 @@
         <v>51.4</v>
       </c>
       <c r="R8" t="n">
-        <v>22.3</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="9">
@@ -2352,7 +2354,7 @@
         <v>16.4</v>
       </c>
       <c r="R10" t="n">
-        <v>71.5</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="11">
@@ -2389,7 +2391,9 @@
       <c r="Q11" t="n">
         <v>29.6</v>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>20.7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2474,7 +2478,7 @@
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>86.8</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="14">
@@ -2518,7 +2522,7 @@
         <v>49.9</v>
       </c>
       <c r="R14" t="n">
-        <v>12.5</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="15">
@@ -2572,7 +2576,7 @@
         <v>32.4</v>
       </c>
       <c r="R15" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="16">
@@ -3063,16 +3067,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>855.5</v>
+        <v>846.8</v>
       </c>
       <c r="D18" t="n">
-        <v>118.8</v>
+        <v>117.4</v>
       </c>
       <c r="E18" t="n">
-        <v>921</v>
+        <v>892.5</v>
       </c>
       <c r="F18" t="n">
         <v>988</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>42.9</v>
+        <v>43.4</v>
       </c>
       <c r="E10" t="n">
-        <v>44.8</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,10 +768,10 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>687.1</v>
+        <v>737.1</v>
       </c>
       <c r="I10" t="n">
-        <v>787.2</v>
+        <v>778.2</v>
       </c>
       <c r="J10" t="n">
         <v>928</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,6 +1086,11 @@
           <t>9/18/26</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>9/19/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1142,6 +1147,7 @@
       <c r="R2" t="n">
         <v>921</v>
       </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1198,6 +1204,7 @@
       <c r="R3" t="n">
         <v>942</v>
       </c>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1248,6 +1255,7 @@
       <c r="R4" t="n">
         <v>959</v>
       </c>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1296,6 +1304,7 @@
       <c r="R5" t="n">
         <v>985</v>
       </c>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1350,6 +1359,7 @@
       <c r="R6" t="n">
         <v>864</v>
       </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1406,6 +1416,7 @@
       <c r="R7" t="n">
         <v>677</v>
       </c>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1461,6 +1472,9 @@
       </c>
       <c r="R8" t="n">
         <v>765</v>
+      </c>
+      <c r="S8" t="n">
+        <v>635</v>
       </c>
     </row>
     <row r="9">
@@ -1488,6 +1502,7 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1542,6 +1557,7 @@
       <c r="R10" t="n">
         <v>923</v>
       </c>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1580,6 +1596,7 @@
       <c r="R11" t="n">
         <v>751</v>
       </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1614,6 +1631,7 @@
         <v>748</v>
       </c>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1666,6 +1684,7 @@
       <c r="R13" t="n">
         <v>988</v>
       </c>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1710,6 +1729,7 @@
       <c r="R14" t="n">
         <v>719</v>
       </c>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1764,6 +1784,7 @@
       <c r="R15" t="n">
         <v>668</v>
       </c>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1794,6 +1815,7 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1806,7 +1828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1900,6 +1922,11 @@
           <t>9/18/26</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>9/19/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1956,6 +1983,7 @@
       <c r="R2" t="n">
         <v>73.59999999999999</v>
       </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2012,6 +2040,7 @@
       <c r="R3" t="n">
         <v>79.09999999999999</v>
       </c>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2062,6 +2091,7 @@
       <c r="R4" t="n">
         <v>83</v>
       </c>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2110,6 +2140,7 @@
       <c r="R5" t="n">
         <v>88</v>
       </c>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2164,6 +2195,7 @@
       <c r="R6" t="n">
         <v>55.8</v>
       </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2220,6 +2252,7 @@
       <c r="R7" t="n">
         <v>7.4</v>
       </c>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2275,6 +2308,9 @@
       </c>
       <c r="R8" t="n">
         <v>24.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -2302,6 +2338,7 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2356,6 +2393,7 @@
       <c r="R10" t="n">
         <v>74.2</v>
       </c>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2394,6 +2432,7 @@
       <c r="R11" t="n">
         <v>20.7</v>
       </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2428,6 +2467,7 @@
         <v>22.9</v>
       </c>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2480,6 +2520,7 @@
       <c r="R13" t="n">
         <v>88.5</v>
       </c>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2524,6 +2565,7 @@
       <c r="R14" t="n">
         <v>13.8</v>
       </c>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2578,6 +2620,7 @@
       <c r="R15" t="n">
         <v>6.4</v>
       </c>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2608,6 +2651,7 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2620,7 +2664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3085,6 +3129,31 @@
         <v>668</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>9/19/26</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>635</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>635</v>
+      </c>
+      <c r="F19" t="n">
+        <v>635</v>
+      </c>
+      <c r="G19" t="n">
+        <v>635</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>46.1</v>
+        <v>48.3</v>
       </c>
       <c r="E9" t="n">
-        <v>42.8</v>
+        <v>43.9</v>
       </c>
       <c r="F9" t="n">
         <v>89.09999999999999</v>
@@ -734,10 +734,10 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>737.6</v>
+        <v>821.7</v>
       </c>
       <c r="I9" t="n">
-        <v>800.6</v>
+        <v>795.4</v>
       </c>
       <c r="J9" t="n">
         <v>975</v>
@@ -756,10 +756,10 @@
         <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>43.4</v>
+        <v>41.4</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>38.9</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>737.1</v>
+        <v>703</v>
       </c>
       <c r="I10" t="n">
         <v>778.2</v>
@@ -1416,7 +1416,9 @@
       <c r="R7" t="n">
         <v>677</v>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>712</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2252,7 +2254,9 @@
       <c r="R7" t="n">
         <v>7.4</v>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2310,7 +2314,7 @@
         <v>24.3</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="9">
@@ -3136,19 +3140,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>635</v>
+        <v>673.5</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="E19" t="n">
-        <v>635</v>
+        <v>673.5</v>
       </c>
       <c r="F19" t="n">
-        <v>635</v>
+        <v>712</v>
       </c>
       <c r="G19" t="n">
         <v>635</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>77.8</v>
+        <v>78.3</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>84.3</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,10 +496,10 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1245.6</v>
+        <v>1331.9</v>
       </c>
       <c r="I2" t="n">
-        <v>886</v>
+        <v>888.5</v>
       </c>
       <c r="J2" t="n">
         <v>991</v>
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>59.4</v>
+        <v>61.6</v>
       </c>
       <c r="E6" t="n">
-        <v>54.5</v>
+        <v>61.9</v>
       </c>
       <c r="F6" t="n">
         <v>93.7</v>
@@ -632,10 +632,10 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>771.6</v>
+        <v>862</v>
       </c>
       <c r="I6" t="n">
-        <v>847.2</v>
+        <v>855.1</v>
       </c>
       <c r="J6" t="n">
         <v>959</v>
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>51.4</v>
+        <v>49.3</v>
       </c>
       <c r="E8" t="n">
-        <v>55.8</v>
+        <v>52.9</v>
       </c>
       <c r="F8" t="n">
         <v>90.2</v>
@@ -700,10 +700,10 @@
         <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>770.9</v>
+        <v>788.1</v>
       </c>
       <c r="I8" t="n">
-        <v>818.3</v>
+        <v>807.3</v>
       </c>
       <c r="J8" t="n">
         <v>960</v>
@@ -722,10 +722,10 @@
         <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>48.3</v>
+        <v>45.3</v>
       </c>
       <c r="E9" t="n">
-        <v>43.9</v>
+        <v>41.6</v>
       </c>
       <c r="F9" t="n">
         <v>89.09999999999999</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>821.7</v>
+        <v>770.1</v>
       </c>
       <c r="I9" t="n">
         <v>795.4</v>
@@ -756,7 +756,7 @@
         <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="E10" t="n">
         <v>38.9</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>703</v>
+        <v>702.9</v>
       </c>
       <c r="I10" t="n">
         <v>778.2</v>
@@ -1147,7 +1147,9 @@
       <c r="R2" t="n">
         <v>921</v>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>929</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1255,7 +1257,9 @@
       <c r="R4" t="n">
         <v>959</v>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>958</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1359,7 +1363,9 @@
       <c r="R6" t="n">
         <v>864</v>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>643</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1985,7 +1991,9 @@
       <c r="R2" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>86.3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2093,7 +2101,9 @@
       <c r="R4" t="n">
         <v>83</v>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>90.40000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2197,7 +2207,9 @@
       <c r="R6" t="n">
         <v>55.8</v>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>17.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2255,7 +2267,7 @@
         <v>7.4</v>
       </c>
       <c r="S7" t="n">
-        <v>84.09999999999999</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="8">
@@ -2314,7 +2326,7 @@
         <v>24.3</v>
       </c>
       <c r="S8" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="9">
@@ -3140,19 +3152,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>673.5</v>
+        <v>775.4</v>
       </c>
       <c r="D19" t="n">
-        <v>38.5</v>
+        <v>140.1</v>
       </c>
       <c r="E19" t="n">
-        <v>673.5</v>
+        <v>712</v>
       </c>
       <c r="F19" t="n">
-        <v>712</v>
+        <v>958</v>
       </c>
       <c r="G19" t="n">
         <v>635</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>78.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>84.3</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1331.9</v>
+        <v>1336.8</v>
       </c>
       <c r="I2" t="n">
         <v>888.5</v>
@@ -620,19 +620,19 @@
         <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>61.6</v>
+        <v>61.9</v>
       </c>
       <c r="E6" t="n">
         <v>61.9</v>
       </c>
       <c r="F6" t="n">
-        <v>93.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="I6" t="n">
         <v>855.1</v>
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>52.4</v>
+        <v>52.7</v>
       </c>
       <c r="E7" t="n">
-        <v>64.59999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="F7" t="n">
         <v>88</v>
@@ -666,10 +666,10 @@
         <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>628.4</v>
+        <v>684.6</v>
       </c>
       <c r="I7" t="n">
-        <v>831.9</v>
+        <v>827.9</v>
       </c>
       <c r="J7" t="n">
         <v>985</v>
@@ -722,7 +722,7 @@
         <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="E9" t="n">
         <v>41.6</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>770.1</v>
+        <v>772.4</v>
       </c>
       <c r="I9" t="n">
         <v>795.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>702.9</v>
+        <v>702.7</v>
       </c>
       <c r="I10" t="n">
         <v>778.2</v>
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>40.2</v>
+        <v>38.6</v>
       </c>
       <c r="E11" t="n">
-        <v>51.1</v>
+        <v>49.9</v>
       </c>
       <c r="F11" t="n">
         <v>64.7</v>
@@ -802,10 +802,10 @@
         <v>13.8</v>
       </c>
       <c r="H11" t="n">
-        <v>401.8</v>
+        <v>424.6</v>
       </c>
       <c r="I11" t="n">
-        <v>772.5</v>
+        <v>763</v>
       </c>
       <c r="J11" t="n">
         <v>916</v>
@@ -1308,7 +1308,9 @@
       <c r="R5" t="n">
         <v>985</v>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1737,7 +1739,9 @@
       <c r="R14" t="n">
         <v>719</v>
       </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>668</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1992,7 +1996,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>86.3</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="3">
@@ -2102,7 +2106,7 @@
         <v>83</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2152,7 +2156,9 @@
       <c r="R5" t="n">
         <v>88</v>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>56.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2267,7 +2273,7 @@
         <v>7.4</v>
       </c>
       <c r="S7" t="n">
-        <v>32.5</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="8">
@@ -2326,7 +2332,7 @@
         <v>24.3</v>
       </c>
       <c r="S8" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="9">
@@ -2581,7 +2587,9 @@
       <c r="R14" t="n">
         <v>13.8</v>
       </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3152,13 +3160,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>775.4</v>
+        <v>760.7</v>
       </c>
       <c r="D19" t="n">
-        <v>140.1</v>
+        <v>124.4</v>
       </c>
       <c r="E19" t="n">
         <v>712</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="E2" t="n">
         <v>84.3</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1336.8</v>
+        <v>1337.3</v>
       </c>
       <c r="I2" t="n">
         <v>888.5</v>
@@ -626,13 +626,13 @@
         <v>61.9</v>
       </c>
       <c r="F6" t="n">
-        <v>94.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>866</v>
+        <v>866.5</v>
       </c>
       <c r="I6" t="n">
         <v>855.1</v>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>52.7</v>
+        <v>52.5</v>
       </c>
       <c r="E7" t="n">
         <v>63.6</v>
@@ -666,7 +666,7 @@
         <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>684.6</v>
+        <v>683</v>
       </c>
       <c r="I7" t="n">
         <v>827.9</v>
@@ -688,7 +688,7 @@
         <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="E8" t="n">
         <v>52.9</v>
@@ -700,7 +700,7 @@
         <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>788.1</v>
+        <v>785.5</v>
       </c>
       <c r="I8" t="n">
         <v>807.3</v>
@@ -722,7 +722,7 @@
         <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="E9" t="n">
         <v>41.6</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>772.4</v>
+        <v>769.7</v>
       </c>
       <c r="I9" t="n">
         <v>795.4</v>
@@ -756,7 +756,7 @@
         <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="E10" t="n">
         <v>38.9</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>702.7</v>
+        <v>700.2</v>
       </c>
       <c r="I10" t="n">
         <v>778.2</v>
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="E11" t="n">
-        <v>49.9</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n">
-        <v>64.7</v>
+        <v>74.2</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>424.6</v>
+        <v>614.9</v>
       </c>
       <c r="I11" t="n">
-        <v>763</v>
+        <v>782.2</v>
       </c>
       <c r="J11" t="n">
-        <v>916</v>
+        <v>924</v>
       </c>
     </row>
     <row r="12">
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>36.8</v>
+        <v>38.4</v>
       </c>
       <c r="E12" t="n">
-        <v>33.9</v>
+        <v>49.9</v>
       </c>
       <c r="F12" t="n">
-        <v>74.2</v>
+        <v>64.7</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>13.8</v>
       </c>
       <c r="H12" t="n">
-        <v>551.4</v>
+        <v>421.9</v>
       </c>
       <c r="I12" t="n">
-        <v>780.5</v>
+        <v>763</v>
       </c>
       <c r="J12" t="n">
-        <v>924</v>
+        <v>916</v>
       </c>
     </row>
     <row r="13">
@@ -1567,7 +1567,9 @@
       <c r="R10" t="n">
         <v>923</v>
       </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>807</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1996,7 +1998,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>91.2</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="3">
@@ -2106,7 +2108,7 @@
         <v>83</v>
       </c>
       <c r="S4" t="n">
-        <v>94.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2157,7 +2159,7 @@
         <v>88</v>
       </c>
       <c r="S5" t="n">
-        <v>56.2</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="6">
@@ -2214,7 +2216,7 @@
         <v>55.8</v>
       </c>
       <c r="S6" t="n">
-        <v>17.2</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="7">
@@ -2273,7 +2275,7 @@
         <v>7.4</v>
       </c>
       <c r="S7" t="n">
-        <v>34.8</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="8">
@@ -2332,7 +2334,7 @@
         <v>24.3</v>
       </c>
       <c r="S8" t="n">
-        <v>15.6</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="9">
@@ -2415,7 +2417,9 @@
       <c r="R10" t="n">
         <v>74.2</v>
       </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>63.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2588,7 +2592,7 @@
         <v>13.8</v>
       </c>
       <c r="S14" t="n">
-        <v>22.8</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="15">
@@ -3160,16 +3164,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>760.7</v>
+        <v>766.5</v>
       </c>
       <c r="D19" t="n">
-        <v>124.4</v>
+        <v>117.3</v>
       </c>
       <c r="E19" t="n">
-        <v>712</v>
+        <v>746</v>
       </c>
       <c r="F19" t="n">
         <v>958</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="E2" t="n">
         <v>84.3</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1337.3</v>
+        <v>1339</v>
       </c>
       <c r="I2" t="n">
         <v>888.5</v>
@@ -620,19 +620,19 @@
         <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>61.9</v>
+        <v>62</v>
       </c>
       <c r="E6" t="n">
         <v>61.9</v>
       </c>
       <c r="F6" t="n">
-        <v>94.90000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>866.5</v>
+        <v>867.7</v>
       </c>
       <c r="I6" t="n">
         <v>855.1</v>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>52.5</v>
+        <v>52.8</v>
       </c>
       <c r="E7" t="n">
         <v>63.6</v>
@@ -666,7 +666,7 @@
         <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>683</v>
+        <v>686.8</v>
       </c>
       <c r="I7" t="n">
         <v>827.9</v>
@@ -688,7 +688,7 @@
         <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E8" t="n">
         <v>52.9</v>
@@ -700,7 +700,7 @@
         <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>785.5</v>
+        <v>787.3</v>
       </c>
       <c r="I8" t="n">
         <v>807.3</v>
@@ -722,7 +722,7 @@
         <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>45.3</v>
+        <v>45.5</v>
       </c>
       <c r="E9" t="n">
         <v>41.6</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>769.7</v>
+        <v>772.8</v>
       </c>
       <c r="I9" t="n">
         <v>795.4</v>
@@ -756,7 +756,7 @@
         <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="E10" t="n">
         <v>38.9</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>700.2</v>
+        <v>701.8</v>
       </c>
       <c r="I10" t="n">
         <v>778.2</v>
@@ -790,7 +790,7 @@
         <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>38.4</v>
+        <v>38.7</v>
       </c>
       <c r="E11" t="n">
         <v>37</v>
@@ -802,7 +802,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>614.9</v>
+        <v>618.7</v>
       </c>
       <c r="I11" t="n">
         <v>782.2</v>
@@ -824,7 +824,7 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="E12" t="n">
         <v>49.9</v>
@@ -836,7 +836,7 @@
         <v>13.8</v>
       </c>
       <c r="H12" t="n">
-        <v>421.9</v>
+        <v>424.1</v>
       </c>
       <c r="I12" t="n">
         <v>763</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="E14" t="n">
-        <v>10.9</v>
+        <v>12.4</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>363.9</v>
+        <v>386.2</v>
       </c>
       <c r="I14" t="n">
-        <v>720</v>
+        <v>716.8</v>
       </c>
       <c r="J14" t="n">
         <v>832</v>
@@ -1798,7 +1798,9 @@
       <c r="R15" t="n">
         <v>668</v>
       </c>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>668</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1998,7 +2000,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>91.7</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2108,7 +2110,7 @@
         <v>83</v>
       </c>
       <c r="S4" t="n">
-        <v>94.90000000000001</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2159,7 +2161,7 @@
         <v>88</v>
       </c>
       <c r="S5" t="n">
-        <v>54.6</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="6">
@@ -2216,7 +2218,7 @@
         <v>55.8</v>
       </c>
       <c r="S6" t="n">
-        <v>14.6</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="7">
@@ -2275,7 +2277,7 @@
         <v>7.4</v>
       </c>
       <c r="S7" t="n">
-        <v>32.1</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="8">
@@ -2334,7 +2336,7 @@
         <v>24.3</v>
       </c>
       <c r="S8" t="n">
-        <v>13.1</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="9">
@@ -2418,7 +2420,7 @@
         <v>74.2</v>
       </c>
       <c r="S10" t="n">
-        <v>63.5</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="11">
@@ -2592,7 +2594,7 @@
         <v>13.8</v>
       </c>
       <c r="S14" t="n">
-        <v>20.1</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="15">
@@ -2648,7 +2650,9 @@
       <c r="R15" t="n">
         <v>6.4</v>
       </c>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3164,16 +3168,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>766.5</v>
+        <v>755.6</v>
       </c>
       <c r="D19" t="n">
-        <v>117.3</v>
+        <v>114.9</v>
       </c>
       <c r="E19" t="n">
-        <v>746</v>
+        <v>712</v>
       </c>
       <c r="F19" t="n">
         <v>958</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>61.2</v>
       </c>
       <c r="E6" t="n">
-        <v>61.9</v>
+        <v>54.5</v>
       </c>
       <c r="F6" t="n">
         <v>96.09999999999999</v>
@@ -632,10 +632,10 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>867.7</v>
+        <v>917.7</v>
       </c>
       <c r="I6" t="n">
-        <v>855.1</v>
+        <v>861.6</v>
       </c>
       <c r="J6" t="n">
         <v>959</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1091,6 +1091,11 @@
           <t>9/19/26</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>9/20/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1150,6 +1155,7 @@
       <c r="S2" t="n">
         <v>929</v>
       </c>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1207,6 +1213,7 @@
         <v>942</v>
       </c>
       <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1259,6 +1266,9 @@
       </c>
       <c r="S4" t="n">
         <v>958</v>
+      </c>
+      <c r="T4" t="n">
+        <v>952</v>
       </c>
     </row>
     <row r="5">
@@ -1311,6 +1321,7 @@
       <c r="S5" t="n">
         <v>780</v>
       </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1368,6 +1379,7 @@
       <c r="S6" t="n">
         <v>643</v>
       </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1427,6 +1439,7 @@
       <c r="S7" t="n">
         <v>712</v>
       </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1486,6 +1499,7 @@
       <c r="S8" t="n">
         <v>635</v>
       </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1513,6 +1527,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1570,6 +1585,7 @@
       <c r="S10" t="n">
         <v>807</v>
       </c>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1609,6 +1625,7 @@
         <v>751</v>
       </c>
       <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1644,6 +1661,7 @@
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1697,6 +1715,7 @@
         <v>988</v>
       </c>
       <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1744,6 +1763,7 @@
       <c r="S14" t="n">
         <v>668</v>
       </c>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1801,6 +1821,7 @@
       <c r="S15" t="n">
         <v>668</v>
       </c>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1832,6 +1853,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1844,7 +1866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1943,6 +1965,11 @@
           <t>9/19/26</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>9/20/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2002,6 +2029,7 @@
       <c r="S2" t="n">
         <v>93.40000000000001</v>
       </c>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2059,6 +2087,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2111,6 +2140,9 @@
       </c>
       <c r="S4" t="n">
         <v>96.09999999999999</v>
+      </c>
+      <c r="T4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -2163,6 +2195,7 @@
       <c r="S5" t="n">
         <v>58.4</v>
       </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2220,6 +2253,7 @@
       <c r="S6" t="n">
         <v>16.4</v>
       </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2279,6 +2313,7 @@
       <c r="S7" t="n">
         <v>35.2</v>
       </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2338,6 +2373,7 @@
       <c r="S8" t="n">
         <v>14.7</v>
       </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2365,6 +2401,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2422,6 +2459,7 @@
       <c r="S10" t="n">
         <v>67.3</v>
       </c>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2461,6 +2499,7 @@
         <v>20.7</v>
       </c>
       <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2496,6 +2535,7 @@
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2549,6 +2589,7 @@
         <v>88.5</v>
       </c>
       <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2596,6 +2637,7 @@
       <c r="S14" t="n">
         <v>22.3</v>
       </c>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2653,6 +2695,7 @@
       <c r="S15" t="n">
         <v>22.3</v>
       </c>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2684,6 +2727,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2696,7 +2740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3186,6 +3230,31 @@
         <v>635</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>9/20/26</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>952</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>952</v>
+      </c>
+      <c r="F20" t="n">
+        <v>952</v>
+      </c>
+      <c r="G20" t="n">
+        <v>952</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -620,7 +620,7 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>61.2</v>
+        <v>58.9</v>
       </c>
       <c r="E6" t="n">
         <v>54.5</v>
@@ -629,10 +629,10 @@
         <v>96.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>22.2</v>
+        <v>15.9</v>
       </c>
       <c r="H6" t="n">
-        <v>917.7</v>
+        <v>883.6</v>
       </c>
       <c r="I6" t="n">
         <v>861.6</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>45.5</v>
+        <v>47.6</v>
       </c>
       <c r="E9" t="n">
-        <v>41.6</v>
+        <v>42.8</v>
       </c>
       <c r="F9" t="n">
         <v>89.09999999999999</v>
@@ -734,10 +734,10 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>772.8</v>
+        <v>856.9</v>
       </c>
       <c r="I9" t="n">
-        <v>795.4</v>
+        <v>804.6</v>
       </c>
       <c r="J9" t="n">
         <v>975</v>
@@ -1439,7 +1439,9 @@
       <c r="S7" t="n">
         <v>712</v>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>960</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2142,7 +2144,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="5">
@@ -2313,7 +2315,9 @@
       <c r="S7" t="n">
         <v>35.2</v>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3237,19 +3241,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="F20" t="n">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="G20" t="n">
         <v>952</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -620,19 +620,19 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>58.9</v>
+        <v>62.9</v>
       </c>
       <c r="E6" t="n">
-        <v>54.5</v>
+        <v>69.3</v>
       </c>
       <c r="F6" t="n">
         <v>96.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>15.9</v>
+        <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>883.6</v>
+        <v>942.8</v>
       </c>
       <c r="I6" t="n">
         <v>861.6</v>
@@ -722,7 +722,7 @@
         <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>47.6</v>
+        <v>47.2</v>
       </c>
       <c r="E9" t="n">
         <v>42.8</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>856.9</v>
+        <v>849.7</v>
       </c>
       <c r="I9" t="n">
         <v>804.6</v>
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="E11" t="n">
-        <v>37</v>
+        <v>49.9</v>
       </c>
       <c r="F11" t="n">
-        <v>74.2</v>
+        <v>64.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>13.8</v>
       </c>
       <c r="H11" t="n">
-        <v>618.7</v>
+        <v>424.1</v>
       </c>
       <c r="I11" t="n">
-        <v>782.2</v>
+        <v>763</v>
       </c>
       <c r="J11" t="n">
-        <v>924</v>
+        <v>916</v>
       </c>
     </row>
     <row r="12">
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>38.6</v>
+        <v>36.9</v>
       </c>
       <c r="E12" t="n">
-        <v>49.9</v>
+        <v>33.9</v>
       </c>
       <c r="F12" t="n">
-        <v>64.7</v>
+        <v>74.2</v>
       </c>
       <c r="G12" t="n">
-        <v>13.8</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>424.1</v>
+        <v>626.6</v>
       </c>
       <c r="I12" t="n">
-        <v>763</v>
+        <v>775.7</v>
       </c>
       <c r="J12" t="n">
-        <v>916</v>
+        <v>924</v>
       </c>
     </row>
     <row r="13">
@@ -1587,7 +1587,9 @@
       <c r="S10" t="n">
         <v>807</v>
       </c>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>672</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2144,7 +2146,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>15.9</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2316,7 +2318,7 @@
         <v>35.2</v>
       </c>
       <c r="T7" t="n">
-        <v>84.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2463,7 +2465,9 @@
       <c r="S10" t="n">
         <v>67.3</v>
       </c>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3241,22 +3245,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>956</v>
+        <v>861.3</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>133.9</v>
       </c>
       <c r="E20" t="n">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="F20" t="n">
         <v>960</v>
       </c>
       <c r="G20" t="n">
-        <v>952</v>
+        <v>672</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>78.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1199.6</v>
+        <v>1277.1</v>
       </c>
       <c r="I3" t="n">
-        <v>882.1</v>
+        <v>888.5</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -620,10 +620,10 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>62.9</v>
+        <v>62.3</v>
       </c>
       <c r="E6" t="n">
-        <v>69.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>96.09999999999999</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>942.8</v>
+        <v>935.1</v>
       </c>
       <c r="I6" t="n">
         <v>861.6</v>
@@ -722,7 +722,7 @@
         <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>47.2</v>
+        <v>46.8</v>
       </c>
       <c r="E9" t="n">
         <v>42.8</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>849.7</v>
+        <v>842.4</v>
       </c>
       <c r="I9" t="n">
         <v>804.6</v>
@@ -824,7 +824,7 @@
         <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>36.9</v>
+        <v>36.6</v>
       </c>
       <c r="E12" t="n">
         <v>33.9</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>626.6</v>
+        <v>623</v>
       </c>
       <c r="I12" t="n">
         <v>775.7</v>
@@ -1213,7 +1213,9 @@
         <v>942</v>
       </c>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>991</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2091,7 +2093,9 @@
         <v>79.09999999999999</v>
       </c>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>77.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2146,7 +2150,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>75.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2318,7 +2322,7 @@
         <v>35.2</v>
       </c>
       <c r="T7" t="n">
-        <v>76.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2466,7 +2470,7 @@
         <v>67.3</v>
       </c>
       <c r="T10" t="n">
-        <v>7.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="11">
@@ -3245,19 +3249,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>861.3</v>
+        <v>893.8</v>
       </c>
       <c r="D20" t="n">
-        <v>133.9</v>
+        <v>128.9</v>
       </c>
       <c r="E20" t="n">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="F20" t="n">
-        <v>960</v>
+        <v>991</v>
       </c>
       <c r="G20" t="n">
         <v>672</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -518,10 +518,10 @@
         <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>75.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="E3" t="n">
-        <v>77.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1277.1</v>
+        <v>1283.2</v>
       </c>
       <c r="I3" t="n">
         <v>888.5</v>
@@ -620,10 +620,10 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>62.3</v>
+        <v>62.9</v>
       </c>
       <c r="E6" t="n">
-        <v>67.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="F6" t="n">
         <v>96.09999999999999</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>935.1</v>
+        <v>943.6</v>
       </c>
       <c r="I6" t="n">
         <v>861.6</v>
@@ -722,7 +722,7 @@
         <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>46.8</v>
+        <v>47.2</v>
       </c>
       <c r="E9" t="n">
         <v>42.8</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>842.4</v>
+        <v>850.4</v>
       </c>
       <c r="I9" t="n">
         <v>804.6</v>
@@ -824,7 +824,7 @@
         <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>36.6</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
         <v>33.9</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>623</v>
+        <v>629.1</v>
       </c>
       <c r="I12" t="n">
         <v>775.7</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14" t="n">
-        <v>24.1</v>
+        <v>23.4</v>
       </c>
       <c r="E14" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>386.2</v>
+        <v>398.2</v>
       </c>
       <c r="I14" t="n">
-        <v>716.8</v>
+        <v>714.8</v>
       </c>
       <c r="J14" t="n">
         <v>832</v>
@@ -1827,7 +1827,9 @@
       <c r="S15" t="n">
         <v>668</v>
       </c>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>684</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2094,7 +2096,7 @@
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>77.5</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2150,7 +2152,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>67.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2322,7 +2324,7 @@
         <v>35.2</v>
       </c>
       <c r="T7" t="n">
-        <v>69.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2470,7 +2472,7 @@
         <v>67.3</v>
       </c>
       <c r="T10" t="n">
-        <v>4.3</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="11">
@@ -2707,7 +2709,9 @@
       <c r="S15" t="n">
         <v>22.3</v>
       </c>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3249,16 +3253,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>893.8</v>
+        <v>851.8</v>
       </c>
       <c r="D20" t="n">
-        <v>128.9</v>
+        <v>142.6</v>
       </c>
       <c r="E20" t="n">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="F20" t="n">
         <v>991</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -518,7 +518,7 @@
         <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>75.5</v>
+        <v>75.8</v>
       </c>
       <c r="E3" t="n">
         <v>79.09999999999999</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1283.2</v>
+        <v>1288.1</v>
       </c>
       <c r="I3" t="n">
         <v>888.5</v>
@@ -620,7 +620,7 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>62.9</v>
+        <v>63.3</v>
       </c>
       <c r="E6" t="n">
         <v>69.3</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>943.6</v>
+        <v>948.8</v>
       </c>
       <c r="I6" t="n">
         <v>861.6</v>
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E8" t="n">
-        <v>52.9</v>
+        <v>51.6</v>
       </c>
       <c r="F8" t="n">
         <v>90.2</v>
@@ -700,10 +700,10 @@
         <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>787.3</v>
+        <v>838.9</v>
       </c>
       <c r="I8" t="n">
-        <v>807.3</v>
+        <v>809.8</v>
       </c>
       <c r="J8" t="n">
         <v>960</v>
@@ -722,7 +722,7 @@
         <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>47.2</v>
+        <v>47.5</v>
       </c>
       <c r="E9" t="n">
         <v>42.8</v>
@@ -734,7 +734,7 @@
         <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>850.4</v>
+        <v>855.6</v>
       </c>
       <c r="I9" t="n">
         <v>804.6</v>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="E10" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,10 +768,10 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>701.8</v>
+        <v>739.2</v>
       </c>
       <c r="I10" t="n">
-        <v>778.2</v>
+        <v>779.8</v>
       </c>
       <c r="J10" t="n">
         <v>928</v>
@@ -824,7 +824,7 @@
         <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="E12" t="n">
         <v>33.9</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>629.1</v>
+        <v>626.4</v>
       </c>
       <c r="I12" t="n">
         <v>775.7</v>
@@ -892,10 +892,10 @@
         <v>17</v>
       </c>
       <c r="D14" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>10.9</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>398.2</v>
+        <v>395.5</v>
       </c>
       <c r="I14" t="n">
         <v>714.8</v>
@@ -1381,7 +1381,9 @@
       <c r="S6" t="n">
         <v>643</v>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>850</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1503,7 +1505,9 @@
       <c r="S8" t="n">
         <v>635</v>
       </c>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>806</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2096,7 +2100,7 @@
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>83.59999999999999</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="4">
@@ -2152,7 +2156,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>75.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2263,7 +2267,9 @@
       <c r="S6" t="n">
         <v>16.4</v>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>51.6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2324,7 +2330,7 @@
         <v>35.2</v>
       </c>
       <c r="T7" t="n">
-        <v>77.59999999999999</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="8">
@@ -2385,7 +2391,9 @@
       <c r="S8" t="n">
         <v>14.7</v>
       </c>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>37.4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2472,7 +2480,7 @@
         <v>67.3</v>
       </c>
       <c r="T10" t="n">
-        <v>10.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="11">
@@ -2710,7 +2718,7 @@
         <v>22.3</v>
       </c>
       <c r="T15" t="n">
-        <v>12</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3253,16 +3261,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>851.8</v>
+        <v>845</v>
       </c>
       <c r="D20" t="n">
-        <v>142.6</v>
+        <v>121.5</v>
       </c>
       <c r="E20" t="n">
-        <v>952</v>
+        <v>850</v>
       </c>
       <c r="F20" t="n">
         <v>991</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>63.3</v>
+        <v>62.4</v>
       </c>
       <c r="E6" t="n">
-        <v>69.3</v>
+        <v>61.9</v>
       </c>
       <c r="F6" t="n">
         <v>96.09999999999999</v>
@@ -632,10 +632,10 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>948.8</v>
+        <v>998.8</v>
       </c>
       <c r="I6" t="n">
-        <v>861.6</v>
+        <v>864.8</v>
       </c>
       <c r="J6" t="n">
         <v>959</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1096,6 +1096,11 @@
           <t>9/20/26</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>9/21/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1156,6 +1161,7 @@
         <v>929</v>
       </c>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1216,6 +1222,7 @@
       <c r="T3" t="n">
         <v>991</v>
       </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1271,6 +1278,9 @@
       </c>
       <c r="T4" t="n">
         <v>952</v>
+      </c>
+      <c r="U4" t="n">
+        <v>912</v>
       </c>
     </row>
     <row r="5">
@@ -1324,6 +1334,7 @@
         <v>780</v>
       </c>
       <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1384,6 +1395,7 @@
       <c r="T6" t="n">
         <v>850</v>
       </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1446,6 +1458,7 @@
       <c r="T7" t="n">
         <v>960</v>
       </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1508,6 +1521,7 @@
       <c r="T8" t="n">
         <v>806</v>
       </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1536,6 +1550,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1596,6 +1611,7 @@
       <c r="T10" t="n">
         <v>672</v>
       </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1636,6 +1652,7 @@
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1672,6 +1689,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1726,6 +1744,7 @@
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1774,6 +1793,7 @@
         <v>668</v>
       </c>
       <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1834,6 +1854,7 @@
       <c r="T15" t="n">
         <v>684</v>
       </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1866,6 +1887,7 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1878,7 +1900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1982,6 +2004,11 @@
           <t>9/20/26</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>9/21/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2042,6 +2069,7 @@
         <v>93.40000000000001</v>
       </c>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2102,6 +2130,7 @@
       <c r="T3" t="n">
         <v>88.5</v>
       </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2157,6 +2186,9 @@
       </c>
       <c r="T4" t="n">
         <v>81.09999999999999</v>
+      </c>
+      <c r="U4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -2210,6 +2242,7 @@
         <v>58.4</v>
       </c>
       <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2270,6 +2303,7 @@
       <c r="T6" t="n">
         <v>51.6</v>
       </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2332,6 +2366,7 @@
       <c r="T7" t="n">
         <v>82.8</v>
       </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2394,6 +2429,7 @@
       <c r="T8" t="n">
         <v>37.4</v>
       </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2422,6 +2458,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2482,6 +2519,7 @@
       <c r="T10" t="n">
         <v>7.7</v>
       </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2522,6 +2560,7 @@
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2558,6 +2597,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2612,6 +2652,7 @@
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2660,6 +2701,7 @@
         <v>22.3</v>
       </c>
       <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2720,6 +2762,7 @@
       <c r="T15" t="n">
         <v>9.300000000000001</v>
       </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2752,6 +2795,7 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2764,7 +2808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3279,6 +3323,31 @@
         <v>672</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>9/21/26</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>912</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>912</v>
+      </c>
+      <c r="F21" t="n">
+        <v>912</v>
+      </c>
+      <c r="G21" t="n">
+        <v>912</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -620,7 +620,7 @@
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>62.4</v>
+        <v>60.3</v>
       </c>
       <c r="E6" t="n">
         <v>61.9</v>
@@ -629,10 +629,10 @@
         <v>96.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>22.2</v>
+        <v>15.9</v>
       </c>
       <c r="H6" t="n">
-        <v>998.8</v>
+        <v>964.7</v>
       </c>
       <c r="I6" t="n">
         <v>864.8</v>
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="E8" t="n">
-        <v>51.6</v>
+        <v>43.9</v>
       </c>
       <c r="F8" t="n">
-        <v>90.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>838.9</v>
+        <v>939.7</v>
       </c>
       <c r="I8" t="n">
-        <v>809.8</v>
+        <v>813.6</v>
       </c>
       <c r="J8" t="n">
-        <v>960</v>
+        <v>976</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>47.5</v>
+        <v>49.3</v>
       </c>
       <c r="E9" t="n">
-        <v>42.8</v>
+        <v>51.6</v>
       </c>
       <c r="F9" t="n">
-        <v>89.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>855.6</v>
+        <v>838.9</v>
       </c>
       <c r="I9" t="n">
-        <v>804.6</v>
+        <v>809.8</v>
       </c>
       <c r="J9" t="n">
-        <v>975</v>
+        <v>960</v>
       </c>
     </row>
     <row r="10">
@@ -1458,7 +1458,9 @@
       <c r="T7" t="n">
         <v>960</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>976</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2188,7 +2190,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>50</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="5">
@@ -2366,7 +2368,9 @@
       <c r="T7" t="n">
         <v>82.8</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3330,19 +3334,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>912</v>
+        <v>944</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>912</v>
+        <v>944</v>
       </c>
       <c r="F21" t="n">
-        <v>912</v>
+        <v>976</v>
       </c>
       <c r="G21" t="n">
         <v>912</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -620,19 +620,19 @@
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>60.3</v>
+        <v>63.1</v>
       </c>
       <c r="E6" t="n">
-        <v>61.9</v>
+        <v>64.8</v>
       </c>
       <c r="F6" t="n">
         <v>96.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>15.9</v>
+        <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>964.7</v>
+        <v>1009</v>
       </c>
       <c r="I6" t="n">
         <v>864.8</v>
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>52.8</v>
+        <v>49.7</v>
       </c>
       <c r="E7" t="n">
-        <v>63.6</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
         <v>88</v>
@@ -666,10 +666,10 @@
         <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>686.8</v>
+        <v>695.9</v>
       </c>
       <c r="I7" t="n">
-        <v>827.9</v>
+        <v>825</v>
       </c>
       <c r="J7" t="n">
         <v>985</v>
@@ -688,7 +688,7 @@
         <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E8" t="n">
         <v>43.9</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>939.7</v>
+        <v>941.5</v>
       </c>
       <c r="I8" t="n">
         <v>813.6</v>
@@ -1334,7 +1334,9 @@
         <v>780</v>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>787</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2190,7 +2192,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>15.9</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="5">
@@ -2244,7 +2246,9 @@
         <v>58.4</v>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>9.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2369,7 +2373,7 @@
         <v>82.8</v>
       </c>
       <c r="U7" t="n">
-        <v>84.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -3334,22 +3338,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>944</v>
+        <v>891.7</v>
       </c>
       <c r="D21" t="n">
-        <v>32</v>
+        <v>78.5</v>
       </c>
       <c r="E21" t="n">
-        <v>944</v>
+        <v>912</v>
       </c>
       <c r="F21" t="n">
         <v>976</v>
       </c>
       <c r="G21" t="n">
-        <v>912</v>
+        <v>787</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>78.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>84.3</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,10 +496,10 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1339</v>
+        <v>1397.5</v>
       </c>
       <c r="I2" t="n">
-        <v>888.5</v>
+        <v>889.4</v>
       </c>
       <c r="J2" t="n">
         <v>991</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>75.8</v>
+        <v>75.7</v>
       </c>
       <c r="E3" t="n">
-        <v>79.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1288.1</v>
+        <v>1363</v>
       </c>
       <c r="I3" t="n">
-        <v>888.5</v>
+        <v>890.8</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>67.90000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="E4" t="n">
-        <v>79.8</v>
+        <v>78.3</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>950.8</v>
+        <v>980</v>
       </c>
       <c r="I4" t="n">
-        <v>854.4</v>
+        <v>854.9</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -620,10 +620,10 @@
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>63.1</v>
+        <v>63.3</v>
       </c>
       <c r="E6" t="n">
-        <v>64.8</v>
+        <v>66.7</v>
       </c>
       <c r="F6" t="n">
         <v>96.09999999999999</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1009</v>
+        <v>1012.9</v>
       </c>
       <c r="I6" t="n">
         <v>864.8</v>
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>43.9</v>
       </c>
       <c r="F7" t="n">
-        <v>88</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>695.9</v>
+        <v>949.2</v>
       </c>
       <c r="I7" t="n">
-        <v>825</v>
+        <v>813.6</v>
       </c>
       <c r="J7" t="n">
-        <v>985</v>
+        <v>976</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
       <c r="E8" t="n">
-        <v>43.9</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>89.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>941.5</v>
+        <v>689.6</v>
       </c>
       <c r="I8" t="n">
-        <v>813.6</v>
+        <v>825</v>
       </c>
       <c r="J8" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
     </row>
     <row r="9">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>49.3</v>
+        <v>48.7</v>
       </c>
       <c r="E9" t="n">
-        <v>51.6</v>
+        <v>50.8</v>
       </c>
       <c r="F9" t="n">
         <v>90.2</v>
@@ -734,10 +734,10 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>838.9</v>
+        <v>876.7</v>
       </c>
       <c r="I9" t="n">
-        <v>809.8</v>
+        <v>813.4</v>
       </c>
       <c r="J9" t="n">
         <v>960</v>
@@ -1161,7 +1161,9 @@
         <v>929</v>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>904</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1222,7 +1224,9 @@
       <c r="T3" t="n">
         <v>991</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>929</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1397,7 +1401,9 @@
       <c r="T6" t="n">
         <v>850</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>875</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1748,7 +1754,9 @@
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>862</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2073,7 +2081,9 @@
         <v>93.40000000000001</v>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>58.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2134,7 +2144,9 @@
       <c r="T3" t="n">
         <v>88.5</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>74.90000000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2192,7 +2204,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>60.2</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2247,7 +2259,7 @@
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>9.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="6">
@@ -2309,7 +2321,9 @@
       <c r="T6" t="n">
         <v>51.6</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>37.8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2373,7 +2387,7 @@
         <v>82.8</v>
       </c>
       <c r="U7" t="n">
-        <v>85.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2660,7 +2674,9 @@
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>29.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3338,16 +3354,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>891.7</v>
+        <v>892.1</v>
       </c>
       <c r="D21" t="n">
-        <v>78.5</v>
+        <v>55</v>
       </c>
       <c r="E21" t="n">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="F21" t="n">
         <v>976</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>77.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E2" t="n">
         <v>82</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1397.5</v>
+        <v>1400.9</v>
       </c>
       <c r="I2" t="n">
         <v>889.4</v>
@@ -518,10 +518,10 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>75.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>78.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1363</v>
+        <v>1366.3</v>
       </c>
       <c r="I3" t="n">
         <v>890.8</v>
@@ -552,7 +552,7 @@
         <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>65.3</v>
+        <v>65.5</v>
       </c>
       <c r="E4" t="n">
         <v>78.3</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>980</v>
+        <v>981.8</v>
       </c>
       <c r="I4" t="n">
         <v>854.9</v>
@@ -620,10 +620,10 @@
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>63.3</v>
+        <v>63.5</v>
       </c>
       <c r="E6" t="n">
-        <v>66.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>96.09999999999999</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1012.9</v>
+        <v>1016.3</v>
       </c>
       <c r="I6" t="n">
         <v>864.8</v>
@@ -660,13 +660,13 @@
         <v>43.9</v>
       </c>
       <c r="F7" t="n">
-        <v>93.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="G7" t="n">
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>949.2</v>
+        <v>950.9</v>
       </c>
       <c r="I7" t="n">
         <v>813.6</v>
@@ -688,7 +688,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="E8" t="n">
         <v>61</v>
@@ -700,7 +700,7 @@
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>689.6</v>
+        <v>689.5</v>
       </c>
       <c r="I8" t="n">
         <v>825</v>
@@ -722,7 +722,7 @@
         <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="E9" t="n">
         <v>50.8</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>876.7</v>
+        <v>879</v>
       </c>
       <c r="I9" t="n">
         <v>813.4</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="E14" t="n">
-        <v>10.9</v>
+        <v>12.4</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,13 +904,13 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>395.5</v>
+        <v>425.1</v>
       </c>
       <c r="I14" t="n">
-        <v>714.8</v>
+        <v>722.9</v>
       </c>
       <c r="J14" t="n">
-        <v>832</v>
+        <v>860</v>
       </c>
     </row>
     <row r="15">
@@ -1866,7 +1866,9 @@
       <c r="T15" t="n">
         <v>684</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>860</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2082,7 +2084,7 @@
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>58.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="3">
@@ -2145,7 +2147,7 @@
         <v>88.5</v>
       </c>
       <c r="U3" t="n">
-        <v>74.90000000000001</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="4">
@@ -2204,7 +2206,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>64.09999999999999</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="5">
@@ -2259,7 +2261,7 @@
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -2322,7 +2324,7 @@
         <v>51.6</v>
       </c>
       <c r="U6" t="n">
-        <v>37.8</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="7">
@@ -2387,7 +2389,7 @@
         <v>82.8</v>
       </c>
       <c r="U7" t="n">
-        <v>93.59999999999999</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="8">
@@ -2675,7 +2677,7 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>29.2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -2786,7 +2788,9 @@
       <c r="T15" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>29.6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3354,16 +3358,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>892.1</v>
+        <v>888.1</v>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
+        <v>52.5</v>
       </c>
       <c r="E21" t="n">
-        <v>904</v>
+        <v>889.5</v>
       </c>
       <c r="F21" t="n">
         <v>976</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>65.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>78.3</v>
+        <v>79.8</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>981.8</v>
+        <v>1065.9</v>
       </c>
       <c r="I4" t="n">
-        <v>854.9</v>
+        <v>856.3</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>41.1</v>
+        <v>39.7</v>
       </c>
       <c r="E10" t="n">
-        <v>38.2</v>
+        <v>37.4</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>739.2</v>
+        <v>755.1</v>
       </c>
       <c r="I10" t="n">
         <v>779.8</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,11 @@
           <t>9/21/26</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>9/22/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1164,6 +1169,7 @@
       <c r="U2" t="n">
         <v>904</v>
       </c>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1227,6 +1233,7 @@
       <c r="U3" t="n">
         <v>929</v>
       </c>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1286,6 +1293,7 @@
       <c r="U4" t="n">
         <v>912</v>
       </c>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1341,6 +1349,7 @@
       <c r="U5" t="n">
         <v>787</v>
       </c>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1404,6 +1413,7 @@
       <c r="U6" t="n">
         <v>875</v>
       </c>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1469,6 +1479,7 @@
       <c r="U7" t="n">
         <v>976</v>
       </c>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1532,6 +1543,9 @@
         <v>806</v>
       </c>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>780</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1561,6 +1575,7 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1622,6 +1637,7 @@
         <v>672</v>
       </c>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1663,6 +1679,7 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1700,6 +1717,7 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1756,6 +1774,9 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
         <v>862</v>
+      </c>
+      <c r="V13" t="n">
+        <v>877</v>
       </c>
     </row>
     <row r="14">
@@ -1806,6 +1827,7 @@
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1869,6 +1891,7 @@
       <c r="U15" t="n">
         <v>860</v>
       </c>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1902,6 +1925,7 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1914,7 +1938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2023,6 +2047,11 @@
           <t>9/21/26</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>9/22/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2086,6 +2115,7 @@
       <c r="U2" t="n">
         <v>61.9</v>
       </c>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2149,6 +2179,7 @@
       <c r="U3" t="n">
         <v>78.2</v>
       </c>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2208,6 +2239,7 @@
       <c r="U4" t="n">
         <v>67.5</v>
       </c>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2263,6 +2295,7 @@
       <c r="U5" t="n">
         <v>2.7</v>
       </c>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2326,6 +2359,7 @@
       <c r="U6" t="n">
         <v>40.1</v>
       </c>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2391,6 +2425,7 @@
       <c r="U7" t="n">
         <v>95.3</v>
       </c>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2454,6 +2489,9 @@
         <v>37.4</v>
       </c>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2483,6 +2521,7 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2544,6 +2583,7 @@
         <v>7.7</v>
       </c>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2585,6 +2625,7 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2622,6 +2663,7 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2678,6 +2720,9 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
         <v>31</v>
+      </c>
+      <c r="V13" t="n">
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2728,6 +2773,7 @@
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2791,6 +2837,7 @@
       <c r="U15" t="n">
         <v>29.6</v>
       </c>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2824,6 +2871,7 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2836,7 +2884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3376,6 +3424,31 @@
         <v>787</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>9/22/26</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>828.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>828.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>877</v>
+      </c>
+      <c r="G22" t="n">
+        <v>780</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -552,10 +552,10 @@
         <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>66.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="E4" t="n">
-        <v>79.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1065.9</v>
+        <v>1060.8</v>
       </c>
       <c r="I4" t="n">
         <v>856.3</v>
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>51.2</v>
       </c>
       <c r="E7" t="n">
-        <v>43.9</v>
+        <v>50.1</v>
       </c>
       <c r="F7" t="n">
         <v>95.3</v>
@@ -666,10 +666,10 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>950.9</v>
+        <v>1023.5</v>
       </c>
       <c r="I7" t="n">
-        <v>813.6</v>
+        <v>816.3</v>
       </c>
       <c r="J7" t="n">
         <v>976</v>
@@ -756,7 +756,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>39.7</v>
+        <v>39.3</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>755.1</v>
+        <v>747.1</v>
       </c>
       <c r="I10" t="n">
         <v>779.8</v>
@@ -1479,7 +1479,9 @@
       <c r="U7" t="n">
         <v>976</v>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>868</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2425,7 +2427,9 @@
       <c r="U7" t="n">
         <v>95.3</v>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>72.59999999999999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2490,7 +2494,7 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>15.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="9">
@@ -2722,7 +2726,7 @@
         <v>31</v>
       </c>
       <c r="V13" t="n">
-        <v>84.09999999999999</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14">
@@ -3431,16 +3435,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>828.5</v>
+        <v>841.7</v>
       </c>
       <c r="D22" t="n">
-        <v>48.5</v>
+        <v>43.8</v>
       </c>
       <c r="E22" t="n">
-        <v>828.5</v>
+        <v>868</v>
       </c>
       <c r="F22" t="n">
         <v>877</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -552,10 +552,10 @@
         <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>66.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>78.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1060.8</v>
+        <v>1062.9</v>
       </c>
       <c r="I4" t="n">
         <v>856.3</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1023.5</v>
+        <v>1024.9</v>
       </c>
       <c r="I7" t="n">
         <v>816.3</v>
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
         <v>49.2</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>51.6</v>
       </c>
       <c r="F8" t="n">
-        <v>88</v>
+        <v>90.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>689.5</v>
+        <v>934.7</v>
       </c>
       <c r="I8" t="n">
-        <v>825</v>
+        <v>815.3</v>
       </c>
       <c r="J8" t="n">
-        <v>985</v>
+        <v>960</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>48.8</v>
+        <v>49.2</v>
       </c>
       <c r="E9" t="n">
-        <v>50.8</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>90.2</v>
+        <v>88</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="H9" t="n">
-        <v>879</v>
+        <v>689.5</v>
       </c>
       <c r="I9" t="n">
-        <v>813.4</v>
+        <v>825</v>
       </c>
       <c r="J9" t="n">
-        <v>960</v>
+        <v>985</v>
       </c>
     </row>
     <row r="10">
@@ -756,7 +756,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>747.1</v>
+        <v>743.9</v>
       </c>
       <c r="I10" t="n">
         <v>779.8</v>
@@ -1413,7 +1413,9 @@
       <c r="U6" t="n">
         <v>875</v>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>849</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2361,7 +2363,9 @@
       <c r="U6" t="n">
         <v>40.1</v>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>55.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2428,7 +2432,7 @@
         <v>95.3</v>
       </c>
       <c r="V7" t="n">
-        <v>72.59999999999999</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -2494,7 +2498,7 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>7.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="9">
@@ -2726,7 +2730,7 @@
         <v>31</v>
       </c>
       <c r="V13" t="n">
-        <v>79</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -3435,16 +3439,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>841.7</v>
+        <v>843.5</v>
       </c>
       <c r="D22" t="n">
-        <v>43.8</v>
+        <v>38</v>
       </c>
       <c r="E22" t="n">
-        <v>868</v>
+        <v>858.5</v>
       </c>
       <c r="F22" t="n">
         <v>877</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>77.8</v>
+        <v>78.8</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>84.3</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,10 +496,10 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1400.9</v>
+        <v>1498</v>
       </c>
       <c r="I2" t="n">
-        <v>889.4</v>
+        <v>894.1</v>
       </c>
       <c r="J2" t="n">
         <v>991</v>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>waltkin</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>66.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>79.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>93.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="G4" t="n">
-        <v>11.4</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>1062.9</v>
+        <v>195.3</v>
       </c>
       <c r="I4" t="n">
-        <v>856.3</v>
+        <v>869.3</v>
       </c>
       <c r="J4" t="n">
-        <v>991</v>
+        <v>960</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>waltkin</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>65.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
-        <v>91.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>99.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>195.3</v>
+        <v>1039.4</v>
       </c>
       <c r="I5" t="n">
-        <v>869.3</v>
+        <v>856.3</v>
       </c>
       <c r="J5" t="n">
-        <v>960</v>
+        <v>991</v>
       </c>
     </row>
     <row r="6">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>63.5</v>
+        <v>61.8</v>
       </c>
       <c r="E6" t="n">
-        <v>68.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="F6" t="n">
         <v>96.09999999999999</v>
@@ -632,10 +632,10 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1016.3</v>
+        <v>1050.7</v>
       </c>
       <c r="I6" t="n">
-        <v>864.8</v>
+        <v>863.4</v>
       </c>
       <c r="J6" t="n">
         <v>959</v>
@@ -654,10 +654,10 @@
         <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>51.2</v>
+        <v>50.1</v>
       </c>
       <c r="E7" t="n">
-        <v>50.1</v>
+        <v>47.8</v>
       </c>
       <c r="F7" t="n">
         <v>95.3</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1024.9</v>
+        <v>1002.5</v>
       </c>
       <c r="I7" t="n">
         <v>816.3</v>
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
         <v>49.2</v>
       </c>
       <c r="E8" t="n">
-        <v>51.6</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>90.2</v>
+        <v>88</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>934.7</v>
+        <v>689.5</v>
       </c>
       <c r="I8" t="n">
-        <v>815.3</v>
+        <v>825</v>
       </c>
       <c r="J8" t="n">
-        <v>960</v>
+        <v>985</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>49.2</v>
+        <v>48.3</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>88</v>
+        <v>90.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>689.5</v>
+        <v>917.9</v>
       </c>
       <c r="I9" t="n">
-        <v>825</v>
+        <v>815.3</v>
       </c>
       <c r="J9" t="n">
-        <v>985</v>
+        <v>960</v>
       </c>
     </row>
     <row r="10">
@@ -756,7 +756,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>743.9</v>
+        <v>746.5</v>
       </c>
       <c r="I10" t="n">
         <v>779.8</v>
@@ -1169,7 +1169,9 @@
       <c r="U2" t="n">
         <v>904</v>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>978</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1293,7 +1295,9 @@
       <c r="U4" t="n">
         <v>912</v>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>842</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2119,7 +2123,9 @@
       <c r="U2" t="n">
         <v>61.9</v>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>97.09999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2243,7 +2249,9 @@
       <c r="U4" t="n">
         <v>67.5</v>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>34.4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2364,7 +2372,7 @@
         <v>40.1</v>
       </c>
       <c r="V6" t="n">
-        <v>55.7</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="7">
@@ -2432,7 +2440,7 @@
         <v>95.3</v>
       </c>
       <c r="V7" t="n">
-        <v>74</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="8">
@@ -2498,7 +2506,7 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>4.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="9">
@@ -2730,7 +2738,7 @@
         <v>31</v>
       </c>
       <c r="V13" t="n">
-        <v>81.09999999999999</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="14">
@@ -3439,19 +3447,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>843.5</v>
+        <v>865.7</v>
       </c>
       <c r="D22" t="n">
-        <v>38</v>
+        <v>59.1</v>
       </c>
       <c r="E22" t="n">
         <v>858.5</v>
       </c>
       <c r="F22" t="n">
-        <v>877</v>
+        <v>978</v>
       </c>
       <c r="G22" t="n">
         <v>780</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="E2" t="n">
         <v>84.3</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1498</v>
+        <v>1495.9</v>
       </c>
       <c r="I2" t="n">
         <v>894.1</v>
@@ -586,7 +586,7 @@
         <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>64.3</v>
       </c>
       <c r="E5" t="n">
         <v>77.40000000000001</v>
@@ -598,7 +598,7 @@
         <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1039.4</v>
+        <v>1028.9</v>
       </c>
       <c r="I5" t="n">
         <v>856.3</v>
@@ -620,7 +620,7 @@
         <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>61.8</v>
+        <v>61.3</v>
       </c>
       <c r="E6" t="n">
         <v>67.5</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1050.7</v>
+        <v>1041.5</v>
       </c>
       <c r="I6" t="n">
         <v>863.4</v>
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>50.1</v>
+        <v>51.8</v>
       </c>
       <c r="E7" t="n">
-        <v>47.8</v>
+        <v>63.6</v>
       </c>
       <c r="F7" t="n">
-        <v>95.3</v>
+        <v>88</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1002.5</v>
+        <v>777.4</v>
       </c>
       <c r="I7" t="n">
-        <v>816.3</v>
+        <v>833.3</v>
       </c>
       <c r="J7" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>49.2</v>
+        <v>49.6</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>42.8</v>
       </c>
       <c r="F8" t="n">
-        <v>88</v>
+        <v>95.3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>689.5</v>
+        <v>992</v>
       </c>
       <c r="I8" t="n">
-        <v>825</v>
+        <v>816.3</v>
       </c>
       <c r="J8" t="n">
-        <v>985</v>
+        <v>976</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +722,7 @@
         <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>48.3</v>
+        <v>47.8</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>917.9</v>
+        <v>908.2</v>
       </c>
       <c r="I9" t="n">
         <v>815.3</v>
@@ -756,7 +756,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>39.3</v>
+        <v>39.1</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>746.5</v>
+        <v>743.5</v>
       </c>
       <c r="I10" t="n">
         <v>779.8</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>23.6</v>
+        <v>25.9</v>
       </c>
       <c r="E14" t="n">
-        <v>12.4</v>
+        <v>13.8</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,13 +904,13 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>425.1</v>
+        <v>491.4</v>
       </c>
       <c r="I14" t="n">
-        <v>722.9</v>
+        <v>732.5</v>
       </c>
       <c r="J14" t="n">
-        <v>860</v>
+        <v>906</v>
       </c>
     </row>
     <row r="15">
@@ -1353,7 +1353,9 @@
       <c r="U5" t="n">
         <v>787</v>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>950</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1899,7 +1901,9 @@
       <c r="U15" t="n">
         <v>860</v>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>906</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2124,7 +2128,7 @@
         <v>61.9</v>
       </c>
       <c r="V2" t="n">
-        <v>97.09999999999999</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3">
@@ -2250,7 +2254,7 @@
         <v>67.5</v>
       </c>
       <c r="V4" t="n">
-        <v>34.4</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="5">
@@ -2307,7 +2311,9 @@
       <c r="U5" t="n">
         <v>2.7</v>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>87.90000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2372,7 +2378,7 @@
         <v>40.1</v>
       </c>
       <c r="V6" t="n">
-        <v>38.9</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="7">
@@ -2440,7 +2446,7 @@
         <v>95.3</v>
       </c>
       <c r="V7" t="n">
-        <v>51.6</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="8">
@@ -2506,7 +2512,7 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>7.3</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="9">
@@ -2738,7 +2744,7 @@
         <v>31</v>
       </c>
       <c r="V13" t="n">
-        <v>57.6</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="14">
@@ -2853,7 +2859,9 @@
       <c r="U15" t="n">
         <v>29.6</v>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>66.3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3447,16 +3455,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>865.7</v>
+        <v>881.2</v>
       </c>
       <c r="D22" t="n">
-        <v>59.1</v>
+        <v>58.9</v>
       </c>
       <c r="E22" t="n">
-        <v>858.5</v>
+        <v>872.5</v>
       </c>
       <c r="F22" t="n">
         <v>978</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="E2" t="n">
         <v>84.3</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1495.9</v>
+        <v>1496.6</v>
       </c>
       <c r="I2" t="n">
         <v>894.1</v>
@@ -586,7 +586,7 @@
         <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>64.3</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
         <v>77.40000000000001</v>
@@ -598,7 +598,7 @@
         <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1028.9</v>
+        <v>1040</v>
       </c>
       <c r="I5" t="n">
         <v>856.3</v>
@@ -620,7 +620,7 @@
         <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>61.3</v>
+        <v>62</v>
       </c>
       <c r="E6" t="n">
         <v>67.5</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1041.5</v>
+        <v>1054</v>
       </c>
       <c r="I6" t="n">
         <v>863.4</v>
@@ -654,19 +654,19 @@
         <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>51.8</v>
+        <v>52</v>
       </c>
       <c r="E7" t="n">
         <v>63.6</v>
       </c>
       <c r="F7" t="n">
-        <v>88</v>
+        <v>90.2</v>
       </c>
       <c r="G7" t="n">
         <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>777.4</v>
+        <v>779.7</v>
       </c>
       <c r="I7" t="n">
         <v>833.3</v>
@@ -688,10 +688,10 @@
         <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>49.6</v>
+        <v>50.2</v>
       </c>
       <c r="E8" t="n">
-        <v>42.8</v>
+        <v>48.4</v>
       </c>
       <c r="F8" t="n">
         <v>95.3</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>992</v>
+        <v>1003.8</v>
       </c>
       <c r="I8" t="n">
         <v>816.3</v>
@@ -722,7 +722,7 @@
         <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>47.8</v>
+        <v>48.5</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>908.2</v>
+        <v>920.7</v>
       </c>
       <c r="I9" t="n">
         <v>815.3</v>
@@ -756,7 +756,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>39.1</v>
+        <v>39.5</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>743.5</v>
+        <v>750</v>
       </c>
       <c r="I10" t="n">
         <v>779.8</v>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>36.8</v>
+        <v>35</v>
       </c>
       <c r="E12" t="n">
-        <v>33.9</v>
+        <v>33.4</v>
       </c>
       <c r="F12" t="n">
         <v>74.2</v>
@@ -836,10 +836,10 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>626.4</v>
+        <v>630.3</v>
       </c>
       <c r="I12" t="n">
-        <v>775.7</v>
+        <v>774</v>
       </c>
       <c r="J12" t="n">
         <v>924</v>
@@ -892,7 +892,7 @@
         <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>25.9</v>
+        <v>26.3</v>
       </c>
       <c r="E14" t="n">
         <v>13.8</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>491.4</v>
+        <v>499</v>
       </c>
       <c r="I14" t="n">
         <v>732.5</v>
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>23.3</v>
+        <v>24.7</v>
       </c>
       <c r="E15" t="n">
-        <v>20.7</v>
+        <v>25.2</v>
       </c>
       <c r="F15" t="n">
         <v>57.5</v>
@@ -938,13 +938,13 @@
         <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>163.3</v>
+        <v>197.6</v>
       </c>
       <c r="I15" t="n">
-        <v>728</v>
+        <v>741.5</v>
       </c>
       <c r="J15" t="n">
-        <v>832</v>
+        <v>836</v>
       </c>
     </row>
     <row r="16">
@@ -1647,7 +1647,9 @@
         <v>672</v>
       </c>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>745</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1689,7 +1691,9 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>836</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2128,7 +2132,7 @@
         <v>61.9</v>
       </c>
       <c r="V2" t="n">
-        <v>95</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="3">
@@ -2254,7 +2258,7 @@
         <v>67.5</v>
       </c>
       <c r="V4" t="n">
-        <v>25.2</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="5">
@@ -2312,7 +2316,7 @@
         <v>2.7</v>
       </c>
       <c r="V5" t="n">
-        <v>87.90000000000001</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="6">
@@ -2378,7 +2382,7 @@
         <v>40.1</v>
       </c>
       <c r="V6" t="n">
-        <v>29.2</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="7">
@@ -2446,7 +2450,7 @@
         <v>95.3</v>
       </c>
       <c r="V7" t="n">
-        <v>41.1</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="8">
@@ -2512,7 +2516,7 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>4.3</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="9">
@@ -2605,7 +2609,9 @@
         <v>7.7</v>
       </c>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2647,7 +2653,9 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>34.3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2744,7 +2752,7 @@
         <v>31</v>
       </c>
       <c r="V13" t="n">
-        <v>47.1</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="14">
@@ -2860,7 +2868,7 @@
         <v>29.6</v>
       </c>
       <c r="V15" t="n">
-        <v>66.3</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3455,22 +3463,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C22" t="n">
-        <v>881.2</v>
+        <v>863.1</v>
       </c>
       <c r="D22" t="n">
-        <v>58.9</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>872.5</v>
+        <v>858.5</v>
       </c>
       <c r="F22" t="n">
         <v>978</v>
       </c>
       <c r="G22" t="n">
-        <v>780</v>
+        <v>745</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1496.6</v>
+        <v>1497.5</v>
       </c>
       <c r="I2" t="n">
         <v>894.1</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>75.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="E3" t="n">
-        <v>78.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1366.3</v>
+        <v>1400.9</v>
       </c>
       <c r="I3" t="n">
-        <v>890.8</v>
+        <v>887.8</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>waltkin</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
         <v>65.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>91.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>99.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>195.3</v>
+        <v>1041.9</v>
       </c>
       <c r="I4" t="n">
-        <v>869.3</v>
+        <v>856.3</v>
       </c>
       <c r="J4" t="n">
-        <v>960</v>
+        <v>991</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>waltkin</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>77.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>93.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="G5" t="n">
-        <v>11.4</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1040</v>
+        <v>195.3</v>
       </c>
       <c r="I5" t="n">
-        <v>856.3</v>
+        <v>869.3</v>
       </c>
       <c r="J5" t="n">
-        <v>991</v>
+        <v>960</v>
       </c>
     </row>
     <row r="6">
@@ -620,7 +620,7 @@
         <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>62.1</v>
       </c>
       <c r="E6" t="n">
         <v>67.5</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="I6" t="n">
         <v>863.4</v>
@@ -654,19 +654,19 @@
         <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="E7" t="n">
         <v>63.6</v>
       </c>
       <c r="F7" t="n">
-        <v>90.2</v>
+        <v>91.7</v>
       </c>
       <c r="G7" t="n">
         <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>779.7</v>
+        <v>781.2</v>
       </c>
       <c r="I7" t="n">
         <v>833.3</v>
@@ -688,10 +688,10 @@
         <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="E8" t="n">
-        <v>48.4</v>
+        <v>49.2</v>
       </c>
       <c r="F8" t="n">
         <v>95.3</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1003.8</v>
+        <v>1005.5</v>
       </c>
       <c r="I8" t="n">
         <v>816.3</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>920.7</v>
+        <v>921.9</v>
       </c>
       <c r="I9" t="n">
         <v>815.3</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>750</v>
+        <v>749.8</v>
       </c>
       <c r="I10" t="n">
         <v>779.8</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>630.3</v>
+        <v>630.1</v>
       </c>
       <c r="I12" t="n">
         <v>774</v>
@@ -892,7 +892,7 @@
         <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="E14" t="n">
         <v>13.8</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>499</v>
+        <v>501.1</v>
       </c>
       <c r="I14" t="n">
         <v>732.5</v>
@@ -926,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="E15" t="n">
         <v>25.2</v>
@@ -938,7 +938,7 @@
         <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>197.6</v>
+        <v>198.5</v>
       </c>
       <c r="I15" t="n">
         <v>741.5</v>
@@ -1235,7 +1235,9 @@
       <c r="U3" t="n">
         <v>929</v>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>835</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2132,7 +2134,7 @@
         <v>61.9</v>
       </c>
       <c r="V2" t="n">
-        <v>95.7</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -2197,7 +2199,9 @@
       <c r="U3" t="n">
         <v>78.2</v>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>34.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2258,7 +2262,7 @@
         <v>67.5</v>
       </c>
       <c r="V4" t="n">
-        <v>37.7</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="5">
@@ -2316,7 +2320,7 @@
         <v>2.7</v>
       </c>
       <c r="V5" t="n">
-        <v>90.2</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="6">
@@ -2382,7 +2386,7 @@
         <v>40.1</v>
       </c>
       <c r="V6" t="n">
-        <v>41.7</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="7">
@@ -2450,7 +2454,7 @@
         <v>95.3</v>
       </c>
       <c r="V7" t="n">
-        <v>52.9</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="8">
@@ -2516,7 +2520,7 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="9">
@@ -2610,7 +2614,7 @@
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="11">
@@ -2654,7 +2658,7 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>34.3</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="12">
@@ -2752,7 +2756,7 @@
         <v>31</v>
       </c>
       <c r="V13" t="n">
-        <v>58.2</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="14">
@@ -2868,7 +2872,7 @@
         <v>29.6</v>
       </c>
       <c r="V15" t="n">
-        <v>73.90000000000001</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
@@ -3463,16 +3467,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" t="n">
-        <v>863.1</v>
+        <v>860.5</v>
       </c>
       <c r="D22" t="n">
-        <v>67.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="E22" t="n">
-        <v>858.5</v>
+        <v>849</v>
       </c>
       <c r="F22" t="n">
         <v>978</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>62.1</v>
+        <v>61.4</v>
       </c>
       <c r="E6" t="n">
-        <v>67.5</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
         <v>96.09999999999999</v>
@@ -632,10 +632,10 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1055</v>
+        <v>1105</v>
       </c>
       <c r="I6" t="n">
-        <v>863.4</v>
+        <v>867.3</v>
       </c>
       <c r="J6" t="n">
         <v>959</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1106,6 +1106,11 @@
           <t>9/22/26</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>9/23/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1172,6 +1177,7 @@
       <c r="V2" t="n">
         <v>978</v>
       </c>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1238,6 +1244,7 @@
       <c r="V3" t="n">
         <v>835</v>
       </c>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1299,6 +1306,9 @@
       </c>
       <c r="V4" t="n">
         <v>842</v>
+      </c>
+      <c r="W4" t="n">
+        <v>934</v>
       </c>
     </row>
     <row r="5">
@@ -1358,6 +1368,7 @@
       <c r="V5" t="n">
         <v>950</v>
       </c>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1424,6 +1435,7 @@
       <c r="V6" t="n">
         <v>849</v>
       </c>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1492,6 +1504,7 @@
       <c r="V7" t="n">
         <v>868</v>
       </c>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1558,6 +1571,7 @@
       <c r="V8" t="n">
         <v>780</v>
       </c>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1588,6 +1602,7 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1652,6 +1667,7 @@
       <c r="V10" t="n">
         <v>745</v>
       </c>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1696,6 +1712,7 @@
       <c r="V11" t="n">
         <v>836</v>
       </c>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1734,6 +1751,7 @@
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1794,6 +1812,7 @@
       <c r="V13" t="n">
         <v>877</v>
       </c>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1844,6 +1863,7 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1910,6 +1930,7 @@
       <c r="V15" t="n">
         <v>906</v>
       </c>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1944,6 +1965,7 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1956,7 +1978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2070,6 +2092,11 @@
           <t>9/22/26</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>9/23/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2136,6 +2163,7 @@
       <c r="V2" t="n">
         <v>96.59999999999999</v>
       </c>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2202,6 +2230,7 @@
       <c r="V3" t="n">
         <v>34.6</v>
       </c>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2263,6 +2292,9 @@
       </c>
       <c r="V4" t="n">
         <v>38.7</v>
+      </c>
+      <c r="W4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -2322,6 +2354,7 @@
       <c r="V5" t="n">
         <v>91.7</v>
       </c>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2388,6 +2421,7 @@
       <c r="V6" t="n">
         <v>42.9</v>
       </c>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2456,6 +2490,7 @@
       <c r="V7" t="n">
         <v>54.6</v>
       </c>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2522,6 +2557,7 @@
       <c r="V8" t="n">
         <v>10.6</v>
       </c>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2552,6 +2588,7 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2616,6 +2653,7 @@
       <c r="V10" t="n">
         <v>3.7</v>
       </c>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2660,6 +2698,7 @@
       <c r="V11" t="n">
         <v>35.2</v>
       </c>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2698,6 +2737,7 @@
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2758,6 +2798,7 @@
       <c r="V13" t="n">
         <v>60.1</v>
       </c>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2808,6 +2849,7 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2874,6 +2916,7 @@
       <c r="V15" t="n">
         <v>76</v>
       </c>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2908,6 +2951,7 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2920,7 +2964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3485,6 +3529,31 @@
         <v>745</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>9/23/26</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>934</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>934</v>
+      </c>
+      <c r="F23" t="n">
+        <v>934</v>
+      </c>
+      <c r="G23" t="n">
+        <v>934</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -620,10 +620,10 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>61.4</v>
+        <v>63.3</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>96.09999999999999</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1105</v>
+        <v>1139.1</v>
       </c>
       <c r="I6" t="n">
         <v>867.3</v>
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>50.3</v>
+        <v>48.6</v>
       </c>
       <c r="E8" t="n">
-        <v>49.2</v>
+        <v>43.9</v>
       </c>
       <c r="F8" t="n">
         <v>95.3</v>
@@ -700,10 +700,10 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1005.5</v>
+        <v>1021.4</v>
       </c>
       <c r="I8" t="n">
-        <v>816.3</v>
+        <v>820.1</v>
       </c>
       <c r="J8" t="n">
         <v>976</v>
@@ -1504,7 +1504,9 @@
       <c r="V7" t="n">
         <v>868</v>
       </c>
-      <c r="W7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>897</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2294,7 +2296,7 @@
         <v>38.7</v>
       </c>
       <c r="W4" t="n">
-        <v>50</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2490,7 +2492,9 @@
       <c r="V7" t="n">
         <v>54.6</v>
       </c>
-      <c r="W7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3536,22 +3540,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>934</v>
+        <v>915.5</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="E23" t="n">
-        <v>934</v>
+        <v>915.5</v>
       </c>
       <c r="F23" t="n">
         <v>934</v>
       </c>
       <c r="G23" t="n">
-        <v>934</v>
+        <v>897</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -620,7 +620,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>63.3</v>
+        <v>62.8</v>
       </c>
       <c r="E6" t="n">
         <v>68.40000000000001</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1139.1</v>
+        <v>1131.2</v>
       </c>
       <c r="I6" t="n">
         <v>867.3</v>
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>52.1</v>
+        <v>53.9</v>
       </c>
       <c r="E7" t="n">
-        <v>63.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F7" t="n">
         <v>91.7</v>
@@ -666,10 +666,10 @@
         <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>781.2</v>
+        <v>861.9</v>
       </c>
       <c r="I7" t="n">
-        <v>833.3</v>
+        <v>840.2</v>
       </c>
       <c r="J7" t="n">
         <v>985</v>
@@ -688,10 +688,10 @@
         <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>48.6</v>
+        <v>50.4</v>
       </c>
       <c r="E8" t="n">
-        <v>43.9</v>
+        <v>52.9</v>
       </c>
       <c r="F8" t="n">
         <v>95.3</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1021.4</v>
+        <v>1058.4</v>
       </c>
       <c r="I8" t="n">
         <v>820.1</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>26.4</v>
+        <v>25.3</v>
       </c>
       <c r="E14" t="n">
-        <v>13.8</v>
+        <v>12.4</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>501.1</v>
+        <v>506</v>
       </c>
       <c r="I14" t="n">
-        <v>732.5</v>
+        <v>735.8</v>
       </c>
       <c r="J14" t="n">
         <v>906</v>
@@ -1368,7 +1368,9 @@
       <c r="V5" t="n">
         <v>950</v>
       </c>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>943</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1932,7 +1934,9 @@
       <c r="V15" t="n">
         <v>906</v>
       </c>
-      <c r="W15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>797</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2296,7 +2300,7 @@
         <v>38.7</v>
       </c>
       <c r="W4" t="n">
-        <v>84.09999999999999</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="5">
@@ -2356,7 +2360,9 @@
       <c r="V5" t="n">
         <v>91.7</v>
       </c>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>80.7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2493,7 +2499,7 @@
         <v>54.6</v>
       </c>
       <c r="W7" t="n">
-        <v>15.9</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="8">
@@ -2920,7 +2926,9 @@
       <c r="V15" t="n">
         <v>76</v>
       </c>
-      <c r="W15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3540,22 +3548,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>915.5</v>
+        <v>892.8</v>
       </c>
       <c r="D23" t="n">
-        <v>18.5</v>
+        <v>57.9</v>
       </c>
       <c r="E23" t="n">
         <v>915.5</v>
       </c>
       <c r="F23" t="n">
-        <v>934</v>
+        <v>943</v>
       </c>
       <c r="G23" t="n">
-        <v>897</v>
+        <v>797</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>78.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>84.3</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,10 +496,10 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1497.5</v>
+        <v>1542.7</v>
       </c>
       <c r="I2" t="n">
-        <v>894.1</v>
+        <v>893.6</v>
       </c>
       <c r="J2" t="n">
         <v>991</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>65.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>77.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1041.9</v>
+        <v>1123.5</v>
       </c>
       <c r="I4" t="n">
-        <v>856.3</v>
+        <v>861</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -620,7 +620,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>62.8</v>
+        <v>63.1</v>
       </c>
       <c r="E6" t="n">
         <v>68.40000000000001</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1131.2</v>
+        <v>1135.6</v>
       </c>
       <c r="I6" t="n">
         <v>867.3</v>
@@ -654,7 +654,7 @@
         <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>53.9</v>
+        <v>54.1</v>
       </c>
       <c r="E7" t="n">
         <v>64.59999999999999</v>
@@ -666,7 +666,7 @@
         <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>861.9</v>
+        <v>866.3</v>
       </c>
       <c r="I7" t="n">
         <v>840.2</v>
@@ -688,10 +688,10 @@
         <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="E8" t="n">
-        <v>52.9</v>
+        <v>54.6</v>
       </c>
       <c r="F8" t="n">
         <v>95.3</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1058.4</v>
+        <v>1060.9</v>
       </c>
       <c r="I8" t="n">
         <v>820.1</v>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12" t="n">
-        <v>33.4</v>
+        <v>33</v>
       </c>
       <c r="F12" t="n">
         <v>74.2</v>
@@ -836,10 +836,10 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>630.1</v>
+        <v>646.3</v>
       </c>
       <c r="I12" t="n">
-        <v>774</v>
+        <v>777.5</v>
       </c>
       <c r="J12" t="n">
         <v>924</v>
@@ -892,7 +892,7 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="E14" t="n">
         <v>12.4</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>506</v>
+        <v>504.4</v>
       </c>
       <c r="I14" t="n">
         <v>735.8</v>
@@ -1177,7 +1177,9 @@
       <c r="V2" t="n">
         <v>978</v>
       </c>
-      <c r="W2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>884</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1671,7 +1673,9 @@
       <c r="V10" t="n">
         <v>745</v>
       </c>
-      <c r="W10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>840</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1816,7 +1820,9 @@
       <c r="V13" t="n">
         <v>877</v>
       </c>
-      <c r="W13" t="inlineStr"/>
+      <c r="W13" t="n">
+        <v>936</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2169,7 +2175,9 @@
       <c r="V2" t="n">
         <v>96.59999999999999</v>
       </c>
-      <c r="W2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>45.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2300,7 +2308,7 @@
         <v>38.7</v>
       </c>
       <c r="W4" t="n">
-        <v>76.2</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2361,7 +2369,7 @@
         <v>91.7</v>
       </c>
       <c r="W5" t="n">
-        <v>80.7</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2499,7 +2507,7 @@
         <v>54.6</v>
       </c>
       <c r="W7" t="n">
-        <v>52.9</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="8">
@@ -2663,7 +2671,9 @@
       <c r="V10" t="n">
         <v>3.7</v>
       </c>
-      <c r="W10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>16.2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2808,7 +2818,9 @@
       <c r="V13" t="n">
         <v>60.1</v>
       </c>
-      <c r="W13" t="inlineStr"/>
+      <c r="W13" t="n">
+        <v>81.59999999999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2927,7 +2939,7 @@
         <v>76</v>
       </c>
       <c r="W15" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="16">
@@ -3548,16 +3560,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>892.8</v>
+        <v>890.1</v>
       </c>
       <c r="D23" t="n">
-        <v>57.9</v>
+        <v>50.8</v>
       </c>
       <c r="E23" t="n">
-        <v>915.5</v>
+        <v>897</v>
       </c>
       <c r="F23" t="n">
         <v>943</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="E2" t="n">
         <v>82</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1542.7</v>
+        <v>1543</v>
       </c>
       <c r="I2" t="n">
         <v>893.6</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>73.7</v>
+        <v>72.3</v>
       </c>
       <c r="E3" t="n">
-        <v>78.2</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1400.9</v>
+        <v>1446.4</v>
       </c>
       <c r="I3" t="n">
-        <v>887.8</v>
+        <v>887.6</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -552,7 +552,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>66.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="E4" t="n">
         <v>78.3</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1123.5</v>
+        <v>1125.5</v>
       </c>
       <c r="I4" t="n">
         <v>861</v>
@@ -620,7 +620,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>63.1</v>
+        <v>63.2</v>
       </c>
       <c r="E6" t="n">
         <v>68.40000000000001</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1135.6</v>
+        <v>1137.6</v>
       </c>
       <c r="I6" t="n">
         <v>867.3</v>
@@ -654,7 +654,7 @@
         <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>54.1</v>
+        <v>54.3</v>
       </c>
       <c r="E7" t="n">
         <v>64.59999999999999</v>
@@ -666,7 +666,7 @@
         <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>866.3</v>
+        <v>868.2</v>
       </c>
       <c r="I7" t="n">
         <v>840.2</v>
@@ -688,7 +688,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E8" t="n">
         <v>54.6</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1060.9</v>
+        <v>1061.9</v>
       </c>
       <c r="I8" t="n">
         <v>820.1</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>646.3</v>
+        <v>645.1</v>
       </c>
       <c r="I12" t="n">
         <v>777.5</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>504.4</v>
+        <v>503.7</v>
       </c>
       <c r="I14" t="n">
         <v>735.8</v>
@@ -1246,7 +1246,9 @@
       <c r="V3" t="n">
         <v>835</v>
       </c>
-      <c r="W3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>884</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2176,7 +2178,7 @@
         <v>96.59999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="3">
@@ -2244,7 +2246,9 @@
       <c r="V3" t="n">
         <v>34.6</v>
       </c>
-      <c r="W3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>45.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2308,7 +2312,7 @@
         <v>38.7</v>
       </c>
       <c r="W4" t="n">
-        <v>80.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2369,7 +2373,7 @@
         <v>91.7</v>
       </c>
       <c r="W5" t="n">
-        <v>85.09999999999999</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
@@ -2507,7 +2511,7 @@
         <v>54.6</v>
       </c>
       <c r="W7" t="n">
-        <v>55.4</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="8">
@@ -2672,7 +2676,7 @@
         <v>3.7</v>
       </c>
       <c r="W10" t="n">
-        <v>16.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -2819,7 +2823,7 @@
         <v>60.1</v>
       </c>
       <c r="W13" t="n">
-        <v>81.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2939,7 +2943,7 @@
         <v>76</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="16">
@@ -3560,16 +3564,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>890.1</v>
+        <v>889.4</v>
       </c>
       <c r="D23" t="n">
-        <v>50.8</v>
+        <v>47.6</v>
       </c>
       <c r="E23" t="n">
-        <v>897</v>
+        <v>890.5</v>
       </c>
       <c r="F23" t="n">
         <v>943</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>82</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1543</v>
+        <v>1541.9</v>
       </c>
       <c r="I2" t="n">
         <v>893.6</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1446.4</v>
+        <v>1445.3</v>
       </c>
       <c r="I3" t="n">
         <v>887.6</v>
@@ -552,7 +552,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>66.2</v>
+        <v>66.3</v>
       </c>
       <c r="E4" t="n">
         <v>78.3</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1125.5</v>
+        <v>1126.4</v>
       </c>
       <c r="I4" t="n">
         <v>861</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1137.6</v>
+        <v>1138.4</v>
       </c>
       <c r="I6" t="n">
         <v>867.3</v>
@@ -666,7 +666,7 @@
         <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>868.2</v>
+        <v>869.1</v>
       </c>
       <c r="I7" t="n">
         <v>840.2</v>
@@ -688,7 +688,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="E8" t="n">
         <v>54.6</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1061.9</v>
+        <v>1061.4</v>
       </c>
       <c r="I8" t="n">
         <v>820.1</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>50.8</v>
       </c>
       <c r="F9" t="n">
         <v>90.2</v>
@@ -734,10 +734,10 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>921.9</v>
+        <v>978.7</v>
       </c>
       <c r="I9" t="n">
-        <v>815.3</v>
+        <v>819.4</v>
       </c>
       <c r="J9" t="n">
         <v>960</v>
@@ -824,7 +824,7 @@
         <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="E12" t="n">
         <v>33</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>645.1</v>
+        <v>643.2</v>
       </c>
       <c r="I12" t="n">
         <v>777.5</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>503.7</v>
+        <v>503</v>
       </c>
       <c r="I14" t="n">
         <v>735.8</v>
@@ -1441,7 +1441,9 @@
       <c r="V6" t="n">
         <v>849</v>
       </c>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>898</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2178,7 +2180,7 @@
         <v>96.59999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>45.5</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="3">
@@ -2247,7 +2249,7 @@
         <v>34.6</v>
       </c>
       <c r="W3" t="n">
-        <v>45.5</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="4">
@@ -2312,7 +2314,7 @@
         <v>38.7</v>
       </c>
       <c r="W4" t="n">
-        <v>82.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2373,7 +2375,7 @@
         <v>91.7</v>
       </c>
       <c r="W5" t="n">
-        <v>87</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2441,7 +2443,9 @@
       <c r="V6" t="n">
         <v>42.9</v>
       </c>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>56.8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2511,7 +2515,7 @@
         <v>54.6</v>
       </c>
       <c r="W7" t="n">
-        <v>56.4</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="8">
@@ -2676,7 +2680,7 @@
         <v>3.7</v>
       </c>
       <c r="W10" t="n">
-        <v>15</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="11">
@@ -2823,7 +2827,7 @@
         <v>60.1</v>
       </c>
       <c r="W13" t="n">
-        <v>83.59999999999999</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="14">
@@ -2943,7 +2947,7 @@
         <v>76</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="16">
@@ -3564,16 +3568,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
-        <v>889.4</v>
+        <v>890.3</v>
       </c>
       <c r="D23" t="n">
-        <v>47.6</v>
+        <v>45</v>
       </c>
       <c r="E23" t="n">
-        <v>890.5</v>
+        <v>897</v>
       </c>
       <c r="F23" t="n">
         <v>943</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1541.9</v>
+        <v>1541.7</v>
       </c>
       <c r="I2" t="n">
         <v>893.6</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1445.3</v>
+        <v>1445.1</v>
       </c>
       <c r="I3" t="n">
         <v>887.6</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1126.4</v>
+        <v>1127.8</v>
       </c>
       <c r="I4" t="n">
         <v>861</v>
@@ -620,7 +620,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
       <c r="E6" t="n">
         <v>68.40000000000001</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1138.4</v>
+        <v>1139.8</v>
       </c>
       <c r="I6" t="n">
         <v>867.3</v>
@@ -654,7 +654,7 @@
         <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="E7" t="n">
         <v>64.59999999999999</v>
@@ -666,7 +666,7 @@
         <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>869.1</v>
+        <v>870.4</v>
       </c>
       <c r="I7" t="n">
         <v>840.2</v>
@@ -688,7 +688,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E8" t="n">
         <v>54.6</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1061.4</v>
+        <v>1061.8</v>
       </c>
       <c r="I8" t="n">
         <v>820.1</v>
@@ -722,7 +722,7 @@
         <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E9" t="n">
         <v>50.8</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>978.7</v>
+        <v>979.2</v>
       </c>
       <c r="I9" t="n">
         <v>819.4</v>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>39.5</v>
+        <v>39.9</v>
       </c>
       <c r="E10" t="n">
-        <v>37.4</v>
+        <v>38.2</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,10 +768,10 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>749.8</v>
+        <v>798.7</v>
       </c>
       <c r="I10" t="n">
-        <v>779.8</v>
+        <v>785.2</v>
       </c>
       <c r="J10" t="n">
         <v>928</v>
@@ -824,7 +824,7 @@
         <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="E12" t="n">
         <v>33</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>643.2</v>
+        <v>642.1</v>
       </c>
       <c r="I12" t="n">
         <v>777.5</v>
@@ -892,7 +892,7 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="E14" t="n">
         <v>12.4</v>
@@ -901,10 +901,10 @@
         <v>84.09999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="H14" t="n">
-        <v>503</v>
+        <v>502.5</v>
       </c>
       <c r="I14" t="n">
         <v>735.8</v>
@@ -1581,7 +1581,9 @@
       <c r="V8" t="n">
         <v>780</v>
       </c>
-      <c r="W8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>889</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2180,7 +2182,7 @@
         <v>96.59999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="3">
@@ -2249,7 +2251,7 @@
         <v>34.6</v>
       </c>
       <c r="W3" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="4">
@@ -2314,7 +2316,7 @@
         <v>38.7</v>
       </c>
       <c r="W4" t="n">
-        <v>83.40000000000001</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="5">
@@ -2375,7 +2377,7 @@
         <v>91.7</v>
       </c>
       <c r="W5" t="n">
-        <v>87.90000000000001</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="6">
@@ -2444,7 +2446,7 @@
         <v>42.9</v>
       </c>
       <c r="W6" t="n">
-        <v>56.8</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="7">
@@ -2515,7 +2517,7 @@
         <v>54.6</v>
       </c>
       <c r="W7" t="n">
-        <v>55.9</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="8">
@@ -2583,7 +2585,9 @@
       <c r="V8" t="n">
         <v>10.6</v>
       </c>
-      <c r="W8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>48.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2680,7 +2684,7 @@
         <v>3.7</v>
       </c>
       <c r="W10" t="n">
-        <v>13.1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -2827,7 +2831,7 @@
         <v>60.1</v>
       </c>
       <c r="W13" t="n">
-        <v>84.5</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2947,7 +2951,7 @@
         <v>76</v>
       </c>
       <c r="W15" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="16">
@@ -3568,16 +3572,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23" t="n">
-        <v>890.3</v>
+        <v>890.2</v>
       </c>
       <c r="D23" t="n">
-        <v>45</v>
+        <v>42.7</v>
       </c>
       <c r="E23" t="n">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="F23" t="n">
         <v>943</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>50.6</v>
+        <v>52.1</v>
       </c>
       <c r="E8" t="n">
-        <v>54.6</v>
+        <v>55.4</v>
       </c>
       <c r="F8" t="n">
         <v>95.3</v>
@@ -700,10 +700,10 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1061.8</v>
+        <v>1145.9</v>
       </c>
       <c r="I8" t="n">
-        <v>820.1</v>
+        <v>827</v>
       </c>
       <c r="J8" t="n">
         <v>976</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>47.4</v>
       </c>
       <c r="E9" t="n">
-        <v>50.8</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
         <v>90.2</v>
@@ -734,10 +734,10 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>979.2</v>
+        <v>995.1</v>
       </c>
       <c r="I9" t="n">
-        <v>819.4</v>
+        <v>822.3</v>
       </c>
       <c r="J9" t="n">
         <v>960</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1111,6 +1111,11 @@
           <t>9/23/26</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>9/24/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1180,6 +1185,7 @@
       <c r="W2" t="n">
         <v>884</v>
       </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1249,6 +1255,7 @@
       <c r="W3" t="n">
         <v>884</v>
       </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1314,6 +1321,7 @@
       <c r="W4" t="n">
         <v>934</v>
       </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1375,6 +1383,7 @@
       <c r="W5" t="n">
         <v>943</v>
       </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1444,6 +1453,9 @@
       <c r="W6" t="n">
         <v>898</v>
       </c>
+      <c r="X6" t="n">
+        <v>880</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1515,6 +1527,9 @@
       <c r="W7" t="n">
         <v>897</v>
       </c>
+      <c r="X7" t="n">
+        <v>972</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1584,6 +1599,7 @@
       <c r="W8" t="n">
         <v>889</v>
       </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1615,6 +1631,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1682,6 +1699,7 @@
       <c r="W10" t="n">
         <v>840</v>
       </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1727,6 +1745,7 @@
         <v>836</v>
       </c>
       <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1766,6 +1785,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1829,6 +1849,7 @@
       <c r="W13" t="n">
         <v>936</v>
       </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1880,6 +1901,7 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1949,6 +1971,7 @@
       <c r="W15" t="n">
         <v>797</v>
       </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1984,6 +2007,7 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1996,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2115,6 +2139,11 @@
           <t>9/23/26</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>9/24/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2184,6 +2213,7 @@
       <c r="W2" t="n">
         <v>44.2</v>
       </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2253,6 +2283,7 @@
       <c r="W3" t="n">
         <v>44.2</v>
       </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2318,6 +2349,7 @@
       <c r="W4" t="n">
         <v>84.8</v>
       </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2379,6 +2411,7 @@
       <c r="W5" t="n">
         <v>89.2</v>
       </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2448,6 +2481,9 @@
       <c r="W6" t="n">
         <v>57.3</v>
       </c>
+      <c r="X6" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2519,6 +2555,9 @@
       <c r="W7" t="n">
         <v>56.3</v>
       </c>
+      <c r="X7" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2588,6 +2627,7 @@
       <c r="W8" t="n">
         <v>48.9</v>
       </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2619,6 +2659,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2686,6 +2727,7 @@
       <c r="W10" t="n">
         <v>12</v>
       </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2731,6 +2773,7 @@
         <v>35.2</v>
       </c>
       <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2770,6 +2813,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2833,6 +2877,7 @@
       <c r="W13" t="n">
         <v>85.90000000000001</v>
       </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2884,6 +2929,7 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2953,6 +2999,7 @@
       <c r="W15" t="n">
         <v>1.4</v>
       </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2988,6 +3035,7 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3000,7 +3048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3590,6 +3638,31 @@
         <v>797</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>9/24/26</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>926</v>
+      </c>
+      <c r="D24" t="n">
+        <v>46</v>
+      </c>
+      <c r="E24" t="n">
+        <v>926</v>
+      </c>
+      <c r="F24" t="n">
+        <v>972</v>
+      </c>
+      <c r="G24" t="n">
+        <v>880</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>77.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>84.3</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,10 +496,10 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1541.7</v>
+        <v>1629.3</v>
       </c>
       <c r="I2" t="n">
-        <v>893.6</v>
+        <v>897.8</v>
       </c>
       <c r="J2" t="n">
         <v>991</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1145.9</v>
+        <v>1146.4</v>
       </c>
       <c r="I8" t="n">
         <v>827</v>
@@ -722,7 +722,7 @@
         <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>47.4</v>
+        <v>48.5</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>995.1</v>
+        <v>1019.5</v>
       </c>
       <c r="I9" t="n">
         <v>822.3</v>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>39.9</v>
+        <v>40.6</v>
       </c>
       <c r="E10" t="n">
-        <v>38.2</v>
+        <v>38.9</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,10 +768,10 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>798.7</v>
+        <v>852.1</v>
       </c>
       <c r="I10" t="n">
-        <v>785.2</v>
+        <v>790.9</v>
       </c>
       <c r="J10" t="n">
         <v>928</v>
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>32.4</v>
+        <v>27.5</v>
       </c>
       <c r="E13" t="n">
-        <v>22.9</v>
+        <v>19.9</v>
       </c>
       <c r="F13" t="n">
         <v>62.8</v>
@@ -870,10 +870,10 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>161.8</v>
+        <v>164.8</v>
       </c>
       <c r="I13" t="n">
-        <v>761.8</v>
+        <v>761.7</v>
       </c>
       <c r="J13" t="n">
         <v>849</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>25.1</v>
+        <v>26.1</v>
       </c>
       <c r="E14" t="n">
-        <v>12.4</v>
+        <v>13.8</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1.4</v>
       </c>
       <c r="H14" t="n">
-        <v>502.5</v>
+        <v>547.1</v>
       </c>
       <c r="I14" t="n">
-        <v>735.8</v>
+        <v>743</v>
       </c>
       <c r="J14" t="n">
         <v>906</v>
@@ -1185,7 +1185,9 @@
       <c r="W2" t="n">
         <v>884</v>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>982</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1599,7 +1601,9 @@
       <c r="W8" t="n">
         <v>889</v>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>904</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1785,7 +1789,9 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>761</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1971,7 +1977,9 @@
       <c r="W15" t="n">
         <v>797</v>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="n">
+        <v>888</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2213,7 +2221,9 @@
       <c r="W2" t="n">
         <v>44.2</v>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>87.59999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2482,7 +2492,7 @@
         <v>57.3</v>
       </c>
       <c r="X6" t="n">
-        <v>15.9</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="7">
@@ -2556,7 +2566,7 @@
         <v>56.3</v>
       </c>
       <c r="X7" t="n">
-        <v>84.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2627,7 +2637,9 @@
       <c r="W8" t="n">
         <v>48.9</v>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>53.4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2813,7 +2825,9 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2999,7 +3013,9 @@
       <c r="W15" t="n">
         <v>1.4</v>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="n">
+        <v>44.6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3645,22 +3661,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>926</v>
+        <v>897.8</v>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>72.8</v>
       </c>
       <c r="E24" t="n">
-        <v>926</v>
+        <v>896</v>
       </c>
       <c r="F24" t="n">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="G24" t="n">
-        <v>880</v>
+        <v>761</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1629.3</v>
+        <v>1630.2</v>
       </c>
       <c r="I2" t="n">
         <v>897.8</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>72.3</v>
+        <v>71.7</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>77.7</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1445.1</v>
+        <v>1504.7</v>
       </c>
       <c r="I3" t="n">
-        <v>887.6</v>
+        <v>889</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1146.4</v>
+        <v>1147.2</v>
       </c>
       <c r="I8" t="n">
         <v>827</v>
@@ -722,7 +722,7 @@
         <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1019.5</v>
+        <v>1017.3</v>
       </c>
       <c r="I9" t="n">
         <v>822.3</v>
@@ -756,7 +756,7 @@
         <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="E10" t="n">
         <v>38.9</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>852.1</v>
+        <v>850.7</v>
       </c>
       <c r="I10" t="n">
         <v>790.9</v>
@@ -858,7 +858,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="E13" t="n">
         <v>19.9</v>
@@ -867,10 +867,10 @@
         <v>62.8</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>164.8</v>
+        <v>163.8</v>
       </c>
       <c r="I13" t="n">
         <v>761.7</v>
@@ -892,7 +892,7 @@
         <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="E14" t="n">
         <v>13.8</v>
@@ -904,7 +904,7 @@
         <v>1.4</v>
       </c>
       <c r="H14" t="n">
-        <v>547.1</v>
+        <v>545.1</v>
       </c>
       <c r="I14" t="n">
         <v>743</v>
@@ -1257,7 +1257,9 @@
       <c r="W3" t="n">
         <v>884</v>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>917</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2222,7 +2224,7 @@
         <v>44.2</v>
       </c>
       <c r="X2" t="n">
-        <v>87.59999999999999</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="3">
@@ -2293,7 +2295,9 @@
       <c r="W3" t="n">
         <v>44.2</v>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>59.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2492,7 +2496,7 @@
         <v>57.3</v>
       </c>
       <c r="X6" t="n">
-        <v>40.3</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="7">
@@ -2566,7 +2570,7 @@
         <v>56.3</v>
       </c>
       <c r="X7" t="n">
-        <v>84.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2638,7 +2642,7 @@
         <v>48.9</v>
       </c>
       <c r="X8" t="n">
-        <v>53.4</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
@@ -2826,7 +2830,7 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -3014,7 +3018,7 @@
         <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>44.6</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="16">
@@ -3661,16 +3665,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>897.8</v>
+        <v>900.6</v>
       </c>
       <c r="D24" t="n">
-        <v>72.8</v>
+        <v>67.7</v>
       </c>
       <c r="E24" t="n">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="F24" t="n">
         <v>982</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="E2" t="n">
         <v>84.3</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1630.2</v>
+        <v>1632.7</v>
       </c>
       <c r="I2" t="n">
         <v>897.8</v>
@@ -518,7 +518,7 @@
         <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>77.7</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1504.7</v>
+        <v>1509.3</v>
       </c>
       <c r="I3" t="n">
         <v>889</v>
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>54.4</v>
+        <v>52.4</v>
       </c>
       <c r="E7" t="n">
-        <v>64.59999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="F7" t="n">
         <v>91.7</v>
@@ -666,10 +666,10 @@
         <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>870.4</v>
+        <v>891</v>
       </c>
       <c r="I7" t="n">
-        <v>840.2</v>
+        <v>840.1</v>
       </c>
       <c r="J7" t="n">
         <v>985</v>
@@ -688,7 +688,7 @@
         <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="E8" t="n">
         <v>55.4</v>
@@ -700,7 +700,7 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1147.2</v>
+        <v>1150.1</v>
       </c>
       <c r="I8" t="n">
         <v>827</v>
@@ -722,7 +722,7 @@
         <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1017.3</v>
+        <v>1021.6</v>
       </c>
       <c r="I9" t="n">
         <v>822.3</v>
@@ -756,7 +756,7 @@
         <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="E10" t="n">
         <v>38.9</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>850.7</v>
+        <v>855.4</v>
       </c>
       <c r="I10" t="n">
         <v>790.9</v>
@@ -858,7 +858,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="E13" t="n">
         <v>19.9</v>
@@ -867,10 +867,10 @@
         <v>62.8</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H13" t="n">
-        <v>163.8</v>
+        <v>164.2</v>
       </c>
       <c r="I13" t="n">
         <v>761.7</v>
@@ -892,7 +892,7 @@
         <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="E14" t="n">
         <v>13.8</v>
@@ -904,7 +904,7 @@
         <v>1.4</v>
       </c>
       <c r="H14" t="n">
-        <v>545.1</v>
+        <v>549.7</v>
       </c>
       <c r="I14" t="n">
         <v>743</v>
@@ -1387,7 +1387,9 @@
       <c r="W5" t="n">
         <v>943</v>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>838</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2224,7 +2226,7 @@
         <v>44.2</v>
       </c>
       <c r="X2" t="n">
-        <v>88.5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
@@ -2296,7 +2298,7 @@
         <v>44.2</v>
       </c>
       <c r="X3" t="n">
-        <v>59.6</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="4">
@@ -2425,7 +2427,9 @@
       <c r="W5" t="n">
         <v>89.2</v>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>20.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2496,7 +2500,7 @@
         <v>57.3</v>
       </c>
       <c r="X6" t="n">
-        <v>38.1</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="7">
@@ -2570,7 +2574,7 @@
         <v>56.3</v>
       </c>
       <c r="X7" t="n">
-        <v>85.40000000000001</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="8">
@@ -2642,7 +2646,7 @@
         <v>48.9</v>
       </c>
       <c r="X8" t="n">
-        <v>52</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="9">
@@ -2830,7 +2834,7 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -3018,7 +3022,7 @@
         <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>42.6</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="16">
@@ -3665,16 +3669,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>900.6</v>
+        <v>892.8</v>
       </c>
       <c r="D24" t="n">
-        <v>67.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="F24" t="n">
         <v>982</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>77.7</v>
+        <v>77.8</v>
       </c>
       <c r="E2" t="n">
         <v>84.3</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1632.7</v>
+        <v>1633.5</v>
       </c>
       <c r="I2" t="n">
         <v>897.8</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1509.3</v>
+        <v>1509.2</v>
       </c>
       <c r="I3" t="n">
         <v>889</v>
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>63.3</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
-        <v>68.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="F6" t="n">
         <v>96.09999999999999</v>
@@ -632,10 +632,10 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1139.8</v>
+        <v>1197.2</v>
       </c>
       <c r="I6" t="n">
-        <v>867.3</v>
+        <v>869.4</v>
       </c>
       <c r="J6" t="n">
         <v>959</v>
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="E7" t="n">
-        <v>63.6</v>
+        <v>55.4</v>
       </c>
       <c r="F7" t="n">
-        <v>91.7</v>
+        <v>95.3</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>891</v>
+        <v>1151</v>
       </c>
       <c r="I7" t="n">
-        <v>840.1</v>
+        <v>827</v>
       </c>
       <c r="J7" t="n">
-        <v>985</v>
+        <v>976</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
         <v>52.3</v>
       </c>
       <c r="E8" t="n">
-        <v>55.4</v>
+        <v>63.6</v>
       </c>
       <c r="F8" t="n">
-        <v>95.3</v>
+        <v>91.7</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1150.1</v>
+        <v>889</v>
       </c>
       <c r="I8" t="n">
-        <v>827</v>
+        <v>840.1</v>
       </c>
       <c r="J8" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
     </row>
     <row r="9">
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1021.6</v>
+        <v>1020.3</v>
       </c>
       <c r="I9" t="n">
         <v>822.3</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>855.4</v>
+        <v>854.9</v>
       </c>
       <c r="I10" t="n">
         <v>790.9</v>
@@ -858,7 +858,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="E13" t="n">
         <v>19.9</v>
@@ -867,10 +867,10 @@
         <v>62.8</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="H13" t="n">
-        <v>164.2</v>
+        <v>163.5</v>
       </c>
       <c r="I13" t="n">
         <v>761.7</v>
@@ -892,7 +892,7 @@
         <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="E14" t="n">
         <v>13.8</v>
@@ -904,7 +904,7 @@
         <v>1.4</v>
       </c>
       <c r="H14" t="n">
-        <v>549.7</v>
+        <v>548.6</v>
       </c>
       <c r="I14" t="n">
         <v>743</v>
@@ -1325,7 +1325,9 @@
       <c r="W4" t="n">
         <v>934</v>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>906</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2226,7 +2228,7 @@
         <v>44.2</v>
       </c>
       <c r="X2" t="n">
-        <v>91</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="3">
@@ -2298,7 +2300,7 @@
         <v>44.2</v>
       </c>
       <c r="X3" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2365,7 +2367,9 @@
       <c r="W4" t="n">
         <v>84.8</v>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>57.4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2428,7 +2432,7 @@
         <v>89.2</v>
       </c>
       <c r="X5" t="n">
-        <v>20.6</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="6">
@@ -2500,7 +2504,7 @@
         <v>57.3</v>
       </c>
       <c r="X6" t="n">
-        <v>42.4</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="7">
@@ -2574,7 +2578,7 @@
         <v>56.3</v>
       </c>
       <c r="X7" t="n">
-        <v>88.3</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="8">
@@ -2646,7 +2650,7 @@
         <v>48.9</v>
       </c>
       <c r="X8" t="n">
-        <v>56.7</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="9">
@@ -2834,7 +2838,7 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="13">
@@ -3022,7 +3026,7 @@
         <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>47.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="16">
@@ -3669,16 +3673,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>892.8</v>
+        <v>894.2</v>
       </c>
       <c r="D24" t="n">
-        <v>66.59999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="E24" t="n">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="F24" t="n">
         <v>982</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1633.5</v>
+        <v>1634.1</v>
       </c>
       <c r="I2" t="n">
         <v>897.8</v>
@@ -518,7 +518,7 @@
         <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="E3" t="n">
         <v>77.7</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1509.2</v>
+        <v>1508.7</v>
       </c>
       <c r="I3" t="n">
         <v>889</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>66.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>78.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1127.8</v>
+        <v>1188.9</v>
       </c>
       <c r="I4" t="n">
-        <v>861</v>
+        <v>863.9</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1197.2</v>
+        <v>1196.4</v>
       </c>
       <c r="I6" t="n">
         <v>869.4</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1151</v>
+        <v>1151.5</v>
       </c>
       <c r="I7" t="n">
         <v>827</v>
@@ -688,7 +688,7 @@
         <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="E8" t="n">
         <v>63.6</v>
@@ -700,7 +700,7 @@
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="I8" t="n">
         <v>840.1</v>
@@ -722,7 +722,7 @@
         <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1020.3</v>
+        <v>1018.6</v>
       </c>
       <c r="I9" t="n">
         <v>822.3</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>854.9</v>
+        <v>853.9</v>
       </c>
       <c r="I10" t="n">
         <v>790.9</v>
@@ -867,10 +867,10 @@
         <v>62.8</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>163.5</v>
+        <v>163</v>
       </c>
       <c r="I13" t="n">
         <v>761.7</v>
@@ -904,7 +904,7 @@
         <v>1.4</v>
       </c>
       <c r="H14" t="n">
-        <v>548.6</v>
+        <v>547.1</v>
       </c>
       <c r="I14" t="n">
         <v>743</v>
@@ -1861,7 +1861,9 @@
       <c r="W13" t="n">
         <v>936</v>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>913</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2228,7 +2230,7 @@
         <v>44.2</v>
       </c>
       <c r="X2" t="n">
-        <v>91.8</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2300,7 +2302,7 @@
         <v>44.2</v>
       </c>
       <c r="X3" t="n">
-        <v>64.09999999999999</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="4">
@@ -2368,7 +2370,7 @@
         <v>84.8</v>
       </c>
       <c r="X4" t="n">
-        <v>57.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="5">
@@ -2432,7 +2434,7 @@
         <v>89.2</v>
       </c>
       <c r="X5" t="n">
-        <v>18.6</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="6">
@@ -2504,7 +2506,7 @@
         <v>57.3</v>
       </c>
       <c r="X6" t="n">
-        <v>41.1</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="7">
@@ -2578,7 +2580,7 @@
         <v>56.3</v>
       </c>
       <c r="X7" t="n">
-        <v>89.2</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="8">
@@ -2650,7 +2652,7 @@
         <v>48.9</v>
       </c>
       <c r="X8" t="n">
-        <v>56.2</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="9">
@@ -2838,7 +2840,7 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13">
@@ -2903,7 +2905,9 @@
       <c r="W13" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>61.1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3026,7 +3030,7 @@
         <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>46.1</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="16">
@@ -3673,16 +3677,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>894.2</v>
+        <v>896.1</v>
       </c>
       <c r="D24" t="n">
-        <v>62.9</v>
+        <v>60</v>
       </c>
       <c r="E24" t="n">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F24" t="n">
         <v>982</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>40.7</v>
+        <v>41.1</v>
       </c>
       <c r="E10" t="n">
-        <v>38.9</v>
+        <v>43.9</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,10 +768,10 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>853.9</v>
+        <v>903.9</v>
       </c>
       <c r="I10" t="n">
-        <v>790.9</v>
+        <v>794.3</v>
       </c>
       <c r="J10" t="n">
         <v>928</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,6 +1116,11 @@
           <t>9/24/26</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>9/25/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1188,6 +1193,7 @@
       <c r="X2" t="n">
         <v>982</v>
       </c>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1260,6 +1266,7 @@
       <c r="X3" t="n">
         <v>917</v>
       </c>
+      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1328,6 +1335,7 @@
       <c r="X4" t="n">
         <v>906</v>
       </c>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1392,6 +1400,7 @@
       <c r="X5" t="n">
         <v>838</v>
       </c>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1464,6 +1473,7 @@
       <c r="X6" t="n">
         <v>880</v>
       </c>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1538,6 +1548,7 @@
       <c r="X7" t="n">
         <v>972</v>
       </c>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1609,6 +1620,9 @@
       </c>
       <c r="X8" t="n">
         <v>904</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>866</v>
       </c>
     </row>
     <row r="9">
@@ -1642,6 +1656,7 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1710,6 +1725,7 @@
         <v>840</v>
       </c>
       <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1756,6 +1772,7 @@
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1798,6 +1815,7 @@
       <c r="X12" t="n">
         <v>761</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1864,6 +1882,7 @@
       <c r="X13" t="n">
         <v>913</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1916,6 +1935,7 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1988,6 +2008,7 @@
       <c r="X15" t="n">
         <v>888</v>
       </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2024,6 +2045,7 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2036,7 +2058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2160,6 +2182,11 @@
           <t>9/24/26</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>9/25/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2232,6 +2259,7 @@
       <c r="X2" t="n">
         <v>92.40000000000001</v>
       </c>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2304,6 +2332,7 @@
       <c r="X3" t="n">
         <v>63.6</v>
       </c>
+      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2372,6 +2401,7 @@
       <c r="X4" t="n">
         <v>56.6</v>
       </c>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2436,6 +2466,7 @@
       <c r="X5" t="n">
         <v>16.6</v>
       </c>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2508,6 +2539,7 @@
       <c r="X6" t="n">
         <v>39.4</v>
       </c>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2582,6 +2614,7 @@
       <c r="X7" t="n">
         <v>89.7</v>
       </c>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2653,6 +2686,9 @@
       </c>
       <c r="X8" t="n">
         <v>55.2</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -2686,6 +2722,7 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2754,6 +2791,7 @@
         <v>12</v>
       </c>
       <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2800,6 +2838,7 @@
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2842,6 +2881,7 @@
       <c r="X12" t="n">
         <v>1.2</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2908,6 +2948,7 @@
       <c r="X13" t="n">
         <v>61.1</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2960,6 +3001,7 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3032,6 +3074,7 @@
       <c r="X15" t="n">
         <v>44.6</v>
       </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3068,6 +3111,7 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3080,7 +3124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3695,6 +3739,31 @@
         <v>761</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>9/25/26</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>866</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>866</v>
+      </c>
+      <c r="F25" t="n">
+        <v>866</v>
+      </c>
+      <c r="G25" t="n">
+        <v>866</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>71.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>77.7</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1508.7</v>
+        <v>1596.6</v>
       </c>
       <c r="I3" t="n">
-        <v>889</v>
+        <v>891.5</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -756,7 +756,7 @@
         <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="E10" t="n">
         <v>43.9</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>903.9</v>
+        <v>907.9</v>
       </c>
       <c r="I10" t="n">
         <v>794.3</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>26.1</v>
+        <v>25.3</v>
       </c>
       <c r="E14" t="n">
-        <v>13.8</v>
+        <v>12.4</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1.4</v>
       </c>
       <c r="H14" t="n">
-        <v>547.1</v>
+        <v>557.3</v>
       </c>
       <c r="I14" t="n">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="J14" t="n">
         <v>906</v>
@@ -1266,7 +1266,9 @@
       <c r="X3" t="n">
         <v>917</v>
       </c>
-      <c r="Y3" t="inlineStr"/>
+      <c r="Y3" t="n">
+        <v>944</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2008,7 +2010,9 @@
       <c r="X15" t="n">
         <v>888</v>
       </c>
-      <c r="Y15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>766</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2332,7 +2336,9 @@
       <c r="X3" t="n">
         <v>63.6</v>
       </c>
-      <c r="Y3" t="inlineStr"/>
+      <c r="Y3" t="n">
+        <v>87.90000000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2688,7 +2694,7 @@
         <v>55.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -3074,7 +3080,9 @@
       <c r="X15" t="n">
         <v>44.6</v>
       </c>
-      <c r="Y15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>10.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3746,22 +3754,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>866</v>
+        <v>858.7</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E25" t="n">
         <v>866</v>
       </c>
       <c r="F25" t="n">
-        <v>866</v>
+        <v>944</v>
       </c>
       <c r="G25" t="n">
-        <v>866</v>
+        <v>766</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>77.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>84.3</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1634.1</v>
+        <v>1695.9</v>
       </c>
       <c r="I2" t="n">
         <v>897.8</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1596.6</v>
+        <v>1596.3</v>
       </c>
       <c r="I3" t="n">
         <v>891.5</v>
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>52.3</v>
+        <v>53.3</v>
       </c>
       <c r="E7" t="n">
-        <v>55.4</v>
+        <v>56.3</v>
       </c>
       <c r="F7" t="n">
         <v>95.3</v>
@@ -666,10 +666,10 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1151.5</v>
+        <v>1224.9</v>
       </c>
       <c r="I7" t="n">
-        <v>827</v>
+        <v>830.9</v>
       </c>
       <c r="J7" t="n">
         <v>976</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>48.5</v>
+        <v>49.1</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>50.8</v>
       </c>
       <c r="F9" t="n">
         <v>90.2</v>
@@ -734,10 +734,10 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1018.6</v>
+        <v>1081.2</v>
       </c>
       <c r="I9" t="n">
-        <v>822.3</v>
+        <v>825.9</v>
       </c>
       <c r="J9" t="n">
         <v>960</v>
@@ -756,10 +756,10 @@
         <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>41.3</v>
+        <v>40.5</v>
       </c>
       <c r="E10" t="n">
-        <v>43.9</v>
+        <v>38.2</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>907.9</v>
+        <v>891.1</v>
       </c>
       <c r="I10" t="n">
         <v>794.3</v>
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>27.2</v>
+        <v>31.3</v>
       </c>
       <c r="E13" t="n">
-        <v>19.9</v>
+        <v>22.9</v>
       </c>
       <c r="F13" t="n">
         <v>62.8</v>
@@ -870,13 +870,13 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>163</v>
+        <v>218.9</v>
       </c>
       <c r="I13" t="n">
-        <v>761.7</v>
+        <v>780.1</v>
       </c>
       <c r="J13" t="n">
-        <v>849</v>
+        <v>891</v>
       </c>
     </row>
     <row r="14">
@@ -892,7 +892,7 @@
         <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>25.3</v>
+        <v>24.9</v>
       </c>
       <c r="E14" t="n">
         <v>12.4</v>
@@ -901,10 +901,10 @@
         <v>84.09999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H14" t="n">
-        <v>557.3</v>
+        <v>548.4</v>
       </c>
       <c r="I14" t="n">
         <v>744</v>
@@ -1193,7 +1193,9 @@
       <c r="X2" t="n">
         <v>982</v>
       </c>
-      <c r="Y2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>899</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1475,7 +1477,9 @@
       <c r="X6" t="n">
         <v>880</v>
       </c>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>900</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1550,7 +1554,9 @@
       <c r="X7" t="n">
         <v>972</v>
       </c>
-      <c r="Y7" t="inlineStr"/>
+      <c r="Y7" t="n">
+        <v>916</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1817,7 +1823,9 @@
       <c r="X12" t="n">
         <v>761</v>
       </c>
-      <c r="Y12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>891</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2263,7 +2271,9 @@
       <c r="X2" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="Y2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>61.8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2337,7 +2347,7 @@
         <v>63.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>87.90000000000001</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2555,9 @@
       <c r="X6" t="n">
         <v>39.4</v>
       </c>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>62.6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2620,7 +2632,9 @@
       <c r="X7" t="n">
         <v>89.7</v>
       </c>
-      <c r="Y7" t="inlineStr"/>
+      <c r="Y7" t="n">
+        <v>73.40000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2694,7 +2708,7 @@
         <v>55.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>54</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="9">
@@ -2887,7 +2901,9 @@
       <c r="X12" t="n">
         <v>1.2</v>
       </c>
-      <c r="Y12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>55.9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3081,7 +3097,7 @@
         <v>44.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="16">
@@ -3754,16 +3770,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>858.7</v>
+        <v>883.1</v>
       </c>
       <c r="D25" t="n">
-        <v>72.90000000000001</v>
+        <v>52.6</v>
       </c>
       <c r="E25" t="n">
-        <v>866</v>
+        <v>899</v>
       </c>
       <c r="F25" t="n">
         <v>944</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="E2" t="n">
         <v>82</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1695.9</v>
+        <v>1697.8</v>
       </c>
       <c r="I2" t="n">
         <v>897.8</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1596.3</v>
+        <v>1598.3</v>
       </c>
       <c r="I3" t="n">
         <v>891.5</v>
@@ -654,7 +654,7 @@
         <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1224.9</v>
+        <v>1227.1</v>
       </c>
       <c r="I7" t="n">
         <v>830.9</v>
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>52.2</v>
+        <v>51.6</v>
       </c>
       <c r="E8" t="n">
-        <v>63.6</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
         <v>91.7</v>
@@ -700,10 +700,10 @@
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>887</v>
+        <v>929.2</v>
       </c>
       <c r="I8" t="n">
-        <v>840.1</v>
+        <v>841.8</v>
       </c>
       <c r="J8" t="n">
         <v>985</v>
@@ -722,7 +722,7 @@
         <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E9" t="n">
         <v>50.8</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1081.2</v>
+        <v>1083</v>
       </c>
       <c r="I9" t="n">
         <v>825.9</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>891.1</v>
+        <v>891.4</v>
       </c>
       <c r="I10" t="n">
         <v>794.3</v>
@@ -858,7 +858,7 @@
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="E13" t="n">
         <v>22.9</v>
@@ -870,7 +870,7 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>218.9</v>
+        <v>220.4</v>
       </c>
       <c r="I13" t="n">
         <v>780.1</v>
@@ -901,10 +901,10 @@
         <v>84.09999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>548.4</v>
+        <v>548.1</v>
       </c>
       <c r="I14" t="n">
         <v>744</v>
@@ -1404,7 +1404,9 @@
       <c r="X5" t="n">
         <v>838</v>
       </c>
-      <c r="Y5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>872</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2272,7 +2274,7 @@
         <v>92.40000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>61.8</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="3">
@@ -2347,7 +2349,7 @@
         <v>63.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>87.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2482,7 +2484,9 @@
       <c r="X5" t="n">
         <v>16.6</v>
       </c>
-      <c r="Y5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>42.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2556,7 +2560,7 @@
         <v>39.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>62.6</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2633,7 +2637,7 @@
         <v>89.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>73.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2708,7 +2712,7 @@
         <v>55.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>37.2</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="9">
@@ -2902,7 +2906,7 @@
         <v>1.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>55.9</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="13">
@@ -3097,7 +3101,7 @@
         <v>44.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3770,16 +3774,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" t="n">
-        <v>883.1</v>
+        <v>881.8</v>
       </c>
       <c r="D25" t="n">
-        <v>52.6</v>
+        <v>49.4</v>
       </c>
       <c r="E25" t="n">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="F25" t="n">
         <v>944</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>77.2</v>
+        <v>76.8</v>
       </c>
       <c r="E2" t="n">
         <v>82</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1697.8</v>
+        <v>1689.6</v>
       </c>
       <c r="I2" t="n">
         <v>897.8</v>
@@ -518,7 +518,7 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>72.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>78</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1598.3</v>
+        <v>1592</v>
       </c>
       <c r="I3" t="n">
         <v>891.5</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>66.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>77.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1188.9</v>
+        <v>1281.5</v>
       </c>
       <c r="I4" t="n">
-        <v>863.9</v>
+        <v>869.5</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -654,7 +654,7 @@
         <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>53.4</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1227.1</v>
+        <v>1218.9</v>
       </c>
       <c r="I7" t="n">
         <v>830.9</v>
@@ -688,7 +688,7 @@
         <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>51.6</v>
+        <v>51.3</v>
       </c>
       <c r="E8" t="n">
         <v>61</v>
@@ -700,7 +700,7 @@
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>929.2</v>
+        <v>922.9</v>
       </c>
       <c r="I8" t="n">
         <v>841.8</v>
@@ -722,7 +722,7 @@
         <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>49.2</v>
+        <v>48.9</v>
       </c>
       <c r="E9" t="n">
         <v>50.8</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1083</v>
+        <v>1074.8</v>
       </c>
       <c r="I9" t="n">
         <v>825.9</v>
@@ -756,7 +756,7 @@
         <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="E10" t="n">
         <v>38.2</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>891.4</v>
+        <v>885.8</v>
       </c>
       <c r="I10" t="n">
         <v>794.3</v>
@@ -858,7 +858,7 @@
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>31.5</v>
+        <v>30.4</v>
       </c>
       <c r="E13" t="n">
         <v>22.9</v>
@@ -870,7 +870,7 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>220.4</v>
+        <v>212.6</v>
       </c>
       <c r="I13" t="n">
         <v>780.1</v>
@@ -1894,7 +1894,9 @@
       <c r="X13" t="n">
         <v>913</v>
       </c>
-      <c r="Y13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>970</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2274,7 +2276,7 @@
         <v>92.40000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>63.7</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="3">
@@ -2349,7 +2351,7 @@
         <v>63.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>89.59999999999999</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="4">
@@ -2485,7 +2487,7 @@
         <v>16.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>42.2</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="6">
@@ -2560,7 +2562,7 @@
         <v>39.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>64.40000000000001</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="7">
@@ -2637,7 +2639,7 @@
         <v>89.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>75.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2712,7 +2714,7 @@
         <v>55.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>37.5</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="9">
@@ -2906,7 +2908,7 @@
         <v>1.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>57.4</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="13">
@@ -2974,7 +2976,9 @@
       <c r="X13" t="n">
         <v>61.1</v>
       </c>
-      <c r="Y13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>92.59999999999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3774,19 +3778,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" t="n">
-        <v>881.8</v>
+        <v>891.6</v>
       </c>
       <c r="D25" t="n">
-        <v>49.4</v>
+        <v>54.2</v>
       </c>
       <c r="E25" t="n">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="F25" t="n">
-        <v>944</v>
+        <v>970</v>
       </c>
       <c r="G25" t="n">
         <v>766</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>40.3</v>
+        <v>40.7</v>
       </c>
       <c r="E10" t="n">
-        <v>38.2</v>
+        <v>38.9</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,10 +768,10 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>885.8</v>
+        <v>935.8</v>
       </c>
       <c r="I10" t="n">
-        <v>794.3</v>
+        <v>794.2</v>
       </c>
       <c r="J10" t="n">
         <v>928</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1121,6 +1121,11 @@
           <t>9/25/26</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>9/26/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1196,6 +1201,7 @@
       <c r="Y2" t="n">
         <v>899</v>
       </c>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1271,6 +1277,7 @@
       <c r="Y3" t="n">
         <v>944</v>
       </c>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1340,6 +1347,7 @@
         <v>906</v>
       </c>
       <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1407,6 +1415,7 @@
       <c r="Y5" t="n">
         <v>872</v>
       </c>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1482,6 +1491,7 @@
       <c r="Y6" t="n">
         <v>900</v>
       </c>
+      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1559,6 +1569,7 @@
       <c r="Y7" t="n">
         <v>916</v>
       </c>
+      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1633,6 +1644,9 @@
       </c>
       <c r="Y8" t="n">
         <v>866</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>792</v>
       </c>
     </row>
     <row r="9">
@@ -1667,6 +1681,7 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1736,6 +1751,7 @@
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1783,6 +1799,7 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1828,6 +1845,7 @@
       <c r="Y12" t="n">
         <v>891</v>
       </c>
+      <c r="Z12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1897,6 +1915,7 @@
       <c r="Y13" t="n">
         <v>970</v>
       </c>
+      <c r="Z13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1950,6 +1969,7 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2025,6 +2045,7 @@
       <c r="Y15" t="n">
         <v>766</v>
       </c>
+      <c r="Z15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2062,6 +2083,7 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2074,7 +2096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2203,6 +2225,11 @@
           <t>9/25/26</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>9/26/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2278,6 +2305,7 @@
       <c r="Y2" t="n">
         <v>55.5</v>
       </c>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2353,6 +2381,7 @@
       <c r="Y3" t="n">
         <v>83.3</v>
       </c>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2422,6 +2451,7 @@
         <v>56.6</v>
       </c>
       <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2489,6 +2519,7 @@
       <c r="Y5" t="n">
         <v>35.9</v>
       </c>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2564,6 +2595,7 @@
       <c r="Y6" t="n">
         <v>56.2</v>
       </c>
+      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2641,6 +2673,7 @@
       <c r="Y7" t="n">
         <v>67.40000000000001</v>
       </c>
+      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2715,6 +2748,9 @@
       </c>
       <c r="Y8" t="n">
         <v>31.9</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -2749,6 +2785,7 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2818,6 +2855,7 @@
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2865,6 +2903,7 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2910,6 +2949,7 @@
       <c r="Y12" t="n">
         <v>49.6</v>
       </c>
+      <c r="Z12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2979,6 +3019,7 @@
       <c r="Y13" t="n">
         <v>92.59999999999999</v>
       </c>
+      <c r="Z13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3032,6 +3073,7 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3107,6 +3149,7 @@
       <c r="Y15" t="n">
         <v>1</v>
       </c>
+      <c r="Z15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3144,6 +3187,7 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3156,7 +3200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3796,6 +3840,31 @@
         <v>766</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>9/26/26</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>792</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>792</v>
+      </c>
+      <c r="F26" t="n">
+        <v>792</v>
+      </c>
+      <c r="G26" t="n">
+        <v>792</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -756,10 +756,10 @@
         <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>40.7</v>
+        <v>39.2</v>
       </c>
       <c r="E10" t="n">
-        <v>38.9</v>
+        <v>37.4</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>935.8</v>
+        <v>901.7</v>
       </c>
       <c r="I10" t="n">
         <v>794.2</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>24.9</v>
+        <v>27.5</v>
       </c>
       <c r="E14" t="n">
-        <v>12.4</v>
+        <v>13.8</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>548.1</v>
+        <v>632.2</v>
       </c>
       <c r="I14" t="n">
-        <v>744</v>
+        <v>749.6</v>
       </c>
       <c r="J14" t="n">
         <v>906</v>
@@ -2045,7 +2045,9 @@
       <c r="Y15" t="n">
         <v>766</v>
       </c>
-      <c r="Z15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>872</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2750,7 +2752,7 @@
         <v>31.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>50</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="9">
@@ -3149,7 +3151,9 @@
       <c r="Y15" t="n">
         <v>1</v>
       </c>
-      <c r="Z15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3847,19 +3851,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>792</v>
+        <v>832</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>792</v>
+        <v>832</v>
       </c>
       <c r="F26" t="n">
-        <v>792</v>
+        <v>872</v>
       </c>
       <c r="G26" t="n">
         <v>792</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>76.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>79.7</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,10 +496,10 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1689.6</v>
+        <v>1762.6</v>
       </c>
       <c r="I2" t="n">
-        <v>897.8</v>
+        <v>897.9</v>
       </c>
       <c r="J2" t="n">
         <v>991</v>
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>54.3</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -666,10 +666,10 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1218.9</v>
+        <v>1302.7</v>
       </c>
       <c r="I7" t="n">
-        <v>830.9</v>
+        <v>834.5</v>
       </c>
       <c r="J7" t="n">
         <v>976</v>
@@ -756,7 +756,7 @@
         <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>39.2</v>
+        <v>38.7</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>901.7</v>
+        <v>891</v>
       </c>
       <c r="I10" t="n">
         <v>794.2</v>
@@ -892,7 +892,7 @@
         <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>27.5</v>
+        <v>26.1</v>
       </c>
       <c r="E14" t="n">
         <v>13.8</v>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>632.2</v>
+        <v>599.3</v>
       </c>
       <c r="I14" t="n">
         <v>749.6</v>
@@ -1201,7 +1201,9 @@
       <c r="Y2" t="n">
         <v>899</v>
       </c>
-      <c r="Z2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>900</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1569,7 +1571,9 @@
       <c r="Y7" t="n">
         <v>916</v>
       </c>
-      <c r="Z7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>918</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2307,7 +2311,9 @@
       <c r="Y2" t="n">
         <v>55.5</v>
       </c>
-      <c r="Z2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2675,7 +2681,9 @@
       <c r="Y7" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="Z7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>83.8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2752,7 +2760,7 @@
         <v>31.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.9</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="9">
@@ -3152,7 +3160,7 @@
         <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>84.09999999999999</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="16">
@@ -3851,19 +3859,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>832</v>
+        <v>870.5</v>
       </c>
       <c r="D26" t="n">
-        <v>40</v>
+        <v>48.2</v>
       </c>
       <c r="E26" t="n">
-        <v>832</v>
+        <v>886</v>
       </c>
       <c r="F26" t="n">
-        <v>872</v>
+        <v>918</v>
       </c>
       <c r="G26" t="n">
         <v>792</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>76.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>79.7</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1762.6</v>
+        <v>1769.5</v>
       </c>
       <c r="I2" t="n">
         <v>897.9</v>
@@ -654,7 +654,7 @@
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>54.3</v>
+        <v>54.5</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1302.7</v>
+        <v>1307.6</v>
       </c>
       <c r="I7" t="n">
         <v>834.5</v>
@@ -756,7 +756,7 @@
         <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="I10" t="n">
         <v>794.2</v>
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>30.4</v>
+        <v>28.8</v>
       </c>
       <c r="E13" t="n">
-        <v>22.9</v>
+        <v>20.4</v>
       </c>
       <c r="F13" t="n">
         <v>62.8</v>
@@ -870,10 +870,10 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>212.6</v>
+        <v>230.6</v>
       </c>
       <c r="I13" t="n">
-        <v>780.1</v>
+        <v>784.5</v>
       </c>
       <c r="J13" t="n">
         <v>891</v>
@@ -892,7 +892,7 @@
         <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>26.1</v>
+        <v>26.5</v>
       </c>
       <c r="E14" t="n">
         <v>13.8</v>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>599.3</v>
+        <v>608.4</v>
       </c>
       <c r="I14" t="n">
         <v>749.6</v>
@@ -1849,7 +1849,9 @@
       <c r="Y12" t="n">
         <v>891</v>
       </c>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>815</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2312,7 +2314,7 @@
         <v>55.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>73</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2682,7 +2684,7 @@
         <v>67.40000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>83.8</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="8">
@@ -2760,7 +2762,7 @@
         <v>31.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2959,7 +2961,9 @@
       <c r="Y12" t="n">
         <v>49.6</v>
       </c>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3160,7 +3164,7 @@
         <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>51.2</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="16">
@@ -3859,16 +3863,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>870.5</v>
+        <v>859.4</v>
       </c>
       <c r="D26" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="E26" t="n">
-        <v>886</v>
+        <v>872</v>
       </c>
       <c r="F26" t="n">
         <v>918</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -487,7 +487,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>79.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1769.5</v>
+        <v>1768.2</v>
       </c>
       <c r="I2" t="n">
         <v>897.9</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1307.6</v>
+        <v>1307.2</v>
       </c>
       <c r="I7" t="n">
         <v>834.5</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>48.9</v>
+        <v>49.7</v>
       </c>
       <c r="E9" t="n">
-        <v>50.8</v>
+        <v>51.6</v>
       </c>
       <c r="F9" t="n">
         <v>90.2</v>
@@ -734,10 +734,10 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1074.8</v>
+        <v>1144.2</v>
       </c>
       <c r="I9" t="n">
-        <v>825.9</v>
+        <v>828.5</v>
       </c>
       <c r="J9" t="n">
         <v>960</v>
@@ -756,7 +756,7 @@
         <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -768,7 +768,7 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>894</v>
+        <v>891.5</v>
       </c>
       <c r="I10" t="n">
         <v>794.2</v>
@@ -858,10 +858,10 @@
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>28.8</v>
+        <v>28.3</v>
       </c>
       <c r="E13" t="n">
-        <v>20.4</v>
+        <v>19.9</v>
       </c>
       <c r="F13" t="n">
         <v>62.8</v>
@@ -870,7 +870,7 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>230.6</v>
+        <v>226.6</v>
       </c>
       <c r="I13" t="n">
         <v>784.5</v>
@@ -892,7 +892,7 @@
         <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="E14" t="n">
         <v>13.8</v>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>608.4</v>
+        <v>605.1</v>
       </c>
       <c r="I14" t="n">
         <v>749.6</v>
@@ -1493,7 +1493,9 @@
       <c r="Y6" t="n">
         <v>900</v>
       </c>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>887</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2314,7 +2316,7 @@
         <v>55.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>79.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -2605,7 +2607,9 @@
       <c r="Y6" t="n">
         <v>56.2</v>
       </c>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>69.40000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2684,7 +2688,7 @@
         <v>67.40000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>88.7</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="8">
@@ -2762,7 +2766,7 @@
         <v>31.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="9">
@@ -2962,7 +2966,7 @@
         <v>49.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -3164,7 +3168,7 @@
         <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>60.3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
@@ -3863,16 +3867,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>859.4</v>
+        <v>864</v>
       </c>
       <c r="D26" t="n">
-        <v>48.5</v>
+        <v>45.4</v>
       </c>
       <c r="E26" t="n">
-        <v>872</v>
+        <v>879.5</v>
       </c>
       <c r="F26" t="n">
         <v>918</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1768.2</v>
+        <v>1768.4</v>
       </c>
       <c r="I2" t="n">
         <v>897.9</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>67.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="E4" t="n">
-        <v>78.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1281.5</v>
+        <v>1343.4</v>
       </c>
       <c r="I4" t="n">
-        <v>869.5</v>
+        <v>870</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1307.2</v>
+        <v>1307.8</v>
       </c>
       <c r="I7" t="n">
         <v>834.5</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1144.2</v>
+        <v>1143.7</v>
       </c>
       <c r="I9" t="n">
         <v>828.5</v>
@@ -756,7 +756,7 @@
         <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="E10" t="n">
         <v>37.4</v>
@@ -765,10 +765,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>891.5</v>
+        <v>889.8</v>
       </c>
       <c r="I10" t="n">
         <v>794.2</v>
@@ -858,7 +858,7 @@
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>28.3</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
         <v>19.9</v>
@@ -870,7 +870,7 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>226.6</v>
+        <v>224</v>
       </c>
       <c r="I13" t="n">
         <v>784.5</v>
@@ -892,7 +892,7 @@
         <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="E14" t="n">
         <v>13.8</v>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>605.1</v>
+        <v>603.6</v>
       </c>
       <c r="I14" t="n">
         <v>749.6</v>
@@ -1923,7 +1923,9 @@
       <c r="Y13" t="n">
         <v>970</v>
       </c>
-      <c r="Z13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>879</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2316,7 +2318,7 @@
         <v>55.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>78.59999999999999</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="3">
@@ -2608,7 +2610,7 @@
         <v>56.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>69.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2688,7 +2690,7 @@
         <v>67.40000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>88.3</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2766,7 +2768,7 @@
         <v>31.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2966,7 +2968,7 @@
         <v>49.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>14</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="13">
@@ -3037,7 +3039,9 @@
       <c r="Y13" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="Z13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>61.9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3168,7 +3172,7 @@
         <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>57</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="16">
@@ -3867,16 +3871,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>864</v>
+        <v>866.1</v>
       </c>
       <c r="D26" t="n">
-        <v>45.4</v>
+        <v>42.4</v>
       </c>
       <c r="E26" t="n">
-        <v>879.5</v>
+        <v>879</v>
       </c>
       <c r="F26" t="n">
         <v>918</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="E2" t="n">
-        <v>79.7</v>
+        <v>81.2</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1768.4</v>
+        <v>1770.8</v>
       </c>
       <c r="I2" t="n">
         <v>897.9</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>72.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>77.7</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1592</v>
+        <v>1632.3</v>
       </c>
       <c r="I3" t="n">
-        <v>891.5</v>
+        <v>890</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -552,7 +552,7 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>67.2</v>
+        <v>67.3</v>
       </c>
       <c r="E4" t="n">
         <v>77.40000000000001</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1343.4</v>
+        <v>1345.5</v>
       </c>
       <c r="I4" t="n">
         <v>870</v>
@@ -654,7 +654,7 @@
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>54.5</v>
+        <v>54.6</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1307.8</v>
+        <v>1309.8</v>
       </c>
       <c r="I7" t="n">
         <v>834.5</v>
@@ -722,7 +722,7 @@
         <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E9" t="n">
         <v>51.6</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1143.7</v>
+        <v>1146</v>
       </c>
       <c r="I9" t="n">
         <v>828.5</v>
@@ -765,10 +765,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>889.8</v>
+        <v>889.2</v>
       </c>
       <c r="I10" t="n">
         <v>794.2</v>
@@ -858,7 +858,7 @@
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="E13" t="n">
         <v>19.9</v>
@@ -870,7 +870,7 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>224</v>
+        <v>223.2</v>
       </c>
       <c r="I13" t="n">
         <v>784.5</v>
@@ -892,7 +892,7 @@
         <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="E14" t="n">
         <v>13.8</v>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>603.6</v>
+        <v>605.3</v>
       </c>
       <c r="I14" t="n">
         <v>749.6</v>
@@ -1279,7 +1279,9 @@
       <c r="Y3" t="n">
         <v>944</v>
       </c>
-      <c r="Z3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>855</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2318,7 +2320,7 @@
         <v>55.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>78.8</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="3">
@@ -2395,7 +2397,9 @@
       <c r="Y3" t="n">
         <v>83.3</v>
       </c>
-      <c r="Z3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>40.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2610,7 +2614,7 @@
         <v>56.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>68.90000000000001</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="7">
@@ -2690,7 +2694,7 @@
         <v>67.40000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>88.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2768,7 +2772,7 @@
         <v>31.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
@@ -2968,7 +2972,7 @@
         <v>49.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>11.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="13">
@@ -3040,7 +3044,7 @@
         <v>92.59999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>61.9</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3172,7 +3176,7 @@
         <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>55.5</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="16">
@@ -3871,16 +3875,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" t="n">
-        <v>866.1</v>
+        <v>864.8</v>
       </c>
       <c r="D26" t="n">
-        <v>42.4</v>
+        <v>39.8</v>
       </c>
       <c r="E26" t="n">
-        <v>879</v>
+        <v>875.5</v>
       </c>
       <c r="F26" t="n">
         <v>918</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>54.6</v>
+        <v>54.4</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -666,10 +666,10 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1309.8</v>
+        <v>1359.8</v>
       </c>
       <c r="I7" t="n">
-        <v>834.5</v>
+        <v>834</v>
       </c>
       <c r="J7" t="n">
         <v>976</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1126,6 +1126,11 @@
           <t>9/26/26</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>9/27/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1204,6 +1209,7 @@
       <c r="Z2" t="n">
         <v>900</v>
       </c>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1282,6 +1288,7 @@
       <c r="Z3" t="n">
         <v>855</v>
       </c>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1352,6 +1359,7 @@
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1420,6 +1428,7 @@
         <v>872</v>
       </c>
       <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1498,6 +1507,7 @@
       <c r="Z6" t="n">
         <v>887</v>
       </c>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1578,6 +1588,9 @@
       <c r="Z7" t="n">
         <v>918</v>
       </c>
+      <c r="AA7" t="n">
+        <v>821</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1656,6 +1669,7 @@
       <c r="Z8" t="n">
         <v>792</v>
       </c>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1690,6 +1704,7 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1760,6 +1775,7 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1808,6 +1824,7 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1856,6 +1873,7 @@
       <c r="Z12" t="n">
         <v>815</v>
       </c>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1928,6 +1946,7 @@
       <c r="Z13" t="n">
         <v>879</v>
       </c>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1982,6 +2001,7 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2060,6 +2080,7 @@
       <c r="Z15" t="n">
         <v>872</v>
       </c>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2098,6 +2119,7 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2110,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2244,6 +2266,11 @@
           <t>9/26/26</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>9/27/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2322,6 +2349,7 @@
       <c r="Z2" t="n">
         <v>81.2</v>
       </c>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2400,6 +2428,7 @@
       <c r="Z3" t="n">
         <v>40.3</v>
       </c>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2470,6 +2499,7 @@
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2538,6 +2568,7 @@
         <v>35.9</v>
       </c>
       <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2616,6 +2647,7 @@
       <c r="Z6" t="n">
         <v>71.2</v>
       </c>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2696,6 +2728,9 @@
       <c r="Z7" t="n">
         <v>90.90000000000001</v>
       </c>
+      <c r="AA7" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2774,6 +2809,7 @@
       <c r="Z8" t="n">
         <v>3.4</v>
       </c>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2808,6 +2844,7 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2878,6 +2915,7 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2926,6 +2964,7 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2974,6 +3013,7 @@
       <c r="Z12" t="n">
         <v>10.6</v>
       </c>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3046,6 +3086,7 @@
       <c r="Z13" t="n">
         <v>64</v>
       </c>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3100,6 +3141,7 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3178,6 +3220,7 @@
       <c r="Z15" t="n">
         <v>57.2</v>
       </c>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3216,6 +3259,7 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3228,7 +3272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3893,6 +3937,31 @@
         <v>792</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>9/27/26</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>821</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>821</v>
+      </c>
+      <c r="F27" t="n">
+        <v>821</v>
+      </c>
+      <c r="G27" t="n">
+        <v>821</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>67.3</v>
+        <v>68.3</v>
       </c>
       <c r="E4" t="n">
-        <v>77.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1345.5</v>
+        <v>1433.6</v>
       </c>
       <c r="I4" t="n">
-        <v>870</v>
+        <v>870.3</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -654,7 +654,7 @@
         <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1359.8</v>
+        <v>1363.2</v>
       </c>
       <c r="I7" t="n">
         <v>834</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>49.8</v>
+        <v>48.2</v>
       </c>
       <c r="E9" t="n">
-        <v>51.6</v>
+        <v>50.8</v>
       </c>
       <c r="F9" t="n">
         <v>90.2</v>
@@ -734,10 +734,10 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1146</v>
+        <v>1156.3</v>
       </c>
       <c r="I9" t="n">
-        <v>828.5</v>
+        <v>825.3</v>
       </c>
       <c r="J9" t="n">
         <v>960</v>
@@ -1507,7 +1507,9 @@
       <c r="Z6" t="n">
         <v>887</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>752</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1946,7 +1948,9 @@
       <c r="Z13" t="n">
         <v>879</v>
       </c>
-      <c r="AA13" t="inlineStr"/>
+      <c r="AA13" t="n">
+        <v>877</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2647,7 +2651,9 @@
       <c r="Z6" t="n">
         <v>71.2</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>10.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2729,7 +2735,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>50</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="8">
@@ -3086,7 +3092,9 @@
       <c r="Z13" t="n">
         <v>64</v>
       </c>
-      <c r="AA13" t="inlineStr"/>
+      <c r="AA13" t="n">
+        <v>88.09999999999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3944,22 +3952,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>821</v>
+        <v>816.7</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>51.1</v>
       </c>
       <c r="E27" t="n">
         <v>821</v>
       </c>
       <c r="F27" t="n">
-        <v>821</v>
+        <v>877</v>
       </c>
       <c r="G27" t="n">
-        <v>821</v>
+        <v>752</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>77</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>81.2</v>
+        <v>82.8</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,10 +496,10 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1770.8</v>
+        <v>1857.3</v>
       </c>
       <c r="I2" t="n">
-        <v>897.9</v>
+        <v>899.7</v>
       </c>
       <c r="J2" t="n">
         <v>991</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>71</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>77.7</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1632.3</v>
+        <v>1714.3</v>
       </c>
       <c r="I3" t="n">
-        <v>890</v>
+        <v>891.5</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -552,10 +552,10 @@
         <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>68.3</v>
+        <v>66.8</v>
       </c>
       <c r="E4" t="n">
-        <v>78.3</v>
+        <v>76.5</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1433.6</v>
+        <v>1403</v>
       </c>
       <c r="I4" t="n">
         <v>870.3</v>
@@ -654,7 +654,7 @@
         <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>54.5</v>
+        <v>53.5</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1363.2</v>
+        <v>1336.9</v>
       </c>
       <c r="I7" t="n">
         <v>834</v>
@@ -722,7 +722,7 @@
         <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>48.2</v>
+        <v>48</v>
       </c>
       <c r="E9" t="n">
         <v>50.8</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1156.3</v>
+        <v>1151.5</v>
       </c>
       <c r="I9" t="n">
         <v>825.3</v>
@@ -1209,7 +1209,9 @@
       <c r="Z2" t="n">
         <v>900</v>
       </c>
-      <c r="AA2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>941</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1288,7 +1290,9 @@
       <c r="Z3" t="n">
         <v>855</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>928</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2353,7 +2357,9 @@
       <c r="Z2" t="n">
         <v>81.2</v>
       </c>
-      <c r="AA2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>86.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2432,7 +2438,9 @@
       <c r="Z3" t="n">
         <v>40.3</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2652,7 +2660,7 @@
         <v>71.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
@@ -2735,7 +2743,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>53.4</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="8">
@@ -3093,7 +3101,7 @@
         <v>64</v>
       </c>
       <c r="AA13" t="n">
-        <v>88.09999999999999</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="14">
@@ -3952,19 +3960,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>816.7</v>
+        <v>863.8</v>
       </c>
       <c r="D27" t="n">
-        <v>51.1</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>821</v>
+        <v>877</v>
       </c>
       <c r="F27" t="n">
-        <v>877</v>
+        <v>941</v>
       </c>
       <c r="G27" t="n">
         <v>752</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>77.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="E2" t="n">
-        <v>82.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1857.3</v>
+        <v>1854.7</v>
       </c>
       <c r="I2" t="n">
         <v>899.7</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1714.3</v>
+        <v>1713.6</v>
       </c>
       <c r="I3" t="n">
         <v>891.5</v>
@@ -552,7 +552,7 @@
         <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>66.8</v>
+        <v>67.3</v>
       </c>
       <c r="E4" t="n">
         <v>76.5</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1403</v>
+        <v>1414.3</v>
       </c>
       <c r="I4" t="n">
         <v>870.3</v>
@@ -654,7 +654,7 @@
         <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>53.5</v>
+        <v>54.5</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1336.9</v>
+        <v>1362</v>
       </c>
       <c r="I7" t="n">
         <v>834</v>
@@ -722,7 +722,7 @@
         <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>49.1</v>
       </c>
       <c r="E9" t="n">
         <v>50.8</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1151.5</v>
+        <v>1177.5</v>
       </c>
       <c r="I9" t="n">
         <v>825.3</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>26.3</v>
+        <v>25.3</v>
       </c>
       <c r="E14" t="n">
-        <v>13.8</v>
+        <v>12.4</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>605.3</v>
+        <v>607.9</v>
       </c>
       <c r="I14" t="n">
-        <v>749.6</v>
+        <v>741.9</v>
       </c>
       <c r="J14" t="n">
         <v>906</v>
@@ -2088,7 +2088,9 @@
       <c r="Z15" t="n">
         <v>872</v>
       </c>
-      <c r="AA15" t="inlineStr"/>
+      <c r="AA15" t="n">
+        <v>565</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2358,7 +2360,7 @@
         <v>81.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>86.5</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2439,7 +2441,7 @@
         <v>40.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>82</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="4">
@@ -2660,7 +2662,7 @@
         <v>71.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="7">
@@ -2743,7 +2745,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>27.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="8">
@@ -3101,7 +3103,7 @@
         <v>64</v>
       </c>
       <c r="AA13" t="n">
-        <v>57.5</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="14">
@@ -3236,7 +3238,9 @@
       <c r="Z15" t="n">
         <v>57.2</v>
       </c>
-      <c r="AA15" t="inlineStr"/>
+      <c r="AA15" t="n">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3960,22 +3964,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>863.8</v>
+        <v>814</v>
       </c>
       <c r="D27" t="n">
-        <v>70.09999999999999</v>
+        <v>128.4</v>
       </c>
       <c r="E27" t="n">
-        <v>877</v>
+        <v>849</v>
       </c>
       <c r="F27" t="n">
         <v>941</v>
       </c>
       <c r="G27" t="n">
-        <v>752</v>
+        <v>565</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,7 +496,7 @@
         <v>30.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1854.7</v>
+        <v>1858.1</v>
       </c>
       <c r="I2" t="n">
         <v>899.7</v>
@@ -518,7 +518,7 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>71.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E3" t="n">
         <v>78</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1713.6</v>
+        <v>1717.4</v>
       </c>
       <c r="I3" t="n">
         <v>891.5</v>
@@ -552,7 +552,7 @@
         <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>67.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>76.5</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1414.3</v>
+        <v>1419.1</v>
       </c>
       <c r="I4" t="n">
         <v>870.3</v>
@@ -654,7 +654,7 @@
         <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>54.5</v>
+        <v>54.7</v>
       </c>
       <c r="E7" t="n">
         <v>56.3</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1362</v>
+        <v>1367.2</v>
       </c>
       <c r="I7" t="n">
         <v>834</v>
@@ -722,7 +722,7 @@
         <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E9" t="n">
         <v>50.8</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1177.5</v>
+        <v>1181.8</v>
       </c>
       <c r="I9" t="n">
         <v>825.3</v>
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="E10" t="n">
-        <v>37.4</v>
+        <v>49.9</v>
       </c>
       <c r="F10" t="n">
-        <v>90.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4</v>
+        <v>13.8</v>
       </c>
       <c r="H10" t="n">
-        <v>889.2</v>
+        <v>424.1</v>
       </c>
       <c r="I10" t="n">
-        <v>794.2</v>
+        <v>763</v>
       </c>
       <c r="J10" t="n">
-        <v>928</v>
+        <v>916</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="E11" t="n">
-        <v>49.9</v>
+        <v>36.7</v>
       </c>
       <c r="F11" t="n">
-        <v>64.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
-        <v>424.1</v>
+        <v>911</v>
       </c>
       <c r="I11" t="n">
-        <v>763</v>
+        <v>790.3</v>
       </c>
       <c r="J11" t="n">
-        <v>916</v>
+        <v>928</v>
       </c>
     </row>
     <row r="12">
@@ -892,7 +892,7 @@
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="E14" t="n">
         <v>12.4</v>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>607.9</v>
+        <v>608.5</v>
       </c>
       <c r="I14" t="n">
         <v>741.9</v>
@@ -1675,7 +1675,9 @@
       <c r="Z8" t="n">
         <v>792</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
+      <c r="AA8" t="n">
+        <v>700</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2360,7 +2362,7 @@
         <v>81.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>83.90000000000001</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="3">
@@ -2441,7 +2443,7 @@
         <v>40.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>81.3</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2662,7 +2664,7 @@
         <v>71.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>31.5</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="7">
@@ -2745,7 +2747,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>52.2</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="8">
@@ -2825,7 +2827,9 @@
       <c r="Z8" t="n">
         <v>3.4</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
+      <c r="AA8" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3103,7 +3107,7 @@
         <v>64</v>
       </c>
       <c r="AA13" t="n">
-        <v>68.8</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -3239,7 +3243,7 @@
         <v>57.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="16">
@@ -3964,16 +3968,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>814</v>
+        <v>797.7</v>
       </c>
       <c r="D27" t="n">
-        <v>128.4</v>
+        <v>125.4</v>
       </c>
       <c r="E27" t="n">
-        <v>849</v>
+        <v>821</v>
       </c>
       <c r="F27" t="n">
         <v>941</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>33.8</v>
+        <v>34.6</v>
       </c>
       <c r="E12" t="n">
-        <v>33</v>
+        <v>33.4</v>
       </c>
       <c r="F12" t="n">
         <v>74.2</v>
@@ -836,10 +836,10 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>642.1</v>
+        <v>692.1</v>
       </c>
       <c r="I12" t="n">
-        <v>777.5</v>
+        <v>779.2</v>
       </c>
       <c r="J12" t="n">
         <v>924</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA16"/>
+  <dimension ref="A1:AB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,6 +1131,11 @@
           <t>9/27/26</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>9/28/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1212,6 +1217,7 @@
       <c r="AA2" t="n">
         <v>941</v>
       </c>
+      <c r="AB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1293,6 +1299,7 @@
       <c r="AA3" t="n">
         <v>928</v>
       </c>
+      <c r="AB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1364,6 +1371,7 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1433,6 +1441,7 @@
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1514,6 +1523,7 @@
       <c r="AA6" t="n">
         <v>752</v>
       </c>
+      <c r="AB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1597,6 +1607,7 @@
       <c r="AA7" t="n">
         <v>821</v>
       </c>
+      <c r="AB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1678,6 +1689,7 @@
       <c r="AA8" t="n">
         <v>700</v>
       </c>
+      <c r="AB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1713,6 +1725,7 @@
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1784,6 +1797,9 @@
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="n">
+        <v>812</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1833,6 +1849,7 @@
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1882,6 +1899,7 @@
         <v>815</v>
       </c>
       <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1957,6 +1975,7 @@
       <c r="AA13" t="n">
         <v>877</v>
       </c>
+      <c r="AB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2012,6 +2031,7 @@
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2093,6 +2113,7 @@
       <c r="AA15" t="n">
         <v>565</v>
       </c>
+      <c r="AB15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2132,6 +2153,7 @@
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2144,7 +2166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA16"/>
+  <dimension ref="A1:AB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2283,6 +2305,11 @@
           <t>9/27/26</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>9/28/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2364,6 +2391,7 @@
       <c r="AA2" t="n">
         <v>87.3</v>
       </c>
+      <c r="AB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2445,6 +2473,7 @@
       <c r="AA3" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="AB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2516,6 +2545,7 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2585,6 +2615,7 @@
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2666,6 +2697,7 @@
       <c r="AA6" t="n">
         <v>35.8</v>
       </c>
+      <c r="AB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2749,6 +2781,7 @@
       <c r="AA7" t="n">
         <v>57.4</v>
       </c>
+      <c r="AB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2830,6 +2863,7 @@
       <c r="AA8" t="n">
         <v>21.8</v>
       </c>
+      <c r="AB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2865,6 +2899,7 @@
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2936,6 +2971,9 @@
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2985,6 +3023,7 @@
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3034,6 +3073,7 @@
         <v>10.6</v>
       </c>
       <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3109,6 +3149,7 @@
       <c r="AA13" t="n">
         <v>73.59999999999999</v>
       </c>
+      <c r="AB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3164,6 +3205,7 @@
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3245,6 +3287,7 @@
       <c r="AA15" t="n">
         <v>3.2</v>
       </c>
+      <c r="AB15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3284,6 +3327,7 @@
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3296,7 +3340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3986,6 +4030,31 @@
         <v>565</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>9/28/26</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>812</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>812</v>
+      </c>
+      <c r="F28" t="n">
+        <v>812</v>
+      </c>
+      <c r="G28" t="n">
+        <v>812</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>49.2</v>
+        <v>47.9</v>
       </c>
       <c r="E9" t="n">
-        <v>50.8</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
         <v>90.2</v>
@@ -734,10 +734,10 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1181.8</v>
+        <v>1197.7</v>
       </c>
       <c r="I9" t="n">
-        <v>825.3</v>
+        <v>823.3</v>
       </c>
       <c r="J9" t="n">
         <v>960</v>
@@ -824,19 +824,19 @@
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>34.6</v>
+        <v>36.3</v>
       </c>
       <c r="E12" t="n">
         <v>33.4</v>
       </c>
       <c r="F12" t="n">
-        <v>74.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>692.1</v>
+        <v>726.2</v>
       </c>
       <c r="I12" t="n">
         <v>779.2</v>
@@ -1523,7 +1523,9 @@
       <c r="AA6" t="n">
         <v>752</v>
       </c>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>775</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2697,7 +2699,9 @@
       <c r="AA6" t="n">
         <v>35.8</v>
       </c>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2972,7 +2976,7 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="n">
-        <v>50</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -4037,22 +4041,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>812</v>
+        <v>793.5</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="E28" t="n">
-        <v>812</v>
+        <v>793.5</v>
       </c>
       <c r="F28" t="n">
         <v>812</v>
       </c>
       <c r="G28" t="n">
-        <v>812</v>
+        <v>775</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>51.3</v>
+        <v>53.4</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>63.6</v>
       </c>
       <c r="F8" t="n">
         <v>91.7</v>
@@ -700,10 +700,10 @@
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>922.9</v>
+        <v>1014.5</v>
       </c>
       <c r="I8" t="n">
-        <v>841.8</v>
+        <v>846.6</v>
       </c>
       <c r="J8" t="n">
         <v>985</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1197.7</v>
+        <v>1198.6</v>
       </c>
       <c r="I9" t="n">
         <v>823.3</v>
@@ -824,19 +824,19 @@
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>36.3</v>
+        <v>33.8</v>
       </c>
       <c r="E12" t="n">
         <v>33.4</v>
       </c>
       <c r="F12" t="n">
-        <v>84.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>726.2</v>
+        <v>676</v>
       </c>
       <c r="I12" t="n">
         <v>779.2</v>
@@ -1441,7 +1441,9 @@
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>933</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2617,7 +2619,9 @@
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>91.59999999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2700,7 +2704,7 @@
         <v>35.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>15.9</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="7">
@@ -2976,7 +2980,7 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="n">
-        <v>84.09999999999999</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="11">
@@ -4041,19 +4045,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>793.5</v>
+        <v>840</v>
       </c>
       <c r="D28" t="n">
-        <v>18.5</v>
+        <v>67.5</v>
       </c>
       <c r="E28" t="n">
-        <v>793.5</v>
+        <v>812</v>
       </c>
       <c r="F28" t="n">
-        <v>812</v>
+        <v>933</v>
       </c>
       <c r="G28" t="n">
         <v>775</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>71.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>78.2</v>
       </c>
       <c r="F3" t="n">
         <v>94.2</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1717.4</v>
+        <v>1802.3</v>
       </c>
       <c r="I3" t="n">
-        <v>891.5</v>
+        <v>893.5</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -688,7 +688,7 @@
         <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>53.4</v>
+        <v>52.9</v>
       </c>
       <c r="E8" t="n">
         <v>63.6</v>
@@ -700,7 +700,7 @@
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1014.5</v>
+        <v>1005.4</v>
       </c>
       <c r="I8" t="n">
         <v>846.6</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1198.6</v>
+        <v>1192.6</v>
       </c>
       <c r="I9" t="n">
         <v>823.3</v>
@@ -824,10 +824,10 @@
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>33.8</v>
+        <v>33.3</v>
       </c>
       <c r="E12" t="n">
-        <v>33.4</v>
+        <v>28.2</v>
       </c>
       <c r="F12" t="n">
         <v>74.2</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>676</v>
+        <v>665.4</v>
       </c>
       <c r="I12" t="n">
         <v>779.2</v>
@@ -1299,7 +1299,9 @@
       <c r="AA3" t="n">
         <v>928</v>
       </c>
-      <c r="AB3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>940</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2477,7 +2479,9 @@
       <c r="AA3" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="AB3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>84.90000000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2620,7 +2624,7 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>91.59999999999999</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="6">
@@ -2704,7 +2708,7 @@
         <v>35.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>16.8</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="7">
@@ -2980,7 +2984,7 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="n">
-        <v>33.9</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="11">
@@ -4045,19 +4049,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="D28" t="n">
-        <v>67.5</v>
+        <v>72.7</v>
       </c>
       <c r="E28" t="n">
-        <v>812</v>
+        <v>872.5</v>
       </c>
       <c r="F28" t="n">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="G28" t="n">
         <v>775</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -518,7 +518,7 @@
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>72.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>78.2</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1802.3</v>
+        <v>1809.1</v>
       </c>
       <c r="I3" t="n">
         <v>893.5</v>
@@ -617,25 +617,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>60.7</v>
       </c>
       <c r="E6" t="n">
-        <v>67.5</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
         <v>96.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>22.2</v>
+        <v>18.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1196.4</v>
+        <v>1214.6</v>
       </c>
       <c r="I6" t="n">
-        <v>869.4</v>
+        <v>864.7</v>
       </c>
       <c r="J6" t="n">
         <v>959</v>
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>54.7</v>
+        <v>55.9</v>
       </c>
       <c r="E7" t="n">
-        <v>56.3</v>
+        <v>56.8</v>
       </c>
       <c r="F7" t="n">
         <v>95.3</v>
@@ -666,10 +666,10 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1367.2</v>
+        <v>1454.4</v>
       </c>
       <c r="I7" t="n">
-        <v>834</v>
+        <v>837.4</v>
       </c>
       <c r="J7" t="n">
         <v>976</v>
@@ -688,7 +688,7 @@
         <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>52.9</v>
+        <v>53.3</v>
       </c>
       <c r="E8" t="n">
         <v>63.6</v>
@@ -700,7 +700,7 @@
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1005.4</v>
+        <v>1013</v>
       </c>
       <c r="I8" t="n">
         <v>846.6</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>47.7</v>
+        <v>48</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1192.6</v>
+        <v>1199.6</v>
       </c>
       <c r="I9" t="n">
         <v>823.3</v>
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="E10" t="n">
-        <v>49.9</v>
+        <v>36.7</v>
       </c>
       <c r="F10" t="n">
-        <v>64.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>13.8</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>424.1</v>
+        <v>911</v>
       </c>
       <c r="I10" t="n">
-        <v>763</v>
+        <v>790.3</v>
       </c>
       <c r="J10" t="n">
-        <v>916</v>
+        <v>928</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>38</v>
+        <v>36.8</v>
       </c>
       <c r="E11" t="n">
-        <v>36.7</v>
+        <v>36.1</v>
       </c>
       <c r="F11" t="n">
-        <v>90.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>13.8</v>
       </c>
       <c r="H11" t="n">
-        <v>911</v>
+        <v>441.9</v>
       </c>
       <c r="I11" t="n">
-        <v>790.3</v>
+        <v>764</v>
       </c>
       <c r="J11" t="n">
-        <v>928</v>
+        <v>916</v>
       </c>
     </row>
     <row r="12">
@@ -824,10 +824,10 @@
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>33.3</v>
+        <v>33.8</v>
       </c>
       <c r="E12" t="n">
-        <v>28.2</v>
+        <v>33.4</v>
       </c>
       <c r="F12" t="n">
         <v>74.2</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>665.4</v>
+        <v>676.4</v>
       </c>
       <c r="I12" t="n">
         <v>779.2</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
         <v>25.4</v>
       </c>
       <c r="E14" t="n">
-        <v>12.4</v>
+        <v>13.8</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>608.5</v>
+        <v>634.1</v>
       </c>
       <c r="I14" t="n">
-        <v>741.9</v>
+        <v>744</v>
       </c>
       <c r="J14" t="n">
         <v>906</v>
@@ -1373,7 +1373,9 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>776</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1613,7 +1615,9 @@
       <c r="AA7" t="n">
         <v>821</v>
       </c>
-      <c r="AB7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>922</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2037,7 +2041,9 @@
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="AB14" t="n">
+        <v>775</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2119,7 +2125,9 @@
       <c r="AA15" t="n">
         <v>565</v>
       </c>
-      <c r="AB15" t="inlineStr"/>
+      <c r="AB15" t="n">
+        <v>794</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2480,7 +2488,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>84.90000000000001</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="4">
@@ -2553,7 +2561,9 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>18.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2624,7 +2634,7 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>82.5</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2708,7 +2718,7 @@
         <v>35.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.8</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="7">
@@ -2793,7 +2803,9 @@
       <c r="AA7" t="n">
         <v>57.4</v>
       </c>
-      <c r="AB7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>87.2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2984,7 +2996,7 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="n">
-        <v>23.3</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="11">
@@ -3217,7 +3229,9 @@
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="AB14" t="n">
+        <v>17.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3299,7 +3313,9 @@
       <c r="AA15" t="n">
         <v>3.2</v>
       </c>
-      <c r="AB15" t="inlineStr"/>
+      <c r="AB15" t="n">
+        <v>25.6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4049,16 +4065,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C28" t="n">
-        <v>865</v>
+        <v>840.9</v>
       </c>
       <c r="D28" t="n">
-        <v>72.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>872.5</v>
+        <v>803</v>
       </c>
       <c r="F28" t="n">
         <v>940</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,25 +481,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>77.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>82.8</v>
+        <v>81.2</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
       </c>
       <c r="G2" t="n">
-        <v>30.5</v>
+        <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1858.1</v>
+        <v>1877.7</v>
       </c>
       <c r="I2" t="n">
-        <v>899.7</v>
+        <v>894.7</v>
       </c>
       <c r="J2" t="n">
         <v>991</v>
@@ -518,19 +518,19 @@
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>72.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="E3" t="n">
         <v>78.2</v>
       </c>
       <c r="F3" t="n">
-        <v>94.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1809.1</v>
+        <v>1812</v>
       </c>
       <c r="I3" t="n">
         <v>893.5</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>67.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>76.5</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1419.1</v>
+        <v>1461.9</v>
       </c>
       <c r="I4" t="n">
-        <v>870.3</v>
+        <v>868</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -620,7 +620,7 @@
         <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>60.7</v>
+        <v>60.8</v>
       </c>
       <c r="E6" t="n">
         <v>62</v>
@@ -629,10 +629,10 @@
         <v>96.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>18.2</v>
+        <v>20.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1214.6</v>
+        <v>1216.5</v>
       </c>
       <c r="I6" t="n">
         <v>864.7</v>
@@ -654,7 +654,7 @@
         <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>55.9</v>
+        <v>56.1</v>
       </c>
       <c r="E7" t="n">
         <v>56.8</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1454.4</v>
+        <v>1458.2</v>
       </c>
       <c r="I7" t="n">
         <v>837.4</v>
@@ -688,19 +688,19 @@
         <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>53.3</v>
+        <v>53.5</v>
       </c>
       <c r="E8" t="n">
         <v>63.6</v>
       </c>
       <c r="F8" t="n">
-        <v>91.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1013</v>
+        <v>1016.3</v>
       </c>
       <c r="I8" t="n">
         <v>846.6</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1199.6</v>
+        <v>1201.4</v>
       </c>
       <c r="I9" t="n">
         <v>823.3</v>
@@ -790,7 +790,7 @@
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="E11" t="n">
         <v>36.1</v>
@@ -802,7 +802,7 @@
         <v>13.8</v>
       </c>
       <c r="H11" t="n">
-        <v>441.9</v>
+        <v>443.7</v>
       </c>
       <c r="I11" t="n">
         <v>764</v>
@@ -824,7 +824,7 @@
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>33.8</v>
+        <v>34</v>
       </c>
       <c r="E12" t="n">
         <v>33.4</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>676.4</v>
+        <v>680.2</v>
       </c>
       <c r="I12" t="n">
         <v>779.2</v>
@@ -892,7 +892,7 @@
         <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="E14" t="n">
         <v>13.8</v>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>634.1</v>
+        <v>636.9</v>
       </c>
       <c r="I14" t="n">
         <v>744</v>
@@ -1217,7 +1217,9 @@
       <c r="AA2" t="n">
         <v>941</v>
       </c>
-      <c r="AB2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>775</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1985,7 +1987,9 @@
       <c r="AA13" t="n">
         <v>877</v>
       </c>
-      <c r="AB13" t="inlineStr"/>
+      <c r="AB13" t="n">
+        <v>820</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2405,7 +2409,9 @@
       <c r="AA2" t="n">
         <v>87.3</v>
       </c>
-      <c r="AB2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>19.6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2488,7 +2494,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>91.7</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2562,7 +2568,7 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>18.2</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="5">
@@ -2634,7 +2640,7 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>90.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2718,7 +2724,7 @@
         <v>35.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>17.8</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="7">
@@ -2804,7 +2810,7 @@
         <v>57.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>87.2</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
@@ -2996,7 +3002,7 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="n">
-        <v>34.3</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="11">
@@ -3173,7 +3179,9 @@
       <c r="AA13" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="AB13" t="inlineStr"/>
+      <c r="AB13" t="n">
+        <v>42.8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3230,7 +3238,7 @@
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="n">
-        <v>17.8</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="15">
@@ -3314,7 +3322,7 @@
         <v>3.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>25.6</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="16">
@@ -4065,13 +4073,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C28" t="n">
-        <v>840.9</v>
+        <v>832.2</v>
       </c>
       <c r="D28" t="n">
-        <v>71.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="E28" t="n">
         <v>803</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
         <v>48.1</v>
@@ -734,10 +734,10 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1201.4</v>
+        <v>1251.4</v>
       </c>
       <c r="I9" t="n">
-        <v>823.3</v>
+        <v>823.7</v>
       </c>
       <c r="J9" t="n">
         <v>960</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1136,6 +1136,11 @@
           <t>9/28/26</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>9/29/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1220,6 +1225,7 @@
       <c r="AB2" t="n">
         <v>775</v>
       </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1304,6 +1310,7 @@
       <c r="AB3" t="n">
         <v>940</v>
       </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1378,6 +1385,7 @@
       <c r="AB4" t="n">
         <v>776</v>
       </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1450,6 +1458,7 @@
       <c r="AB5" t="n">
         <v>933</v>
       </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1534,6 +1543,9 @@
       <c r="AB6" t="n">
         <v>775</v>
       </c>
+      <c r="AC6" t="n">
+        <v>832</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1620,6 +1632,7 @@
       <c r="AB7" t="n">
         <v>922</v>
       </c>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1702,6 +1715,7 @@
         <v>700</v>
       </c>
       <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1738,6 +1752,7 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1812,6 +1827,7 @@
       <c r="AB10" t="n">
         <v>812</v>
       </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1862,6 +1878,7 @@
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1912,6 +1929,7 @@
       </c>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1990,6 +2008,7 @@
       <c r="AB13" t="n">
         <v>820</v>
       </c>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2048,6 +2067,7 @@
       <c r="AB14" t="n">
         <v>775</v>
       </c>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2132,6 +2152,7 @@
       <c r="AB15" t="n">
         <v>794</v>
       </c>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2172,6 +2193,7 @@
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2184,7 +2206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,6 +2350,11 @@
           <t>9/28/26</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>9/29/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2412,6 +2439,7 @@
       <c r="AB2" t="n">
         <v>19.6</v>
       </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2496,6 +2524,7 @@
       <c r="AB3" t="n">
         <v>94.59999999999999</v>
       </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2570,6 +2599,7 @@
       <c r="AB4" t="n">
         <v>20.1</v>
       </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2642,6 +2672,7 @@
       <c r="AB5" t="n">
         <v>93.40000000000001</v>
       </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2726,6 +2757,9 @@
       <c r="AB6" t="n">
         <v>19.6</v>
       </c>
+      <c r="AC6" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2812,6 +2846,7 @@
       <c r="AB7" t="n">
         <v>91</v>
       </c>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2894,6 +2929,7 @@
         <v>21.8</v>
       </c>
       <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2930,6 +2966,7 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3004,6 +3041,7 @@
       <c r="AB10" t="n">
         <v>38.1</v>
       </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3054,6 +3092,7 @@
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3104,6 +3143,7 @@
       </c>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3182,6 +3222,7 @@
       <c r="AB13" t="n">
         <v>42.8</v>
       </c>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3240,6 +3281,7 @@
       <c r="AB14" t="n">
         <v>19.6</v>
       </c>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3324,6 +3366,7 @@
       <c r="AB15" t="n">
         <v>28.4</v>
       </c>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3364,6 +3407,7 @@
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3376,7 +3420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4091,6 +4135,31 @@
         <v>775</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>9/29/26</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>832</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>832</v>
+      </c>
+      <c r="F29" t="n">
+        <v>832</v>
+      </c>
+      <c r="G29" t="n">
+        <v>832</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>75.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="E2" t="n">
-        <v>81.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,10 +496,10 @@
         <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1877.7</v>
+        <v>1961.8</v>
       </c>
       <c r="I2" t="n">
-        <v>894.7</v>
+        <v>896.5</v>
       </c>
       <c r="J2" t="n">
         <v>991</v>
@@ -722,10 +722,10 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>48.1</v>
+        <v>46.8</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
         <v>90.2</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1251.4</v>
+        <v>1217.3</v>
       </c>
       <c r="I9" t="n">
         <v>823.7</v>
@@ -1225,7 +1225,9 @@
       <c r="AB2" t="n">
         <v>775</v>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>941</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2439,7 +2441,9 @@
       <c r="AB2" t="n">
         <v>19.6</v>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2758,7 +2762,7 @@
         <v>19.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>50</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="7">
@@ -4142,19 +4146,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>832</v>
+        <v>886.5</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>54.5</v>
       </c>
       <c r="E29" t="n">
-        <v>832</v>
+        <v>886.5</v>
       </c>
       <c r="F29" t="n">
-        <v>832</v>
+        <v>941</v>
       </c>
       <c r="G29" t="n">
         <v>832</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>75.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>82.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,7 +496,7 @@
         <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1961.8</v>
+        <v>1948.3</v>
       </c>
       <c r="I2" t="n">
         <v>896.5</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>66.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>76.5</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1461.9</v>
+        <v>1542.4</v>
       </c>
       <c r="I4" t="n">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -722,7 +722,7 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>46.8</v>
+        <v>46.5</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1217.3</v>
+        <v>1209.4</v>
       </c>
       <c r="I9" t="n">
         <v>823.7</v>
@@ -2010,7 +2010,9 @@
       <c r="AB13" t="n">
         <v>820</v>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>959</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2442,7 +2444,7 @@
         <v>19.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>84.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -2762,7 +2764,7 @@
         <v>19.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -3226,7 +3228,9 @@
       <c r="AB13" t="n">
         <v>42.8</v>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>80.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4146,19 +4150,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>886.5</v>
+        <v>910.7</v>
       </c>
       <c r="D29" t="n">
-        <v>54.5</v>
+        <v>56.1</v>
       </c>
       <c r="E29" t="n">
-        <v>886.5</v>
+        <v>941</v>
       </c>
       <c r="F29" t="n">
-        <v>941</v>
+        <v>959</v>
       </c>
       <c r="G29" t="n">
         <v>832</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>74.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E2" t="n">
-        <v>80.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,7 +496,7 @@
         <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1948.3</v>
+        <v>1957.6</v>
       </c>
       <c r="I2" t="n">
         <v>896.5</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>72.5</v>
+        <v>71.5</v>
       </c>
       <c r="E3" t="n">
-        <v>78.2</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
         <v>94.59999999999999</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1812</v>
+        <v>1858.6</v>
       </c>
       <c r="I3" t="n">
-        <v>893.5</v>
+        <v>893.7</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -552,7 +552,7 @@
         <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>67.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E4" t="n">
         <v>76.5</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1542.4</v>
+        <v>1551.2</v>
       </c>
       <c r="I4" t="n">
         <v>872</v>
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>60.8</v>
+        <v>59.6</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>56.6</v>
       </c>
       <c r="F6" t="n">
         <v>96.09999999999999</v>
@@ -632,10 +632,10 @@
         <v>20.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1216.5</v>
+        <v>1251.8</v>
       </c>
       <c r="I6" t="n">
-        <v>864.7</v>
+        <v>865.8</v>
       </c>
       <c r="J6" t="n">
         <v>959</v>
@@ -722,7 +722,7 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1209.4</v>
+        <v>1206.7</v>
       </c>
       <c r="I9" t="n">
         <v>823.7</v>
@@ -1312,7 +1312,9 @@
       <c r="AB3" t="n">
         <v>940</v>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>900</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1387,7 +1389,9 @@
       <c r="AB4" t="n">
         <v>776</v>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>887</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2444,7 +2448,7 @@
         <v>19.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>70.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2530,7 +2534,9 @@
       <c r="AB3" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>46.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2605,7 +2611,9 @@
       <c r="AB4" t="n">
         <v>20.1</v>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>35.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2764,7 +2772,7 @@
         <v>19.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="7">
@@ -3229,7 +3237,7 @@
         <v>42.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>80.5</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="14">
@@ -4150,16 +4158,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>910.7</v>
+        <v>903.8</v>
       </c>
       <c r="D29" t="n">
-        <v>56.1</v>
+        <v>44.5</v>
       </c>
       <c r="E29" t="n">
-        <v>941</v>
+        <v>900</v>
       </c>
       <c r="F29" t="n">
         <v>959</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>75.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>80.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,7 +496,7 @@
         <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1957.6</v>
+        <v>1961.4</v>
       </c>
       <c r="I2" t="n">
         <v>896.5</v>
@@ -518,7 +518,7 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E3" t="n">
         <v>78</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1858.6</v>
+        <v>1861.7</v>
       </c>
       <c r="I3" t="n">
         <v>893.7</v>
@@ -552,7 +552,7 @@
         <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>67.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>76.5</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1551.2</v>
+        <v>1554.1</v>
       </c>
       <c r="I4" t="n">
         <v>872</v>
@@ -620,7 +620,7 @@
         <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
       <c r="E6" t="n">
         <v>56.6</v>
@@ -632,7 +632,7 @@
         <v>20.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1251.8</v>
+        <v>1253.8</v>
       </c>
       <c r="I6" t="n">
         <v>865.8</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1206.7</v>
+        <v>1206.3</v>
       </c>
       <c r="I9" t="n">
         <v>823.7</v>
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>27.9</v>
+        <v>28.5</v>
       </c>
       <c r="E13" t="n">
-        <v>19.9</v>
+        <v>22.9</v>
       </c>
       <c r="F13" t="n">
         <v>62.8</v>
@@ -870,10 +870,10 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>223.2</v>
+        <v>256.9</v>
       </c>
       <c r="I13" t="n">
-        <v>784.5</v>
+        <v>795.4</v>
       </c>
       <c r="J13" t="n">
         <v>891</v>
@@ -1935,7 +1935,9 @@
       </c>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>883</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2448,7 +2450,7 @@
         <v>19.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>79.90000000000001</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="3">
@@ -2535,7 +2537,7 @@
         <v>94.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>46.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="4">
@@ -2612,7 +2614,7 @@
         <v>20.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>35.3</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="5">
@@ -2772,7 +2774,7 @@
         <v>19.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -3157,7 +3159,9 @@
       </c>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>33.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3237,7 +3241,7 @@
         <v>42.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>89.3</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="14">
@@ -4158,16 +4162,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>903.8</v>
+        <v>900.3</v>
       </c>
       <c r="D29" t="n">
-        <v>44.5</v>
+        <v>41.3</v>
       </c>
       <c r="E29" t="n">
-        <v>900</v>
+        <v>893.5</v>
       </c>
       <c r="F29" t="n">
         <v>959</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>75.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="E2" t="n">
-        <v>82.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,7 +496,7 @@
         <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1961.4</v>
+        <v>1964</v>
       </c>
       <c r="I2" t="n">
         <v>896.5</v>
@@ -518,7 +518,7 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>71.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="E3" t="n">
         <v>78</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1861.7</v>
+        <v>1871.4</v>
       </c>
       <c r="I3" t="n">
         <v>893.7</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1554.1</v>
+        <v>1554.8</v>
       </c>
       <c r="I4" t="n">
         <v>872</v>
@@ -620,7 +620,7 @@
         <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>59.7</v>
+        <v>60.2</v>
       </c>
       <c r="E6" t="n">
         <v>56.6</v>
@@ -632,7 +632,7 @@
         <v>20.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1253.8</v>
+        <v>1265.2</v>
       </c>
       <c r="I6" t="n">
         <v>865.8</v>
@@ -722,7 +722,7 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>46.4</v>
+        <v>46.7</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1206.3</v>
+        <v>1213.3</v>
       </c>
       <c r="I9" t="n">
         <v>823.7</v>
@@ -858,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>28.5</v>
+        <v>29.8</v>
       </c>
       <c r="E13" t="n">
         <v>22.9</v>
@@ -870,7 +870,7 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>256.9</v>
+        <v>268.6</v>
       </c>
       <c r="I13" t="n">
         <v>795.4</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>25.5</v>
+        <v>24.8</v>
       </c>
       <c r="E14" t="n">
-        <v>13.8</v>
+        <v>12.4</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>636.9</v>
+        <v>643.9</v>
       </c>
       <c r="I14" t="n">
-        <v>744</v>
+        <v>746.8</v>
       </c>
       <c r="J14" t="n">
         <v>906</v>
@@ -2162,7 +2162,9 @@
       <c r="AB15" t="n">
         <v>794</v>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>818</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2450,7 +2452,7 @@
         <v>19.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>83.7</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="3">
@@ -2537,7 +2539,7 @@
         <v>94.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>49.7</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="4">
@@ -2614,7 +2616,7 @@
         <v>20.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>37.3</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="5">
@@ -2774,7 +2776,7 @@
         <v>19.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.9</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="7">
@@ -3160,7 +3162,7 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>33.7</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="13">
@@ -3241,7 +3243,7 @@
         <v>42.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>92.2</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -3386,7 +3388,9 @@
       <c r="AB15" t="n">
         <v>28.4</v>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4162,22 +4166,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" t="n">
-        <v>900.3</v>
+        <v>888.6</v>
       </c>
       <c r="D29" t="n">
-        <v>41.3</v>
+        <v>47.9</v>
       </c>
       <c r="E29" t="n">
-        <v>893.5</v>
+        <v>887</v>
       </c>
       <c r="F29" t="n">
         <v>959</v>
       </c>
       <c r="G29" t="n">
-        <v>832</v>
+        <v>818</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>75.5</v>
+        <v>75.3</v>
       </c>
       <c r="E2" t="n">
-        <v>82.8</v>
+        <v>80.8</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,7 +496,7 @@
         <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1964</v>
+        <v>1958</v>
       </c>
       <c r="I2" t="n">
         <v>896.5</v>
@@ -518,7 +518,7 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>71.7</v>
       </c>
       <c r="E3" t="n">
         <v>78</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1871.4</v>
+        <v>1863.9</v>
       </c>
       <c r="I3" t="n">
         <v>893.7</v>
@@ -552,7 +552,7 @@
         <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>67.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E4" t="n">
         <v>76.5</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1554.8</v>
+        <v>1550.6</v>
       </c>
       <c r="I4" t="n">
         <v>872</v>
@@ -620,7 +620,7 @@
         <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>60.2</v>
+        <v>59.9</v>
       </c>
       <c r="E6" t="n">
         <v>56.6</v>
@@ -632,7 +632,7 @@
         <v>20.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1265.2</v>
+        <v>1258.2</v>
       </c>
       <c r="I6" t="n">
         <v>865.8</v>
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
-        <v>56.1</v>
+        <v>57.3</v>
       </c>
       <c r="E7" t="n">
-        <v>56.8</v>
+        <v>57.4</v>
       </c>
       <c r="F7" t="n">
         <v>95.3</v>
@@ -666,10 +666,10 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1458.2</v>
+        <v>1547.6</v>
       </c>
       <c r="I7" t="n">
-        <v>837.4</v>
+        <v>842</v>
       </c>
       <c r="J7" t="n">
         <v>976</v>
@@ -722,7 +722,7 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1213.3</v>
+        <v>1211.2</v>
       </c>
       <c r="I9" t="n">
         <v>823.7</v>
@@ -858,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>29.8</v>
+        <v>29.1</v>
       </c>
       <c r="E13" t="n">
         <v>22.9</v>
@@ -870,7 +870,7 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>268.6</v>
+        <v>261.9</v>
       </c>
       <c r="I13" t="n">
         <v>795.4</v>
@@ -885,32 +885,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>brhunt</t>
+          <t>cartert</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>24.8</v>
       </c>
       <c r="E14" t="n">
-        <v>12.4</v>
+        <v>25.2</v>
       </c>
       <c r="F14" t="n">
-        <v>84.09999999999999</v>
+        <v>57.5</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H14" t="n">
-        <v>643.9</v>
+        <v>198.5</v>
       </c>
       <c r="I14" t="n">
-        <v>746.8</v>
+        <v>741.5</v>
       </c>
       <c r="J14" t="n">
-        <v>906</v>
+        <v>836</v>
       </c>
     </row>
     <row r="15">
@@ -919,32 +919,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cartert</t>
+          <t>brhunt</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="E15" t="n">
-        <v>25.2</v>
+        <v>12.4</v>
       </c>
       <c r="F15" t="n">
-        <v>57.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>198.5</v>
+        <v>642.8</v>
       </c>
       <c r="I15" t="n">
-        <v>741.5</v>
+        <v>746.8</v>
       </c>
       <c r="J15" t="n">
-        <v>836</v>
+        <v>906</v>
       </c>
     </row>
     <row r="16">
@@ -1638,7 +1638,9 @@
       <c r="AB7" t="n">
         <v>922</v>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>961</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2452,7 +2454,7 @@
         <v>19.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>86.3</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="3">
@@ -2539,7 +2541,7 @@
         <v>94.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>59.4</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="4">
@@ -2616,7 +2618,7 @@
         <v>20.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>48.7</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="5">
@@ -2776,7 +2778,7 @@
         <v>19.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2864,7 +2866,9 @@
       <c r="AB7" t="n">
         <v>91</v>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>89.40000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3162,7 +3166,7 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>45.4</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="13">
@@ -3243,7 +3247,7 @@
         <v>42.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>92.90000000000001</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="14">
@@ -3389,7 +3393,7 @@
         <v>28.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="16">
@@ -4166,19 +4170,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C29" t="n">
-        <v>888.6</v>
+        <v>897.6</v>
       </c>
       <c r="D29" t="n">
-        <v>47.9</v>
+        <v>50.8</v>
       </c>
       <c r="E29" t="n">
-        <v>887</v>
+        <v>893.5</v>
       </c>
       <c r="F29" t="n">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="G29" t="n">
         <v>818</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>75.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>80.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,7 +496,7 @@
         <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1958</v>
+        <v>1961.2</v>
       </c>
       <c r="I2" t="n">
         <v>896.5</v>
@@ -518,7 +518,7 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>78</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1863.9</v>
+        <v>1868.9</v>
       </c>
       <c r="I3" t="n">
         <v>893.7</v>
@@ -552,7 +552,7 @@
         <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>67.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="E4" t="n">
         <v>76.5</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1550.6</v>
+        <v>1552.6</v>
       </c>
       <c r="I4" t="n">
         <v>872</v>
@@ -620,7 +620,7 @@
         <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>59.9</v>
+        <v>60.2</v>
       </c>
       <c r="E6" t="n">
         <v>56.6</v>
@@ -632,7 +632,7 @@
         <v>20.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1258.2</v>
+        <v>1263.3</v>
       </c>
       <c r="I6" t="n">
         <v>865.8</v>
@@ -654,7 +654,7 @@
         <v>27</v>
       </c>
       <c r="D7" t="n">
-        <v>57.3</v>
+        <v>57.4</v>
       </c>
       <c r="E7" t="n">
         <v>57.4</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1547.6</v>
+        <v>1549.5</v>
       </c>
       <c r="I7" t="n">
         <v>842</v>
@@ -722,7 +722,7 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1211.2</v>
+        <v>1213.9</v>
       </c>
       <c r="I9" t="n">
         <v>823.7</v>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>38</v>
+        <v>37.1</v>
       </c>
       <c r="E10" t="n">
-        <v>36.7</v>
+        <v>36</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,10 +768,10 @@
         <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>911</v>
+        <v>926.5</v>
       </c>
       <c r="I10" t="n">
-        <v>790.3</v>
+        <v>792.2</v>
       </c>
       <c r="J10" t="n">
         <v>928</v>
@@ -858,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>29.1</v>
+        <v>29.7</v>
       </c>
       <c r="E13" t="n">
         <v>22.9</v>
@@ -870,7 +870,7 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>261.9</v>
+        <v>266.9</v>
       </c>
       <c r="I13" t="n">
         <v>795.4</v>
@@ -885,32 +885,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cartert</t>
+          <t>brhunt</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
         <v>24.8</v>
       </c>
       <c r="E14" t="n">
-        <v>25.2</v>
+        <v>12.4</v>
       </c>
       <c r="F14" t="n">
-        <v>57.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>198.5</v>
+        <v>644.6</v>
       </c>
       <c r="I14" t="n">
-        <v>741.5</v>
+        <v>746.8</v>
       </c>
       <c r="J14" t="n">
-        <v>836</v>
+        <v>906</v>
       </c>
     </row>
     <row r="15">
@@ -919,32 +919,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>brhunt</t>
+          <t>cartert</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="E15" t="n">
-        <v>12.4</v>
+        <v>25.2</v>
       </c>
       <c r="F15" t="n">
-        <v>84.09999999999999</v>
+        <v>57.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>642.8</v>
+        <v>198.5</v>
       </c>
       <c r="I15" t="n">
-        <v>746.8</v>
+        <v>741.5</v>
       </c>
       <c r="J15" t="n">
-        <v>906</v>
+        <v>836</v>
       </c>
     </row>
     <row r="16">
@@ -1723,7 +1723,9 @@
         <v>700</v>
       </c>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>839</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2454,7 +2456,7 @@
         <v>19.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>80.3</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="3">
@@ -2541,7 +2543,7 @@
         <v>94.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>51.9</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="4">
@@ -2618,7 +2620,7 @@
         <v>20.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>41.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="5">
@@ -2778,7 +2780,7 @@
         <v>19.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="7">
@@ -2867,7 +2869,7 @@
         <v>91</v>
       </c>
       <c r="AC7" t="n">
-        <v>89.40000000000001</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="8">
@@ -2951,7 +2953,9 @@
         <v>21.8</v>
       </c>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>15.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3166,7 +3170,7 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>38.7</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="13">
@@ -3247,7 +3251,7 @@
         <v>42.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>88.7</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="14">
@@ -3393,7 +3397,7 @@
         <v>28.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="16">
@@ -4170,16 +4174,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C29" t="n">
-        <v>897.6</v>
+        <v>891.1</v>
       </c>
       <c r="D29" t="n">
-        <v>50.8</v>
+        <v>51.3</v>
       </c>
       <c r="E29" t="n">
-        <v>893.5</v>
+        <v>887</v>
       </c>
       <c r="F29" t="n">
         <v>961</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>75.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="E2" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,7 +496,7 @@
         <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1961.2</v>
+        <v>1961.8</v>
       </c>
       <c r="I2" t="n">
         <v>896.5</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1868.9</v>
+        <v>1868.4</v>
       </c>
       <c r="I3" t="n">
         <v>893.7</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1552.6</v>
+        <v>1553.4</v>
       </c>
       <c r="I4" t="n">
         <v>872</v>
@@ -620,7 +620,7 @@
         <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>60.2</v>
+        <v>60.1</v>
       </c>
       <c r="E6" t="n">
         <v>56.6</v>
@@ -632,7 +632,7 @@
         <v>20.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1263.3</v>
+        <v>1262.3</v>
       </c>
       <c r="I6" t="n">
         <v>865.8</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1549.5</v>
+        <v>1550.3</v>
       </c>
       <c r="I7" t="n">
         <v>842</v>
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>53.5</v>
+        <v>53.7</v>
       </c>
       <c r="E8" t="n">
-        <v>63.6</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
         <v>93.40000000000001</v>
@@ -700,10 +700,10 @@
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1016.3</v>
+        <v>1074.3</v>
       </c>
       <c r="I8" t="n">
-        <v>846.6</v>
+        <v>849.4</v>
       </c>
       <c r="J8" t="n">
         <v>985</v>
@@ -722,7 +722,7 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1213.9</v>
+        <v>1212.3</v>
       </c>
       <c r="I9" t="n">
         <v>823.7</v>
@@ -756,7 +756,7 @@
         <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="E10" t="n">
         <v>36</v>
@@ -768,7 +768,7 @@
         <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>926.5</v>
+        <v>924.8</v>
       </c>
       <c r="I10" t="n">
         <v>792.2</v>
@@ -858,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="E13" t="n">
         <v>22.9</v>
@@ -870,7 +870,7 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>266.9</v>
+        <v>265.7</v>
       </c>
       <c r="I13" t="n">
         <v>795.4</v>
@@ -885,32 +885,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>brhunt</t>
+          <t>cartert</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>24.8</v>
       </c>
       <c r="E14" t="n">
-        <v>12.4</v>
+        <v>25.2</v>
       </c>
       <c r="F14" t="n">
-        <v>84.09999999999999</v>
+        <v>57.5</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H14" t="n">
-        <v>644.6</v>
+        <v>198.5</v>
       </c>
       <c r="I14" t="n">
-        <v>746.8</v>
+        <v>741.5</v>
       </c>
       <c r="J14" t="n">
-        <v>906</v>
+        <v>836</v>
       </c>
     </row>
     <row r="15">
@@ -919,32 +919,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cartert</t>
+          <t>brhunt</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="E15" t="n">
-        <v>25.2</v>
+        <v>12.4</v>
       </c>
       <c r="F15" t="n">
-        <v>57.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>198.5</v>
+        <v>643.3</v>
       </c>
       <c r="I15" t="n">
-        <v>741.5</v>
+        <v>746.8</v>
       </c>
       <c r="J15" t="n">
-        <v>836</v>
+        <v>906</v>
       </c>
     </row>
     <row r="16">
@@ -1464,7 +1464,9 @@
       <c r="AB5" t="n">
         <v>933</v>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>902</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2456,7 +2458,7 @@
         <v>19.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>83.5</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -2543,7 +2545,7 @@
         <v>94.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>56.9</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="4">
@@ -2620,7 +2622,7 @@
         <v>20.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>46.8</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="5">
@@ -2694,7 +2696,9 @@
       <c r="AB5" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2780,7 +2784,7 @@
         <v>19.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.5</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="7">
@@ -2869,7 +2873,7 @@
         <v>91</v>
       </c>
       <c r="AC7" t="n">
-        <v>91.3</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2954,7 +2958,7 @@
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>15.5</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="9">
@@ -3170,7 +3174,7 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>43.7</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="13">
@@ -3251,7 +3255,7 @@
         <v>42.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>90.7</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="14">
@@ -3397,7 +3401,7 @@
         <v>28.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="16">
@@ -4174,16 +4178,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>891.1</v>
+        <v>892.2</v>
       </c>
       <c r="D29" t="n">
-        <v>51.3</v>
+        <v>48.8</v>
       </c>
       <c r="E29" t="n">
-        <v>887</v>
+        <v>893.5</v>
       </c>
       <c r="F29" t="n">
         <v>961</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
         <v>90.2</v>
@@ -734,10 +734,10 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1212.3</v>
+        <v>1262.3</v>
       </c>
       <c r="I9" t="n">
-        <v>823.7</v>
+        <v>816.8</v>
       </c>
       <c r="J9" t="n">
         <v>960</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AD16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,6 +1141,11 @@
           <t>9/29/26</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>9/30/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1228,6 +1233,7 @@
       <c r="AC2" t="n">
         <v>941</v>
       </c>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1315,6 +1321,7 @@
       <c r="AC3" t="n">
         <v>900</v>
       </c>
+      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1392,6 +1399,7 @@
       <c r="AC4" t="n">
         <v>887</v>
       </c>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1467,6 +1475,7 @@
       <c r="AC5" t="n">
         <v>902</v>
       </c>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1554,6 +1563,9 @@
       <c r="AC6" t="n">
         <v>832</v>
       </c>
+      <c r="AD6" t="n">
+        <v>638</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1643,6 +1655,7 @@
       <c r="AC7" t="n">
         <v>961</v>
       </c>
+      <c r="AD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1728,6 +1741,7 @@
       <c r="AC8" t="n">
         <v>839</v>
       </c>
+      <c r="AD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1765,6 +1779,7 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1840,6 +1855,7 @@
         <v>812</v>
       </c>
       <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1891,6 +1907,7 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1944,6 +1961,7 @@
       <c r="AC12" t="n">
         <v>883</v>
       </c>
+      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2025,6 +2043,7 @@
       <c r="AC13" t="n">
         <v>959</v>
       </c>
+      <c r="AD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2084,6 +2103,7 @@
         <v>775</v>
       </c>
       <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2171,6 +2191,7 @@
       <c r="AC15" t="n">
         <v>818</v>
       </c>
+      <c r="AD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2212,6 +2233,7 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2224,7 +2246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AD16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2373,6 +2395,11 @@
           <t>9/29/26</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>9/30/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2460,6 +2487,7 @@
       <c r="AC2" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2547,6 +2575,7 @@
       <c r="AC3" t="n">
         <v>56.4</v>
       </c>
+      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2624,6 +2653,7 @@
       <c r="AC4" t="n">
         <v>45.8</v>
       </c>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2699,6 +2729,7 @@
       <c r="AC5" t="n">
         <v>58</v>
       </c>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2786,6 +2817,9 @@
       <c r="AC6" t="n">
         <v>10.9</v>
       </c>
+      <c r="AD6" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2875,6 +2909,7 @@
       <c r="AC7" t="n">
         <v>92.09999999999999</v>
       </c>
+      <c r="AD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2960,6 +2995,7 @@
       <c r="AC8" t="n">
         <v>13.8</v>
       </c>
+      <c r="AD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2997,6 +3033,7 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3072,6 +3109,7 @@
         <v>38.1</v>
       </c>
       <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3123,6 +3161,7 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3176,6 +3215,7 @@
       <c r="AC12" t="n">
         <v>42.5</v>
       </c>
+      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3257,6 +3297,7 @@
       <c r="AC13" t="n">
         <v>91.5</v>
       </c>
+      <c r="AD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3316,6 +3357,7 @@
         <v>19.6</v>
       </c>
       <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3403,6 +3445,7 @@
       <c r="AC15" t="n">
         <v>6.4</v>
       </c>
+      <c r="AD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3444,6 +3487,7 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3456,7 +3500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4196,6 +4240,31 @@
         <v>818</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>9/30/26</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>638</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>638</v>
+      </c>
+      <c r="F30" t="n">
+        <v>638</v>
+      </c>
+      <c r="G30" t="n">
+        <v>638</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -722,7 +722,7 @@
         <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>46.8</v>
+        <v>48</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1262.3</v>
+        <v>1296.4</v>
       </c>
       <c r="I9" t="n">
         <v>816.8</v>
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>29.5</v>
+        <v>28.2</v>
       </c>
       <c r="E13" t="n">
-        <v>22.9</v>
+        <v>19.9</v>
       </c>
       <c r="F13" t="n">
         <v>62.8</v>
@@ -870,10 +870,10 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>265.7</v>
+        <v>281.6</v>
       </c>
       <c r="I13" t="n">
-        <v>795.4</v>
+        <v>776.3</v>
       </c>
       <c r="J13" t="n">
         <v>891</v>
@@ -1961,7 +1961,9 @@
       <c r="AC12" t="n">
         <v>883</v>
       </c>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>604</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2818,7 +2820,7 @@
         <v>10.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>50</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -3215,7 +3217,9 @@
       <c r="AC12" t="n">
         <v>42.5</v>
       </c>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4247,22 +4251,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="F30" t="n">
         <v>638</v>
       </c>
       <c r="G30" t="n">
-        <v>638</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>78.2</v>
       </c>
       <c r="F3" t="n">
         <v>94.59999999999999</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1868.4</v>
+        <v>1960.4</v>
       </c>
       <c r="I3" t="n">
-        <v>893.7</v>
+        <v>892.4</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -722,10 +722,10 @@
         <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>47.9</v>
       </c>
       <c r="F9" t="n">
         <v>90.2</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1296.4</v>
+        <v>1241.4</v>
       </c>
       <c r="I9" t="n">
         <v>816.8</v>
@@ -858,10 +858,10 @@
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>28.2</v>
+        <v>28.5</v>
       </c>
       <c r="E13" t="n">
-        <v>19.9</v>
+        <v>21.3</v>
       </c>
       <c r="F13" t="n">
         <v>62.8</v>
@@ -870,7 +870,7 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>281.6</v>
+        <v>285.4</v>
       </c>
       <c r="I13" t="n">
         <v>776.3</v>
@@ -1321,7 +1321,9 @@
       <c r="AC3" t="n">
         <v>900</v>
       </c>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>858</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2577,7 +2579,9 @@
       <c r="AC3" t="n">
         <v>56.4</v>
       </c>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2820,7 +2824,7 @@
         <v>10.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>84.09999999999999</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="7">
@@ -3218,7 +3222,7 @@
         <v>42.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>15.9</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="13">
@@ -4251,19 +4255,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>621</v>
+        <v>700</v>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>112.6</v>
       </c>
       <c r="E30" t="n">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="F30" t="n">
-        <v>638</v>
+        <v>858</v>
       </c>
       <c r="G30" t="n">
         <v>604</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -518,7 +518,7 @@
         <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>72.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="E3" t="n">
         <v>78.2</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1960.4</v>
+        <v>1957.6</v>
       </c>
       <c r="I3" t="n">
         <v>892.4</v>
@@ -722,7 +722,7 @@
         <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>46</v>
+        <v>45.7</v>
       </c>
       <c r="E9" t="n">
         <v>47.9</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1241.4</v>
+        <v>1233</v>
       </c>
       <c r="I9" t="n">
         <v>816.8</v>
@@ -858,10 +858,10 @@
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>28.5</v>
+        <v>27.9</v>
       </c>
       <c r="E13" t="n">
-        <v>21.3</v>
+        <v>19.9</v>
       </c>
       <c r="F13" t="n">
         <v>62.8</v>
@@ -870,7 +870,7 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>285.4</v>
+        <v>278.5</v>
       </c>
       <c r="I13" t="n">
         <v>776.3</v>
@@ -885,32 +885,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cartert</t>
+          <t>brhunt</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>24.8</v>
+        <v>26.7</v>
       </c>
       <c r="E14" t="n">
-        <v>25.2</v>
+        <v>13.8</v>
       </c>
       <c r="F14" t="n">
-        <v>57.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>198.5</v>
+        <v>719.6</v>
       </c>
       <c r="I14" t="n">
-        <v>741.5</v>
+        <v>748.9</v>
       </c>
       <c r="J14" t="n">
-        <v>836</v>
+        <v>906</v>
       </c>
     </row>
     <row r="15">
@@ -919,32 +919,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>brhunt</t>
+          <t>cartert</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="E15" t="n">
-        <v>12.4</v>
+        <v>25.2</v>
       </c>
       <c r="F15" t="n">
-        <v>84.09999999999999</v>
+        <v>57.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>643.3</v>
+        <v>198.5</v>
       </c>
       <c r="I15" t="n">
-        <v>746.8</v>
+        <v>741.5</v>
       </c>
       <c r="J15" t="n">
-        <v>906</v>
+        <v>836</v>
       </c>
     </row>
     <row r="16">
@@ -2195,7 +2195,9 @@
       <c r="AC15" t="n">
         <v>818</v>
       </c>
-      <c r="AD15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>802</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2580,7 +2582,7 @@
         <v>56.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>92</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="4">
@@ -2824,7 +2826,7 @@
         <v>10.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>29.1</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="7">
@@ -3222,7 +3224,7 @@
         <v>42.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>19.7</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="13">
@@ -3453,7 +3455,9 @@
       <c r="AC15" t="n">
         <v>6.4</v>
       </c>
-      <c r="AD15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>76.3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4255,16 +4259,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>700</v>
+        <v>725.5</v>
       </c>
       <c r="D30" t="n">
-        <v>112.6</v>
+        <v>107</v>
       </c>
       <c r="E30" t="n">
-        <v>638</v>
+        <v>720</v>
       </c>
       <c r="F30" t="n">
         <v>858</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
         <v>75.5</v>
       </c>
       <c r="E2" t="n">
-        <v>82.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,10 +496,10 @@
         <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1961.8</v>
+        <v>2039.7</v>
       </c>
       <c r="I2" t="n">
-        <v>896.5</v>
+        <v>893.9</v>
       </c>
       <c r="J2" t="n">
         <v>991</v>
@@ -518,7 +518,7 @@
         <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>78.2</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1957.6</v>
+        <v>1954.5</v>
       </c>
       <c r="I3" t="n">
         <v>892.4</v>
@@ -722,7 +722,7 @@
         <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="E9" t="n">
         <v>47.9</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1233</v>
+        <v>1227.3</v>
       </c>
       <c r="I9" t="n">
         <v>816.8</v>
@@ -858,7 +858,7 @@
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>27.9</v>
+        <v>27.4</v>
       </c>
       <c r="E13" t="n">
         <v>19.9</v>
@@ -870,7 +870,7 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>278.5</v>
+        <v>274.3</v>
       </c>
       <c r="I13" t="n">
         <v>776.3</v>
@@ -892,7 +892,7 @@
         <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>26.7</v>
+        <v>26.4</v>
       </c>
       <c r="E14" t="n">
         <v>13.8</v>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>719.6</v>
+        <v>714</v>
       </c>
       <c r="I14" t="n">
         <v>748.9</v>
@@ -1233,7 +1233,9 @@
       <c r="AC2" t="n">
         <v>941</v>
       </c>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>825</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2493,7 +2495,9 @@
       <c r="AC2" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>77.90000000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2582,7 +2586,7 @@
         <v>56.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>89.2</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2826,7 +2830,7 @@
         <v>10.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>20.7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -3224,7 +3228,7 @@
         <v>42.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>12.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="13">
@@ -3456,7 +3460,7 @@
         <v>6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>76.3</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="16">
@@ -4259,16 +4263,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>725.5</v>
+        <v>745.4</v>
       </c>
       <c r="D30" t="n">
-        <v>107</v>
+        <v>103.7</v>
       </c>
       <c r="E30" t="n">
-        <v>720</v>
+        <v>802</v>
       </c>
       <c r="F30" t="n">
         <v>858</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>75.5</v>
+        <v>75.3</v>
       </c>
       <c r="E2" t="n">
         <v>81.2</v>
@@ -496,7 +496,7 @@
         <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2039.7</v>
+        <v>2034.4</v>
       </c>
       <c r="I2" t="n">
         <v>893.9</v>
@@ -518,7 +518,7 @@
         <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>72.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="E3" t="n">
         <v>78.2</v>
@@ -530,7 +530,7 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1954.5</v>
+        <v>1950.5</v>
       </c>
       <c r="I3" t="n">
         <v>892.4</v>
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>53.7</v>
+        <v>55</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>63.6</v>
       </c>
       <c r="F8" t="n">
         <v>93.40000000000001</v>
@@ -700,10 +700,10 @@
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1074.3</v>
+        <v>1155.1</v>
       </c>
       <c r="I8" t="n">
-        <v>849.4</v>
+        <v>849.6</v>
       </c>
       <c r="J8" t="n">
         <v>985</v>
@@ -722,7 +722,7 @@
         <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
       <c r="E9" t="n">
         <v>47.9</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1227.3</v>
+        <v>1223.4</v>
       </c>
       <c r="I9" t="n">
         <v>816.8</v>
@@ -858,7 +858,7 @@
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="E13" t="n">
         <v>19.9</v>
@@ -870,7 +870,7 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>274.3</v>
+        <v>271.8</v>
       </c>
       <c r="I13" t="n">
         <v>776.3</v>
@@ -892,7 +892,7 @@
         <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="E14" t="n">
         <v>13.8</v>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="I14" t="n">
         <v>748.9</v>
@@ -1479,7 +1479,9 @@
       <c r="AC5" t="n">
         <v>902</v>
       </c>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>853</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2496,7 +2498,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>77.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -2586,7 +2588,7 @@
         <v>56.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>86.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2741,7 +2743,9 @@
       <c r="AC5" t="n">
         <v>58</v>
       </c>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>80.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2830,7 +2834,7 @@
         <v>10.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="7">
@@ -3228,7 +3232,7 @@
         <v>42.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>8.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="13">
@@ -3460,7 +3464,7 @@
         <v>6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>70.7</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="16">
@@ -4263,16 +4267,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>745.4</v>
+        <v>763.3</v>
       </c>
       <c r="D30" t="n">
-        <v>103.7</v>
+        <v>102.8</v>
       </c>
       <c r="E30" t="n">
-        <v>802</v>
+        <v>813.5</v>
       </c>
       <c r="F30" t="n">
         <v>858</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>75.3</v>
+        <v>75</v>
       </c>
       <c r="E2" t="n">
         <v>81.2</v>
@@ -496,7 +496,7 @@
         <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2034.4</v>
+        <v>2023.9</v>
       </c>
       <c r="I2" t="n">
         <v>893.9</v>
@@ -511,32 +511,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pparril</t>
+          <t>waltkin</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>72.2</v>
+        <v>72</v>
       </c>
       <c r="E3" t="n">
-        <v>78.2</v>
+        <v>92.2</v>
       </c>
       <c r="F3" t="n">
-        <v>94.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="G3" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>1950.5</v>
+        <v>288.1</v>
       </c>
       <c r="I3" t="n">
-        <v>892.4</v>
+        <v>888.2</v>
       </c>
       <c r="J3" t="n">
-        <v>997</v>
+        <v>960</v>
       </c>
     </row>
     <row r="4">
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>pparril</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>67.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>76.5</v>
+        <v>77.7</v>
       </c>
       <c r="F4" t="n">
-        <v>93.59999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>11.4</v>
+        <v>31</v>
       </c>
       <c r="H4" t="n">
-        <v>1553.4</v>
+        <v>1941.8</v>
       </c>
       <c r="I4" t="n">
-        <v>872</v>
+        <v>892.4</v>
       </c>
       <c r="J4" t="n">
-        <v>991</v>
+        <v>997</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>waltkin</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>65.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="E5" t="n">
-        <v>91.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>99.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>195.3</v>
+        <v>1626.5</v>
       </c>
       <c r="I5" t="n">
-        <v>869.3</v>
+        <v>871.3</v>
       </c>
       <c r="J5" t="n">
-        <v>960</v>
+        <v>991</v>
       </c>
     </row>
     <row r="6">
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>57.4</v>
+        <v>56.6</v>
       </c>
       <c r="E7" t="n">
-        <v>57.4</v>
+        <v>56.8</v>
       </c>
       <c r="F7" t="n">
         <v>95.3</v>
@@ -666,10 +666,10 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1550.3</v>
+        <v>1586</v>
       </c>
       <c r="I7" t="n">
-        <v>842</v>
+        <v>838.9</v>
       </c>
       <c r="J7" t="n">
         <v>976</v>
@@ -688,7 +688,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>54.6</v>
       </c>
       <c r="E8" t="n">
         <v>63.6</v>
@@ -700,7 +700,7 @@
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1155.1</v>
+        <v>1146.1</v>
       </c>
       <c r="I8" t="n">
         <v>849.6</v>
@@ -722,7 +722,7 @@
         <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="E9" t="n">
         <v>47.9</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1223.4</v>
+        <v>1219.1</v>
       </c>
       <c r="I9" t="n">
         <v>816.8</v>
@@ -858,7 +858,7 @@
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>27.2</v>
+        <v>26.9</v>
       </c>
       <c r="E13" t="n">
         <v>19.9</v>
@@ -870,7 +870,7 @@
         <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>271.8</v>
+        <v>269.2</v>
       </c>
       <c r="I13" t="n">
         <v>776.3</v>
@@ -892,7 +892,7 @@
         <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>26.2</v>
+        <v>25.8</v>
       </c>
       <c r="E14" t="n">
         <v>13.8</v>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>708</v>
+        <v>696.7</v>
       </c>
       <c r="I14" t="n">
         <v>748.9</v>
@@ -1661,7 +1661,9 @@
       <c r="AC7" t="n">
         <v>961</v>
       </c>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>755</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2051,7 +2053,9 @@
       <c r="AC13" t="n">
         <v>959</v>
       </c>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>857</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2243,7 +2247,9 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
+      <c r="AD16" t="n">
+        <v>945</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2498,7 +2504,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>72.59999999999999</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="3">
@@ -2588,7 +2594,7 @@
         <v>56.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>82.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -2744,7 +2750,7 @@
         <v>58</v>
       </c>
       <c r="AD5" t="n">
-        <v>80.8</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="6">
@@ -2834,7 +2840,7 @@
         <v>10.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>11.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="7">
@@ -2925,7 +2931,9 @@
       <c r="AC7" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>35.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3232,7 +3240,7 @@
         <v>42.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13">
@@ -3315,7 +3323,9 @@
       <c r="AC13" t="n">
         <v>91.5</v>
       </c>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>73.09999999999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3464,7 +3474,7 @@
         <v>6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>64.7</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="16">
@@ -3507,7 +3517,9 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
+      <c r="AD16" t="n">
+        <v>92.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4267,19 +4279,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>763.3</v>
+        <v>793</v>
       </c>
       <c r="D30" t="n">
-        <v>102.8</v>
+        <v>104</v>
       </c>
       <c r="E30" t="n">
-        <v>813.5</v>
+        <v>825</v>
       </c>
       <c r="F30" t="n">
-        <v>858</v>
+        <v>945</v>
       </c>
       <c r="G30" t="n">
         <v>604</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="E10" t="n">
-        <v>36</v>
+        <v>36.7</v>
       </c>
       <c r="F10" t="n">
         <v>90.90000000000001</v>
@@ -768,10 +768,10 @@
         <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>924.8</v>
+        <v>974.8</v>
       </c>
       <c r="I10" t="n">
-        <v>792.2</v>
+        <v>785.8</v>
       </c>
       <c r="J10" t="n">
         <v>928</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:AE16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1146,6 +1146,11 @@
           <t>9/30/26</t>
         </is>
       </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>10/1/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1236,6 +1241,7 @@
       <c r="AD2" t="n">
         <v>825</v>
       </c>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1326,6 +1332,7 @@
       <c r="AD3" t="n">
         <v>858</v>
       </c>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1404,6 +1411,7 @@
         <v>887</v>
       </c>
       <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1482,6 +1490,7 @@
       <c r="AD5" t="n">
         <v>853</v>
       </c>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1572,6 +1581,7 @@
       <c r="AD6" t="n">
         <v>638</v>
       </c>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1664,6 +1674,7 @@
       <c r="AD7" t="n">
         <v>755</v>
       </c>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1750,6 +1761,9 @@
         <v>839</v>
       </c>
       <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>624</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1788,6 +1802,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1864,6 +1879,7 @@
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1916,6 +1932,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1972,6 +1989,7 @@
       <c r="AD12" t="n">
         <v>604</v>
       </c>
+      <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2056,6 +2074,7 @@
       <c r="AD13" t="n">
         <v>857</v>
       </c>
+      <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2116,6 +2135,7 @@
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2206,6 +2226,7 @@
       <c r="AD15" t="n">
         <v>802</v>
       </c>
+      <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2250,6 +2271,7 @@
       <c r="AD16" t="n">
         <v>945</v>
       </c>
+      <c r="AE16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2262,7 +2284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:AE16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2416,6 +2438,11 @@
           <t>9/30/26</t>
         </is>
       </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>10/1/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2506,6 +2533,7 @@
       <c r="AD2" t="n">
         <v>62.1</v>
       </c>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2596,6 +2624,7 @@
       <c r="AD3" t="n">
         <v>73.40000000000001</v>
       </c>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2674,6 +2703,7 @@
         <v>45.8</v>
       </c>
       <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2752,6 +2782,7 @@
       <c r="AD5" t="n">
         <v>71.8</v>
       </c>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2842,6 +2873,7 @@
       <c r="AD6" t="n">
         <v>6.8</v>
       </c>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2934,6 +2966,7 @@
       <c r="AD7" t="n">
         <v>35.7</v>
       </c>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3020,6 +3053,9 @@
         <v>13.8</v>
       </c>
       <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3058,6 +3094,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3134,6 +3171,7 @@
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3186,6 +3224,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3242,6 +3281,7 @@
       <c r="AD12" t="n">
         <v>3.5</v>
       </c>
+      <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3326,6 +3366,7 @@
       <c r="AD13" t="n">
         <v>73.09999999999999</v>
       </c>
+      <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3386,6 +3427,7 @@
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3476,6 +3518,7 @@
       <c r="AD15" t="n">
         <v>53.4</v>
       </c>
+      <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3520,6 +3563,7 @@
       <c r="AD16" t="n">
         <v>92.8</v>
       </c>
+      <c r="AE16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3532,7 +3576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4297,6 +4341,31 @@
         <v>604</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>10/1/26</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>624</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>624</v>
+      </c>
+      <c r="F31" t="n">
+        <v>624</v>
+      </c>
+      <c r="G31" t="n">
+        <v>624</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>45.2</v>
+        <v>46.5</v>
       </c>
       <c r="E9" t="n">
-        <v>47.9</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
         <v>90.2</v>
@@ -734,10 +734,10 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1219.1</v>
+        <v>1303.2</v>
       </c>
       <c r="I9" t="n">
-        <v>816.8</v>
+        <v>813.3</v>
       </c>
       <c r="J9" t="n">
         <v>960</v>
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="E10" t="n">
-        <v>36.7</v>
+        <v>36.1</v>
       </c>
       <c r="F10" t="n">
-        <v>90.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4</v>
+        <v>13.8</v>
       </c>
       <c r="H10" t="n">
-        <v>974.8</v>
+        <v>443.7</v>
       </c>
       <c r="I10" t="n">
-        <v>785.8</v>
+        <v>764</v>
       </c>
       <c r="J10" t="n">
-        <v>928</v>
+        <v>916</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>37</v>
+        <v>36.2</v>
       </c>
       <c r="E11" t="n">
-        <v>36.1</v>
+        <v>34</v>
       </c>
       <c r="F11" t="n">
-        <v>64.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
-        <v>443.7</v>
+        <v>940.7</v>
       </c>
       <c r="I11" t="n">
-        <v>764</v>
+        <v>785.8</v>
       </c>
       <c r="J11" t="n">
-        <v>916</v>
+        <v>928</v>
       </c>
     </row>
     <row r="12">
@@ -1581,7 +1581,9 @@
       <c r="AD6" t="n">
         <v>638</v>
       </c>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>719</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2873,7 +2875,9 @@
       <c r="AD6" t="n">
         <v>6.8</v>
       </c>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3054,7 +3058,7 @@
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>50</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="9">
@@ -4348,19 +4352,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>624</v>
+        <v>671.5</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="E31" t="n">
-        <v>624</v>
+        <v>671.5</v>
       </c>
       <c r="F31" t="n">
-        <v>624</v>
+        <v>719</v>
       </c>
       <c r="G31" t="n">
         <v>624</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="E8" t="n">
-        <v>63.6</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
         <v>93.40000000000001</v>
@@ -700,10 +700,10 @@
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1146.1</v>
+        <v>1202.8</v>
       </c>
       <c r="I8" t="n">
-        <v>849.6</v>
+        <v>843.8</v>
       </c>
       <c r="J8" t="n">
         <v>985</v>
@@ -722,7 +722,7 @@
         <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>46.5</v>
+        <v>45.5</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1303.2</v>
+        <v>1273</v>
       </c>
       <c r="I9" t="n">
         <v>813.3</v>
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>36.2</v>
+        <v>36.7</v>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="F11" t="n">
-        <v>90.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>940.7</v>
+        <v>770</v>
       </c>
       <c r="I11" t="n">
-        <v>785.8</v>
+        <v>779.6</v>
       </c>
       <c r="J11" t="n">
-        <v>928</v>
+        <v>924</v>
       </c>
     </row>
     <row r="12">
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="E12" t="n">
         <v>34</v>
       </c>
-      <c r="E12" t="n">
-        <v>33.4</v>
-      </c>
       <c r="F12" t="n">
-        <v>74.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="H12" t="n">
-        <v>680.2</v>
+        <v>931</v>
       </c>
       <c r="I12" t="n">
-        <v>779.2</v>
+        <v>785.8</v>
       </c>
       <c r="J12" t="n">
-        <v>924</v>
+        <v>928</v>
       </c>
     </row>
     <row r="13">
@@ -1490,7 +1490,9 @@
       <c r="AD5" t="n">
         <v>853</v>
       </c>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>723</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1881,7 +1883,9 @@
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>787</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2784,7 +2788,9 @@
       <c r="AD5" t="n">
         <v>71.8</v>
       </c>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>56.7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2876,7 +2882,7 @@
         <v>6.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>84.09999999999999</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="7">
@@ -3058,7 +3064,7 @@
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>15.9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="9">
@@ -3175,7 +3181,9 @@
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>89.8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4352,19 +4360,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>671.5</v>
+        <v>713.2</v>
       </c>
       <c r="D31" t="n">
-        <v>47.5</v>
+        <v>58.2</v>
       </c>
       <c r="E31" t="n">
-        <v>671.5</v>
+        <v>721</v>
       </c>
       <c r="F31" t="n">
-        <v>719</v>
+        <v>787</v>
       </c>
       <c r="G31" t="n">
         <v>624</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>75</v>
+        <v>74.3</v>
       </c>
       <c r="E2" t="n">
-        <v>81.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>97.7</v>
@@ -496,10 +496,10 @@
         <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2023.9</v>
+        <v>2079.9</v>
       </c>
       <c r="I2" t="n">
-        <v>893.9</v>
+        <v>887.6</v>
       </c>
       <c r="J2" t="n">
         <v>991</v>
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>67.8</v>
+        <v>68.5</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>76.5</v>
       </c>
       <c r="F5" t="n">
         <v>93.59999999999999</v>
@@ -598,10 +598,10 @@
         <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1626.5</v>
+        <v>1713.7</v>
       </c>
       <c r="I5" t="n">
-        <v>871.3</v>
+        <v>867.8</v>
       </c>
       <c r="J5" t="n">
         <v>991</v>
@@ -688,10 +688,10 @@
         <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>61.3</v>
       </c>
       <c r="F8" t="n">
         <v>93.40000000000001</v>
@@ -700,7 +700,7 @@
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1202.8</v>
+        <v>1205.1</v>
       </c>
       <c r="I8" t="n">
         <v>843.8</v>
@@ -722,7 +722,7 @@
         <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1273</v>
+        <v>1275.7</v>
       </c>
       <c r="I9" t="n">
         <v>813.3</v>
@@ -790,19 +790,19 @@
         <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="E11" t="n">
         <v>33.9</v>
       </c>
       <c r="F11" t="n">
-        <v>89.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>770</v>
+        <v>768.6</v>
       </c>
       <c r="I11" t="n">
         <v>779.6</v>
@@ -824,7 +824,7 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="E12" t="n">
         <v>34</v>
@@ -836,7 +836,7 @@
         <v>3.4</v>
       </c>
       <c r="H12" t="n">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="I12" t="n">
         <v>785.8</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>25.8</v>
+        <v>25.1</v>
       </c>
       <c r="E14" t="n">
-        <v>13.8</v>
+        <v>12.4</v>
       </c>
       <c r="F14" t="n">
         <v>84.09999999999999</v>
@@ -904,10 +904,10 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>696.7</v>
+        <v>702.1</v>
       </c>
       <c r="I14" t="n">
-        <v>748.9</v>
+        <v>743.6</v>
       </c>
       <c r="J14" t="n">
         <v>906</v>
@@ -1241,7 +1241,9 @@
       <c r="AD2" t="n">
         <v>825</v>
       </c>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>718</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2080,7 +2082,9 @@
       <c r="AD13" t="n">
         <v>857</v>
       </c>
-      <c r="AE13" t="inlineStr"/>
+      <c r="AE13" t="n">
+        <v>783</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2232,7 +2236,9 @@
       <c r="AD15" t="n">
         <v>802</v>
       </c>
-      <c r="AE15" t="inlineStr"/>
+      <c r="AE15" t="n">
+        <v>602</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2539,7 +2545,9 @@
       <c r="AD2" t="n">
         <v>62.1</v>
       </c>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2789,7 +2797,7 @@
         <v>71.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>56.7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
@@ -2882,7 +2890,7 @@
         <v>6.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>53.9</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="7">
@@ -3064,7 +3072,7 @@
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>6.2</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="9">
@@ -3182,7 +3190,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>89.8</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -3378,7 +3386,9 @@
       <c r="AD13" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="AE13" t="inlineStr"/>
+      <c r="AE13" t="n">
+        <v>87.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3530,7 +3540,9 @@
       <c r="AD15" t="n">
         <v>53.4</v>
       </c>
-      <c r="AE15" t="inlineStr"/>
+      <c r="AE15" t="n">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4360,22 +4372,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C31" t="n">
-        <v>713.2</v>
+        <v>708</v>
       </c>
       <c r="D31" t="n">
-        <v>58.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="F31" t="n">
         <v>787</v>
       </c>
       <c r="G31" t="n">
-        <v>624</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="E2" t="n">
         <v>80.40000000000001</v>
@@ -496,7 +496,7 @@
         <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2079.9</v>
+        <v>2078.5</v>
       </c>
       <c r="I2" t="n">
         <v>887.6</v>
@@ -586,7 +586,7 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>68.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>76.5</v>
@@ -598,7 +598,7 @@
         <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1713.7</v>
+        <v>1714.2</v>
       </c>
       <c r="I5" t="n">
         <v>867.8</v>
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>56.6</v>
+        <v>56.8</v>
       </c>
       <c r="E7" t="n">
-        <v>56.8</v>
+        <v>57.4</v>
       </c>
       <c r="F7" t="n">
         <v>95.3</v>
@@ -666,10 +666,10 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1586</v>
+        <v>1648.1</v>
       </c>
       <c r="I7" t="n">
-        <v>838.9</v>
+        <v>835.1</v>
       </c>
       <c r="J7" t="n">
         <v>976</v>
@@ -688,10 +688,10 @@
         <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="E8" t="n">
-        <v>61.3</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
         <v>93.40000000000001</v>
@@ -700,7 +700,7 @@
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1205.1</v>
+        <v>1203.9</v>
       </c>
       <c r="I8" t="n">
         <v>843.8</v>
@@ -722,7 +722,7 @@
         <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1275.7</v>
+        <v>1274.4</v>
       </c>
       <c r="I9" t="n">
         <v>813.3</v>
@@ -796,13 +796,13 @@
         <v>33.9</v>
       </c>
       <c r="F11" t="n">
-        <v>88.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>768.6</v>
+        <v>769.2</v>
       </c>
       <c r="I11" t="n">
         <v>779.6</v>
@@ -824,7 +824,7 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="E12" t="n">
         <v>34</v>
@@ -836,7 +836,7 @@
         <v>3.4</v>
       </c>
       <c r="H12" t="n">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="I12" t="n">
         <v>785.8</v>
@@ -892,7 +892,7 @@
         <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="E14" t="n">
         <v>12.4</v>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>702.1</v>
+        <v>700.7</v>
       </c>
       <c r="I14" t="n">
         <v>743.6</v>
@@ -1680,7 +1680,9 @@
       <c r="AD7" t="n">
         <v>755</v>
       </c>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>730</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2546,7 +2548,7 @@
         <v>62.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>56</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="3">
@@ -2797,7 +2799,7 @@
         <v>71.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>59</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="6">
@@ -2890,7 +2892,7 @@
         <v>6.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>56.6</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="7">
@@ -2984,7 +2986,9 @@
       <c r="AD7" t="n">
         <v>35.7</v>
       </c>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>62.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3072,7 +3076,7 @@
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>10.2</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -3190,7 +3194,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>88.40000000000001</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11">
@@ -3387,7 +3391,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="AE13" t="n">
-        <v>87.2</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="14">
@@ -3541,7 +3545,7 @@
         <v>53.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -4372,16 +4376,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C31" t="n">
-        <v>708</v>
+        <v>710.8</v>
       </c>
       <c r="D31" t="n">
-        <v>66.09999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="E31" t="n">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="F31" t="n">
         <v>787</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>80.40000000000001</v>
@@ -496,7 +496,7 @@
         <v>19.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2078.5</v>
+        <v>2074</v>
       </c>
       <c r="I2" t="n">
         <v>887.6</v>
@@ -511,32 +511,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>waltkin</t>
+          <t>pparril</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>72.3</v>
       </c>
       <c r="E3" t="n">
-        <v>92.2</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>99.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>288.1</v>
+        <v>2023.6</v>
       </c>
       <c r="I3" t="n">
         <v>888.2</v>
       </c>
       <c r="J3" t="n">
-        <v>960</v>
+        <v>997</v>
       </c>
     </row>
     <row r="4">
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pparril</t>
+          <t>waltkin</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>71.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="E4" t="n">
-        <v>77.7</v>
+        <v>92.2</v>
       </c>
       <c r="F4" t="n">
-        <v>94.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="G4" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>1941.8</v>
+        <v>288.1</v>
       </c>
       <c r="I4" t="n">
-        <v>892.4</v>
+        <v>888.2</v>
       </c>
       <c r="J4" t="n">
-        <v>997</v>
+        <v>960</v>
       </c>
     </row>
     <row r="5">
@@ -586,7 +586,7 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="E5" t="n">
         <v>76.5</v>
@@ -598,7 +598,7 @@
         <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1714.2</v>
+        <v>1711.9</v>
       </c>
       <c r="I5" t="n">
         <v>867.8</v>
@@ -654,7 +654,7 @@
         <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
       <c r="E7" t="n">
         <v>57.4</v>
@@ -666,7 +666,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1648.1</v>
+        <v>1643.8</v>
       </c>
       <c r="I7" t="n">
         <v>835.1</v>
@@ -688,7 +688,7 @@
         <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>54.7</v>
+        <v>54.5</v>
       </c>
       <c r="E8" t="n">
         <v>61</v>
@@ -700,7 +700,7 @@
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1203.9</v>
+        <v>1199.5</v>
       </c>
       <c r="I8" t="n">
         <v>843.8</v>
@@ -722,7 +722,7 @@
         <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1274.4</v>
+        <v>1269.9</v>
       </c>
       <c r="I9" t="n">
         <v>813.3</v>
@@ -790,19 +790,19 @@
         <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="E11" t="n">
         <v>33.9</v>
       </c>
       <c r="F11" t="n">
-        <v>89</v>
+        <v>86.8</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>769.2</v>
+        <v>767</v>
       </c>
       <c r="I11" t="n">
         <v>779.6</v>
@@ -824,7 +824,7 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="E12" t="n">
         <v>34</v>
@@ -836,7 +836,7 @@
         <v>3.4</v>
       </c>
       <c r="H12" t="n">
-        <v>933</v>
+        <v>931.3</v>
       </c>
       <c r="I12" t="n">
         <v>785.8</v>
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>700.7</v>
+        <v>699.8</v>
       </c>
       <c r="I14" t="n">
         <v>743.6</v>
@@ -1334,7 +1334,9 @@
       <c r="AD3" t="n">
         <v>858</v>
       </c>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>774</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2548,7 +2550,7 @@
         <v>62.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>54.6</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="3">
@@ -2640,7 +2642,9 @@
       <c r="AD3" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>81.8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2799,7 +2803,7 @@
         <v>71.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>57.8</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="6">
@@ -2892,7 +2896,7 @@
         <v>6.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>55.3</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="7">
@@ -2987,7 +2991,7 @@
         <v>35.7</v>
       </c>
       <c r="AE7" t="n">
-        <v>62.1</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="8">
@@ -3076,7 +3080,7 @@
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
@@ -3194,7 +3198,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>89</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="11">
@@ -3391,7 +3395,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="AE13" t="n">
-        <v>87.7</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -3545,7 +3549,7 @@
         <v>53.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="16">
@@ -4376,16 +4380,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" t="n">
-        <v>710.8</v>
+        <v>717.8</v>
       </c>
       <c r="D31" t="n">
-        <v>62.3</v>
+        <v>62</v>
       </c>
       <c r="E31" t="n">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F31" t="n">
         <v>787</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" t="n">
-        <v>35.8</v>
+        <v>36.3</v>
       </c>
       <c r="E12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12" t="n">
         <v>90.90000000000001</v>
@@ -836,10 +836,10 @@
         <v>3.4</v>
       </c>
       <c r="H12" t="n">
-        <v>931.3</v>
+        <v>981.3</v>
       </c>
       <c r="I12" t="n">
-        <v>785.8</v>
+        <v>788</v>
       </c>
       <c r="J12" t="n">
         <v>928</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE16"/>
+  <dimension ref="A1:AF16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1151,6 +1151,11 @@
           <t>10/1/26</t>
         </is>
       </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>10/2/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1244,6 +1249,7 @@
       <c r="AE2" t="n">
         <v>718</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1337,6 +1343,7 @@
       <c r="AE3" t="n">
         <v>774</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1416,6 +1423,7 @@
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1497,6 +1505,7 @@
       <c r="AE5" t="n">
         <v>723</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1590,6 +1599,7 @@
       <c r="AE6" t="n">
         <v>719</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1685,6 +1695,7 @@
       <c r="AE7" t="n">
         <v>730</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1773,6 +1784,9 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
         <v>624</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>845</v>
       </c>
     </row>
     <row r="9">
@@ -1813,6 +1827,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1892,6 +1907,7 @@
       <c r="AE10" t="n">
         <v>787</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1945,6 +1961,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2002,6 +2019,7 @@
         <v>604</v>
       </c>
       <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2089,6 +2107,7 @@
       <c r="AE13" t="n">
         <v>783</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2150,6 +2169,7 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2243,6 +2263,7 @@
       <c r="AE15" t="n">
         <v>602</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2288,6 +2309,7 @@
         <v>945</v>
       </c>
       <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2300,7 +2322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE16"/>
+  <dimension ref="A1:AF16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2459,6 +2481,11 @@
           <t>10/1/26</t>
         </is>
       </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>10/2/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2552,6 +2579,7 @@
       <c r="AE2" t="n">
         <v>50.1</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2645,6 +2673,7 @@
       <c r="AE3" t="n">
         <v>81.8</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2724,6 +2753,7 @@
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2805,6 +2835,7 @@
       <c r="AE5" t="n">
         <v>53.4</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2898,6 +2929,7 @@
       <c r="AE6" t="n">
         <v>50.8</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2993,6 +3025,7 @@
       <c r="AE7" t="n">
         <v>57.8</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3081,6 +3114,9 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
         <v>6.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -3121,6 +3157,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3200,6 +3237,7 @@
       <c r="AE10" t="n">
         <v>86.8</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3253,6 +3291,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3310,6 +3349,7 @@
         <v>3.5</v>
       </c>
       <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3397,6 +3437,7 @@
       <c r="AE13" t="n">
         <v>85.40000000000001</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3458,6 +3499,7 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3551,6 +3593,7 @@
       <c r="AE15" t="n">
         <v>3.1</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3596,6 +3639,7 @@
         <v>92.8</v>
       </c>
       <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3608,7 +3652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4398,6 +4442,31 @@
         <v>602</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>10/2/26</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>845</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>845</v>
+      </c>
+      <c r="F32" t="n">
+        <v>845</v>
+      </c>
+      <c r="G32" t="n">
+        <v>845</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>45.4</v>
+        <v>44.3</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>47.9</v>
       </c>
       <c r="F9" t="n">
         <v>90.2</v>
@@ -734,10 +734,10 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1269.9</v>
+        <v>1285.8</v>
       </c>
       <c r="I9" t="n">
-        <v>813.3</v>
+        <v>814</v>
       </c>
       <c r="J9" t="n">
         <v>960</v>
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>37</v>
+        <v>37.6</v>
       </c>
       <c r="E10" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="F10" t="n">
-        <v>64.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>13.8</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>443.7</v>
+        <v>1015.4</v>
       </c>
       <c r="I10" t="n">
-        <v>764</v>
+        <v>788</v>
       </c>
       <c r="J10" t="n">
-        <v>916</v>
+        <v>928</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="E11" t="n">
-        <v>33.9</v>
+        <v>36.1</v>
       </c>
       <c r="F11" t="n">
-        <v>86.8</v>
+        <v>64.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>13.8</v>
       </c>
       <c r="H11" t="n">
-        <v>767</v>
+        <v>443.7</v>
       </c>
       <c r="I11" t="n">
-        <v>779.6</v>
+        <v>764</v>
       </c>
       <c r="J11" t="n">
-        <v>924</v>
+        <v>916</v>
       </c>
     </row>
     <row r="12">
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="E12" t="n">
-        <v>36</v>
+        <v>33.9</v>
       </c>
       <c r="F12" t="n">
-        <v>90.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="G12" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>981.3</v>
+        <v>767</v>
       </c>
       <c r="I12" t="n">
-        <v>788</v>
+        <v>779.6</v>
       </c>
       <c r="J12" t="n">
-        <v>928</v>
+        <v>924</v>
       </c>
     </row>
     <row r="13">
@@ -1599,7 +1599,9 @@
       <c r="AE6" t="n">
         <v>719</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>833</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2929,7 +2931,9 @@
       <c r="AE6" t="n">
         <v>50.8</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3116,7 +3120,7 @@
         <v>6.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>50</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -4449,22 +4453,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="F32" t="n">
         <v>845</v>
       </c>
       <c r="G32" t="n">
-        <v>845</v>
+        <v>833</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>72.3</v>
+        <v>72.7</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>78.2</v>
       </c>
       <c r="F3" t="n">
         <v>94.59999999999999</v>
@@ -530,10 +530,10 @@
         <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>2023.6</v>
+        <v>2109</v>
       </c>
       <c r="I3" t="n">
-        <v>888.2</v>
+        <v>888.6</v>
       </c>
       <c r="J3" t="n">
         <v>997</v>
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>56.7</v>
+        <v>55</v>
       </c>
       <c r="E7" t="n">
-        <v>57.4</v>
+        <v>56.8</v>
       </c>
       <c r="F7" t="n">
         <v>95.3</v>
@@ -666,10 +666,10 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1643.8</v>
+        <v>1648.8</v>
       </c>
       <c r="I7" t="n">
-        <v>835.1</v>
+        <v>830.1</v>
       </c>
       <c r="J7" t="n">
         <v>976</v>
@@ -722,10 +722,10 @@
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>44.3</v>
+        <v>45.8</v>
       </c>
       <c r="E9" t="n">
-        <v>47.9</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
         <v>90.2</v>
@@ -734,7 +734,7 @@
         <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1285.8</v>
+        <v>1328.6</v>
       </c>
       <c r="I9" t="n">
         <v>814</v>
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>37.6</v>
+        <v>37</v>
       </c>
       <c r="E10" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="F10" t="n">
-        <v>90.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4</v>
+        <v>13.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1015.4</v>
+        <v>443.7</v>
       </c>
       <c r="I10" t="n">
-        <v>788</v>
+        <v>764</v>
       </c>
       <c r="J10" t="n">
-        <v>928</v>
+        <v>916</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="E11" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>64.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
-        <v>443.7</v>
+        <v>995.8</v>
       </c>
       <c r="I11" t="n">
-        <v>764</v>
+        <v>788</v>
       </c>
       <c r="J11" t="n">
-        <v>916</v>
+        <v>928</v>
       </c>
     </row>
     <row r="12">
@@ -1343,7 +1343,9 @@
       <c r="AE3" t="n">
         <v>774</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>899</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1697,7 +1699,9 @@
       <c r="AE7" t="n">
         <v>730</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
+      <c r="AF7" t="n">
+        <v>686</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2675,7 +2679,9 @@
       <c r="AE3" t="n">
         <v>81.8</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>85.40000000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2932,7 +2938,7 @@
         <v>50.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>15.9</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="7">
@@ -3029,7 +3035,9 @@
       <c r="AE7" t="n">
         <v>57.8</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
+      <c r="AF7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3120,7 +3128,7 @@
         <v>6.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>84.09999999999999</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="9">
@@ -4453,22 +4461,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>839</v>
+        <v>815.8</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E32" t="n">
         <v>839</v>
       </c>
       <c r="F32" t="n">
-        <v>845</v>
+        <v>899</v>
       </c>
       <c r="G32" t="n">
-        <v>833</v>
+        <v>686</v>
       </c>
     </row>
   </sheetData>
